--- a/FincaOS_Data.xlsx
+++ b/FincaOS_Data.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="Rf796aefc1e124ccc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="Ra359c8b44596451d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="R23d99de1281045a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="R7d8a85c35e67482c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R996f4c1088e04f76"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="R517d35d3ccb74ec7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rad5c7874ac774de6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="R410a057a7e0d4537"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R8b47655fe9e3474b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="R8eeee3fc33104605"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="R0b86ea484d9743f4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R1012150921b5493e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="R41f029a7eeee41bc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rbb3d227439c340c8"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -60,7 +60,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="19">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -100,6 +100,7 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -385,7 +386,7 @@
       </x:c>
       <x:c r="B5" t="n">
         <x:f>COUNTIF(Unidades!E:E,"Activa")</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -394,7 +395,7 @@
       </x:c>
       <x:c r="B6" t="n">
         <x:f>COUNTIF(VistaCultivos!H:H,"CUL_DISPONIBLE")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -475,7 +476,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R063c53f7bcc449d2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab8b6e1440904f6d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -600,10 +601,10 @@
         <x:v>Cama</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>No activa</x:v>
+        <x:v>Activa</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Sin cultivos activos</x:v>
+        <x:v>Espacio disponible</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -663,7 +664,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb919dbf7118e4c22"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18e4de3126af4ffc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1129,7 +1130,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4cd7d521f1e049b0"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbce355b0b034631"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2111,10 +2112,272 @@
       </x:c>
       <x:c r="M26" s="11" t="str"/>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>SIE_FRA_018</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>UNI_FRA_CAMA_04</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>CUL_DISPONIBLE</x:v>
+      </x:c>
+      <x:c r="E27" s="18"/>
+      <x:c r="F27" s="18"/>
+      <x:c r="G27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Disponible</x:v>
+      </x:c>
+      <x:c r="I27" s="18"/>
+      <x:c r="J27" s="18"/>
+      <x:c r="K27" s="18"/>
+      <x:c r="L27" t="str">
+        <x:v>Completa</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>Espacio disponible</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="E28" s="18"/>
+      <x:c r="F28" s="18"/>
+      <x:c r="I28" s="18"/>
+      <x:c r="J28" s="18"/>
+      <x:c r="K28" s="18"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="E29" s="18"/>
+      <x:c r="F29" s="18"/>
+      <x:c r="I29" s="18"/>
+      <x:c r="J29" s="18"/>
+      <x:c r="K29" s="18"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="E30" s="18"/>
+      <x:c r="F30" s="18"/>
+      <x:c r="I30" s="18"/>
+      <x:c r="J30" s="18"/>
+      <x:c r="K30" s="18"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="E31" s="18"/>
+      <x:c r="F31" s="18"/>
+      <x:c r="I31" s="18"/>
+      <x:c r="J31" s="18"/>
+      <x:c r="K31" s="18"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="E32" s="18"/>
+      <x:c r="F32" s="18"/>
+      <x:c r="I32" s="18"/>
+      <x:c r="J32" s="18"/>
+      <x:c r="K32" s="18"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="E33" s="18"/>
+      <x:c r="F33" s="18"/>
+      <x:c r="I33" s="18"/>
+      <x:c r="J33" s="18"/>
+      <x:c r="K33" s="18"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="E34" s="18"/>
+      <x:c r="F34" s="18"/>
+      <x:c r="I34" s="18"/>
+      <x:c r="J34" s="18"/>
+      <x:c r="K34" s="18"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="E35" s="18"/>
+      <x:c r="F35" s="18"/>
+      <x:c r="I35" s="18"/>
+      <x:c r="J35" s="18"/>
+      <x:c r="K35" s="18"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="E36" s="18"/>
+      <x:c r="F36" s="18"/>
+      <x:c r="I36" s="18"/>
+      <x:c r="J36" s="18"/>
+      <x:c r="K36" s="18"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="E37" s="18"/>
+      <x:c r="F37" s="18"/>
+      <x:c r="I37" s="18"/>
+      <x:c r="J37" s="18"/>
+      <x:c r="K37" s="18"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="E38" s="18"/>
+      <x:c r="F38" s="18"/>
+      <x:c r="I38" s="18"/>
+      <x:c r="J38" s="18"/>
+      <x:c r="K38" s="18"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="E39" s="18"/>
+      <x:c r="F39" s="18"/>
+      <x:c r="I39" s="18"/>
+      <x:c r="J39" s="18"/>
+      <x:c r="K39" s="18"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="E40" s="18"/>
+      <x:c r="F40" s="18"/>
+      <x:c r="I40" s="18"/>
+      <x:c r="J40" s="18"/>
+      <x:c r="K40" s="18"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="E41" s="18"/>
+      <x:c r="F41" s="18"/>
+      <x:c r="I41" s="18"/>
+      <x:c r="J41" s="18"/>
+      <x:c r="K41" s="18"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="E42" s="18"/>
+      <x:c r="F42" s="18"/>
+      <x:c r="I42" s="18"/>
+      <x:c r="J42" s="18"/>
+      <x:c r="K42" s="18"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="E43" s="18"/>
+      <x:c r="F43" s="18"/>
+      <x:c r="I43" s="18"/>
+      <x:c r="J43" s="18"/>
+      <x:c r="K43" s="18"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="E44" s="18"/>
+      <x:c r="F44" s="18"/>
+      <x:c r="I44" s="18"/>
+      <x:c r="J44" s="18"/>
+      <x:c r="K44" s="18"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="E45" s="18"/>
+      <x:c r="F45" s="18"/>
+      <x:c r="I45" s="18"/>
+      <x:c r="J45" s="18"/>
+      <x:c r="K45" s="18"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="E46" s="18"/>
+      <x:c r="F46" s="18"/>
+      <x:c r="I46" s="18"/>
+      <x:c r="J46" s="18"/>
+      <x:c r="K46" s="18"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="E47" s="18"/>
+      <x:c r="F47" s="18"/>
+      <x:c r="I47" s="18"/>
+      <x:c r="J47" s="18"/>
+      <x:c r="K47" s="18"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="E48" s="18"/>
+      <x:c r="F48" s="18"/>
+      <x:c r="I48" s="18"/>
+      <x:c r="J48" s="18"/>
+      <x:c r="K48" s="18"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="E49" s="18"/>
+      <x:c r="F49" s="18"/>
+      <x:c r="I49" s="18"/>
+      <x:c r="J49" s="18"/>
+      <x:c r="K49" s="18"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="E50" s="18"/>
+      <x:c r="F50" s="18"/>
+      <x:c r="I50" s="18"/>
+      <x:c r="J50" s="18"/>
+      <x:c r="K50" s="18"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="E51" s="18"/>
+      <x:c r="F51" s="18"/>
+      <x:c r="I51" s="18"/>
+      <x:c r="J51" s="18"/>
+      <x:c r="K51" s="18"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="E52" s="18"/>
+      <x:c r="F52" s="18"/>
+      <x:c r="I52" s="18"/>
+      <x:c r="J52" s="18"/>
+      <x:c r="K52" s="18"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="E53" s="18"/>
+      <x:c r="F53" s="18"/>
+      <x:c r="I53" s="18"/>
+      <x:c r="J53" s="18"/>
+      <x:c r="K53" s="18"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="E54" s="18"/>
+      <x:c r="F54" s="18"/>
+      <x:c r="I54" s="18"/>
+      <x:c r="J54" s="18"/>
+      <x:c r="K54" s="18"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="E55" s="18"/>
+      <x:c r="F55" s="18"/>
+      <x:c r="I55" s="18"/>
+      <x:c r="J55" s="18"/>
+      <x:c r="K55" s="18"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="E56" s="18"/>
+      <x:c r="F56" s="18"/>
+      <x:c r="I56" s="18"/>
+      <x:c r="J56" s="18"/>
+      <x:c r="K56" s="18"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="E57" s="18"/>
+      <x:c r="F57" s="18"/>
+      <x:c r="I57" s="18"/>
+      <x:c r="J57" s="18"/>
+      <x:c r="K57" s="18"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="E58" s="18"/>
+      <x:c r="F58" s="18"/>
+      <x:c r="I58" s="18"/>
+      <x:c r="J58" s="18"/>
+      <x:c r="K58" s="18"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="E59" s="18"/>
+      <x:c r="F59" s="18"/>
+      <x:c r="I59" s="18"/>
+      <x:c r="J59" s="18"/>
+      <x:c r="K59" s="18"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="E60" s="18"/>
+      <x:c r="F60" s="18"/>
+      <x:c r="I60" s="18"/>
+      <x:c r="J60" s="18"/>
+      <x:c r="K60" s="18"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9e72ee909b7e401d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05c3115e59984aa8"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3408,10 +3671,282 @@
         <x:v>2026-07</x:v>
       </x:c>
     </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>SIE_FRA_018</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Cama Frailes 4</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>UNI_FRA_CAMA_04</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Disponible</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>CUL_DISPONIBLE</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>Disponible</x:v>
+      </x:c>
+      <x:c r="K27" s="18"/>
+      <x:c r="L27" s="18"/>
+      <x:c r="M27" s="18"/>
+      <x:c r="N27" s="18"/>
+      <x:c r="O27" s="18"/>
+      <x:c r="P27"/>
+      <x:c r="Q27" t="str">
+        <x:v>Sin fecha</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="K28" s="18"/>
+      <x:c r="L28" s="18"/>
+      <x:c r="M28" s="18"/>
+      <x:c r="N28" s="18"/>
+      <x:c r="O28" s="18"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="K29" s="18"/>
+      <x:c r="L29" s="18"/>
+      <x:c r="M29" s="18"/>
+      <x:c r="N29" s="18"/>
+      <x:c r="O29" s="18"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="K30" s="18"/>
+      <x:c r="L30" s="18"/>
+      <x:c r="M30" s="18"/>
+      <x:c r="N30" s="18"/>
+      <x:c r="O30" s="18"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="K31" s="18"/>
+      <x:c r="L31" s="18"/>
+      <x:c r="M31" s="18"/>
+      <x:c r="N31" s="18"/>
+      <x:c r="O31" s="18"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="K32" s="18"/>
+      <x:c r="L32" s="18"/>
+      <x:c r="M32" s="18"/>
+      <x:c r="N32" s="18"/>
+      <x:c r="O32" s="18"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="K33" s="18"/>
+      <x:c r="L33" s="18"/>
+      <x:c r="M33" s="18"/>
+      <x:c r="N33" s="18"/>
+      <x:c r="O33" s="18"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="K34" s="18"/>
+      <x:c r="L34" s="18"/>
+      <x:c r="M34" s="18"/>
+      <x:c r="N34" s="18"/>
+      <x:c r="O34" s="18"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="K35" s="18"/>
+      <x:c r="L35" s="18"/>
+      <x:c r="M35" s="18"/>
+      <x:c r="N35" s="18"/>
+      <x:c r="O35" s="18"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="K36" s="18"/>
+      <x:c r="L36" s="18"/>
+      <x:c r="M36" s="18"/>
+      <x:c r="N36" s="18"/>
+      <x:c r="O36" s="18"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="K37" s="18"/>
+      <x:c r="L37" s="18"/>
+      <x:c r="M37" s="18"/>
+      <x:c r="N37" s="18"/>
+      <x:c r="O37" s="18"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="K38" s="18"/>
+      <x:c r="L38" s="18"/>
+      <x:c r="M38" s="18"/>
+      <x:c r="N38" s="18"/>
+      <x:c r="O38" s="18"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="K39" s="18"/>
+      <x:c r="L39" s="18"/>
+      <x:c r="M39" s="18"/>
+      <x:c r="N39" s="18"/>
+      <x:c r="O39" s="18"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="K40" s="18"/>
+      <x:c r="L40" s="18"/>
+      <x:c r="M40" s="18"/>
+      <x:c r="N40" s="18"/>
+      <x:c r="O40" s="18"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="K41" s="18"/>
+      <x:c r="L41" s="18"/>
+      <x:c r="M41" s="18"/>
+      <x:c r="N41" s="18"/>
+      <x:c r="O41" s="18"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="K42" s="18"/>
+      <x:c r="L42" s="18"/>
+      <x:c r="M42" s="18"/>
+      <x:c r="N42" s="18"/>
+      <x:c r="O42" s="18"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="K43" s="18"/>
+      <x:c r="L43" s="18"/>
+      <x:c r="M43" s="18"/>
+      <x:c r="N43" s="18"/>
+      <x:c r="O43" s="18"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="K44" s="18"/>
+      <x:c r="L44" s="18"/>
+      <x:c r="M44" s="18"/>
+      <x:c r="N44" s="18"/>
+      <x:c r="O44" s="18"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="K45" s="18"/>
+      <x:c r="L45" s="18"/>
+      <x:c r="M45" s="18"/>
+      <x:c r="N45" s="18"/>
+      <x:c r="O45" s="18"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="K46" s="18"/>
+      <x:c r="L46" s="18"/>
+      <x:c r="M46" s="18"/>
+      <x:c r="N46" s="18"/>
+      <x:c r="O46" s="18"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="K47" s="18"/>
+      <x:c r="L47" s="18"/>
+      <x:c r="M47" s="18"/>
+      <x:c r="N47" s="18"/>
+      <x:c r="O47" s="18"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="K48" s="18"/>
+      <x:c r="L48" s="18"/>
+      <x:c r="M48" s="18"/>
+      <x:c r="N48" s="18"/>
+      <x:c r="O48" s="18"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="K49" s="18"/>
+      <x:c r="L49" s="18"/>
+      <x:c r="M49" s="18"/>
+      <x:c r="N49" s="18"/>
+      <x:c r="O49" s="18"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="K50" s="18"/>
+      <x:c r="L50" s="18"/>
+      <x:c r="M50" s="18"/>
+      <x:c r="N50" s="18"/>
+      <x:c r="O50" s="18"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="K51" s="18"/>
+      <x:c r="L51" s="18"/>
+      <x:c r="M51" s="18"/>
+      <x:c r="N51" s="18"/>
+      <x:c r="O51" s="18"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="K52" s="18"/>
+      <x:c r="L52" s="18"/>
+      <x:c r="M52" s="18"/>
+      <x:c r="N52" s="18"/>
+      <x:c r="O52" s="18"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="K53" s="18"/>
+      <x:c r="L53" s="18"/>
+      <x:c r="M53" s="18"/>
+      <x:c r="N53" s="18"/>
+      <x:c r="O53" s="18"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="K54" s="18"/>
+      <x:c r="L54" s="18"/>
+      <x:c r="M54" s="18"/>
+      <x:c r="N54" s="18"/>
+      <x:c r="O54" s="18"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="K55" s="18"/>
+      <x:c r="L55" s="18"/>
+      <x:c r="M55" s="18"/>
+      <x:c r="N55" s="18"/>
+      <x:c r="O55" s="18"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="K56" s="18"/>
+      <x:c r="L56" s="18"/>
+      <x:c r="M56" s="18"/>
+      <x:c r="N56" s="18"/>
+      <x:c r="O56" s="18"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="K57" s="18"/>
+      <x:c r="L57" s="18"/>
+      <x:c r="M57" s="18"/>
+      <x:c r="N57" s="18"/>
+      <x:c r="O57" s="18"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="K58" s="18"/>
+      <x:c r="L58" s="18"/>
+      <x:c r="M58" s="18"/>
+      <x:c r="N58" s="18"/>
+      <x:c r="O58" s="18"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="K59" s="18"/>
+      <x:c r="L59" s="18"/>
+      <x:c r="M59" s="18"/>
+      <x:c r="N59" s="18"/>
+      <x:c r="O59" s="18"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="K60" s="18"/>
+      <x:c r="L60" s="18"/>
+      <x:c r="M60" s="18"/>
+      <x:c r="N60" s="18"/>
+      <x:c r="O60" s="18"/>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R67bfee80707b40a6"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfb2610916084ac5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3491,7 +4026,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4a57a00970ed48a4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R424b526d81824a0b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/FincaOS_Data.xlsx
+++ b/FincaOS_Data.xlsx
@@ -2,13 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="R410a057a7e0d4537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R8b47655fe9e3474b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="R8eeee3fc33104605"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="R0b86ea484d9743f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R1012150921b5493e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="R41f029a7eeee41bc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rbb3d227439c340c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="R9aad752ec9a94537"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R4227a49d0f304110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="R9dd6a40f9cb141f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="Rc586b383e229446b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R7b4481c77f444a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="Ra67245b67036419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rec6e71267c9e4fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="8" r:id="R92d437cfcdcb4aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arboles" sheetId="9" r:id="R4f69b264cfb94400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventosAgricolas" sheetId="10" r:id="Rcf79399ec49c4a7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -40,7 +43,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="4">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -52,6 +55,11 @@
         <x:fgColor rgb="14532D"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="0F3D25"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -60,7 +68,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="20">
+  <x:cellXfs count="25">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -101,6 +109,17 @@
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="200" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -421,6 +440,810 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="8.210000038146973" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.729999542236328" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18.84000015258789" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="6.460000038146973" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.09000015258789" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="5.650000095367432" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="21.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11.569999694824219" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="15.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13.460000038146973" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="31.6299991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>ID_Evento</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>Tipo_Evento</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>ID_Insumo</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>Nombre_Insumo</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>Target_Tipo</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>Target_ID</x:v>
+      </x:c>
+      <x:c r="G1" s="24" t="str">
+        <x:v>Target_Label</x:v>
+      </x:c>
+      <x:c r="H1" s="24" t="str">
+        <x:v>Finca_ID</x:v>
+      </x:c>
+      <x:c r="I1" s="24" t="str">
+        <x:v>Finca</x:v>
+      </x:c>
+      <x:c r="J1" s="24" t="str">
+        <x:v>Unidad_ID</x:v>
+      </x:c>
+      <x:c r="K1" s="24" t="str">
+        <x:v>Unidad</x:v>
+      </x:c>
+      <x:c r="L1" s="24" t="str">
+        <x:v>Cultivo_ID</x:v>
+      </x:c>
+      <x:c r="M1" s="24" t="str">
+        <x:v>Cultivo</x:v>
+      </x:c>
+      <x:c r="N1" s="24" t="str">
+        <x:v>Arbol_ID</x:v>
+      </x:c>
+      <x:c r="O1" s="24" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="P1" s="24" t="str">
+        <x:v>Fecha_Programada</x:v>
+      </x:c>
+      <x:c r="Q1" s="24" t="str">
+        <x:v>Fecha_Realizada</x:v>
+      </x:c>
+      <x:c r="R1" s="24" t="str">
+        <x:v>Estado</x:v>
+      </x:c>
+      <x:c r="S1" s="24" t="str">
+        <x:v>Notas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>EVT_001</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>INS_COBRE</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Cobre</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>Cultivo</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>SIE_FRA_003</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>Cama Frailes 1 - Pepino</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str">
+        <x:v>UNI_FRA_CAMA_01</x:v>
+      </x:c>
+      <x:c r="K2" s="11" t="str">
+        <x:v>Cama Frailes 1</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="str">
+        <x:v>CUL_PEPINO</x:v>
+      </x:c>
+      <x:c r="M2" s="11" t="str">
+        <x:v>Pepino</x:v>
+      </x:c>
+      <x:c r="N2" s="11" t="str"/>
+      <x:c r="O2" s="11" t="str"/>
+      <x:c r="P2" s="14"/>
+      <x:c r="Q2" s="14" t="n">
+        <x:v>46152</x:v>
+      </x:c>
+      <x:c r="R2" s="11" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="S2" s="11" t="str">
+        <x:v>Ejemplo: control fitosanitario con cobre</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>EVT_002</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>INS_MISTRAL</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>Cultivo</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>SIE_FRA_003</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>Cama Frailes 1 - Pepino</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str">
+        <x:v>UNI_FRA_CAMA_01</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="str">
+        <x:v>Cama Frailes 1</x:v>
+      </x:c>
+      <x:c r="L3" s="11" t="str">
+        <x:v>CUL_PEPINO</x:v>
+      </x:c>
+      <x:c r="M3" s="11" t="str">
+        <x:v>Pepino</x:v>
+      </x:c>
+      <x:c r="N3" s="11" t="str"/>
+      <x:c r="O3" s="11" t="str"/>
+      <x:c r="P3" s="14" t="n">
+        <x:v>46188</x:v>
+      </x:c>
+      <x:c r="Q3" s="14"/>
+      <x:c r="R3" s="11" t="str">
+        <x:v>No empezado</x:v>
+      </x:c>
+      <x:c r="S3" s="11" t="str">
+        <x:v>Próximo control fitosanitario</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>EVT_003</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>INS_CAL_DOLOMITA</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Cal Dolomita</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>Guayaba - Frailes</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str"/>
+      <x:c r="K4" s="11" t="str"/>
+      <x:c r="L4" s="11" t="str"/>
+      <x:c r="M4" s="11" t="str"/>
+      <x:c r="N4" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="O4" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="P4" s="14"/>
+      <x:c r="Q4" s="14" t="n">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="R4" s="11" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="S4" s="11" t="str">
+        <x:v>Aplicación de cal dolomita</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>EVT_004</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>INS_YARAMILA</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>Guayaba - Frailes</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str"/>
+      <x:c r="K5" s="11" t="str"/>
+      <x:c r="L5" s="11" t="str"/>
+      <x:c r="M5" s="11" t="str"/>
+      <x:c r="N5" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="O5" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="P5" s="14"/>
+      <x:c r="Q5" s="14" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="R5" s="11" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="S5" s="11" t="str">
+        <x:v>Aplicación de YaraMila</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>EVT_005</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>INS_MISTRAL</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>Mango peludo - Frailes</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str"/>
+      <x:c r="K6" s="11" t="str"/>
+      <x:c r="L6" s="11" t="str"/>
+      <x:c r="M6" s="11" t="str"/>
+      <x:c r="N6" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="O6" s="11" t="str">
+        <x:v>Mango peludo</x:v>
+      </x:c>
+      <x:c r="P6" s="14" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="Q6" s="14"/>
+      <x:c r="R6" s="11" t="str">
+        <x:v>No empezado</x:v>
+      </x:c>
+      <x:c r="S6" s="11" t="str">
+        <x:v>Control fitosanitario programado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>EVT_006</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>Poda</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str"/>
+      <x:c r="D7" s="11" t="str"/>
+      <x:c r="E7" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>Mango peludo - Frailes</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str"/>
+      <x:c r="K7" s="11" t="str"/>
+      <x:c r="L7" s="11" t="str"/>
+      <x:c r="M7" s="11" t="str"/>
+      <x:c r="N7" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="O7" s="11" t="str">
+        <x:v>Mango peludo</x:v>
+      </x:c>
+      <x:c r="P7" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="Q7" s="14"/>
+      <x:c r="R7" s="11" t="str">
+        <x:v>No empezado</x:v>
+      </x:c>
+      <x:c r="S7" s="11" t="str">
+        <x:v>Poda programada</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>EVT_007</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>INS_CALCIO_BORO</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>Calcio Boro</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>Manzano tico - Moravia</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str"/>
+      <x:c r="K8" s="11" t="str"/>
+      <x:c r="L8" s="11" t="str"/>
+      <x:c r="M8" s="11" t="str"/>
+      <x:c r="N8" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="O8" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="P8" s="14" t="n">
+        <x:v>46193</x:v>
+      </x:c>
+      <x:c r="Q8" s="14"/>
+      <x:c r="R8" s="11" t="str">
+        <x:v>No empezado</x:v>
+      </x:c>
+      <x:c r="S8" s="11" t="str">
+        <x:v>Apoyo foliar en llenado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="P9" s="18"/>
+      <x:c r="Q9" s="18"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="P10" s="18"/>
+      <x:c r="Q10" s="18"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="P11" s="18"/>
+      <x:c r="Q11" s="18"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="P12" s="18"/>
+      <x:c r="Q12" s="18"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="P13" s="18"/>
+      <x:c r="Q13" s="18"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="P14" s="18"/>
+      <x:c r="Q14" s="18"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="P15" s="18"/>
+      <x:c r="Q15" s="18"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="P16" s="18"/>
+      <x:c r="Q16" s="18"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="P17" s="18"/>
+      <x:c r="Q17" s="18"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="P18" s="18"/>
+      <x:c r="Q18" s="18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="P19" s="18"/>
+      <x:c r="Q19" s="18"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="P20" s="18"/>
+      <x:c r="Q20" s="18"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="P21" s="18"/>
+      <x:c r="Q21" s="18"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="P22" s="18"/>
+      <x:c r="Q22" s="18"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="P23" s="18"/>
+      <x:c r="Q23" s="18"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="P24" s="18"/>
+      <x:c r="Q24" s="18"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="P25" s="18"/>
+      <x:c r="Q25" s="18"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="P26" s="18"/>
+      <x:c r="Q26" s="18"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="P27" s="18"/>
+      <x:c r="Q27" s="18"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="P28" s="18"/>
+      <x:c r="Q28" s="18"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="P29" s="18"/>
+      <x:c r="Q29" s="18"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="P30" s="18"/>
+      <x:c r="Q30" s="18"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="P31" s="18"/>
+      <x:c r="Q31" s="18"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="P32" s="18"/>
+      <x:c r="Q32" s="18"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="P33" s="18"/>
+      <x:c r="Q33" s="18"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="P34" s="18"/>
+      <x:c r="Q34" s="18"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="P35" s="18"/>
+      <x:c r="Q35" s="18"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="P36" s="18"/>
+      <x:c r="Q36" s="18"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="P37" s="18"/>
+      <x:c r="Q37" s="18"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="P38" s="18"/>
+      <x:c r="Q38" s="18"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="P39" s="18"/>
+      <x:c r="Q39" s="18"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="P40" s="18"/>
+      <x:c r="Q40" s="18"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="P41" s="18"/>
+      <x:c r="Q41" s="18"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="P42" s="18"/>
+      <x:c r="Q42" s="18"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="P43" s="18"/>
+      <x:c r="Q43" s="18"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="P44" s="18"/>
+      <x:c r="Q44" s="18"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="P45" s="18"/>
+      <x:c r="Q45" s="18"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="P46" s="18"/>
+      <x:c r="Q46" s="18"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="P47" s="18"/>
+      <x:c r="Q47" s="18"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="P48" s="18"/>
+      <x:c r="Q48" s="18"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="P49" s="18"/>
+      <x:c r="Q49" s="18"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="P50" s="18"/>
+      <x:c r="Q50" s="18"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="P51" s="18"/>
+      <x:c r="Q51" s="18"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="P52" s="18"/>
+      <x:c r="Q52" s="18"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="P53" s="18"/>
+      <x:c r="Q53" s="18"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="P54" s="18"/>
+      <x:c r="Q54" s="18"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="P55" s="18"/>
+      <x:c r="Q55" s="18"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="P56" s="18"/>
+      <x:c r="Q56" s="18"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="P57" s="18"/>
+      <x:c r="Q57" s="18"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="P58" s="18"/>
+      <x:c r="Q58" s="18"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="P59" s="18"/>
+      <x:c r="Q59" s="18"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="P60" s="18"/>
+      <x:c r="Q60" s="18"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="P61" s="18"/>
+      <x:c r="Q61" s="18"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="P62" s="18"/>
+      <x:c r="Q62" s="18"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="P63" s="18"/>
+      <x:c r="Q63" s="18"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="P64" s="18"/>
+      <x:c r="Q64" s="18"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="P65" s="18"/>
+      <x:c r="Q65" s="18"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="P66" s="18"/>
+      <x:c r="Q66" s="18"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="P67" s="18"/>
+      <x:c r="Q67" s="18"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="P68" s="18"/>
+      <x:c r="Q68" s="18"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="P69" s="18"/>
+      <x:c r="Q69" s="18"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="P70" s="18"/>
+      <x:c r="Q70" s="18"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="P71" s="18"/>
+      <x:c r="Q71" s="18"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="P72" s="18"/>
+      <x:c r="Q72" s="18"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="P73" s="18"/>
+      <x:c r="Q73" s="18"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="P74" s="18"/>
+      <x:c r="Q74" s="18"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="P75" s="18"/>
+      <x:c r="Q75" s="18"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="P76" s="18"/>
+      <x:c r="Q76" s="18"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="P77" s="18"/>
+      <x:c r="Q77" s="18"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="P78" s="18"/>
+      <x:c r="Q78" s="18"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="P79" s="18"/>
+      <x:c r="Q79" s="18"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="P80" s="18"/>
+      <x:c r="Q80" s="18"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="P81" s="18"/>
+      <x:c r="Q81" s="18"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="P82" s="18"/>
+      <x:c r="Q82" s="18"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="P83" s="18"/>
+      <x:c r="Q83" s="18"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="P84" s="18"/>
+      <x:c r="Q84" s="18"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="P85" s="18"/>
+      <x:c r="Q85" s="18"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="P86" s="18"/>
+      <x:c r="Q86" s="18"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="P87" s="18"/>
+      <x:c r="Q87" s="18"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="P88" s="18"/>
+      <x:c r="Q88" s="18"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="P89" s="18"/>
+      <x:c r="Q89" s="18"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="P90" s="18"/>
+      <x:c r="Q90" s="18"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="P91" s="18"/>
+      <x:c r="Q91" s="18"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="P92" s="18"/>
+      <x:c r="Q92" s="18"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="P93" s="18"/>
+      <x:c r="Q93" s="18"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="P94" s="18"/>
+      <x:c r="Q94" s="18"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="P95" s="18"/>
+      <x:c r="Q95" s="18"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="P96" s="18"/>
+      <x:c r="Q96" s="18"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="P97" s="18"/>
+      <x:c r="Q97" s="18"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="P98" s="18"/>
+      <x:c r="Q98" s="18"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="P99" s="18"/>
+      <x:c r="Q99" s="18"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="P100" s="18"/>
+      <x:c r="Q100" s="18"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
@@ -476,7 +1299,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rab8b6e1440904f6d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c2aa61fcde94ed2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -664,7 +1487,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R18e4de3126af4ffc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4a4299ed9a4465"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1130,7 +1953,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdbce355b0b034631"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92f6337ef8614c14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1194,6 +2017,9 @@
       <x:c r="M1" s="10" t="str">
         <x:v>Notas</x:v>
       </x:c>
+      <x:c r="N1" s="23" t="str">
+        <x:v>Evento_Agricola</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -1231,6 +2057,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M2" s="11" t="str"/>
+      <x:c r="N2" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -1268,6 +2097,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M3" s="11" t="str"/>
+      <x:c r="N3" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -1305,6 +2137,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M4" s="11" t="str"/>
+      <x:c r="N4" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -1342,6 +2177,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M5" s="11" t="str"/>
+      <x:c r="N5" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -1379,6 +2217,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M6" s="11" t="str"/>
+      <x:c r="N6" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -1416,6 +2257,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M7" s="11" t="str"/>
+      <x:c r="N7" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -1453,6 +2297,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M8" s="11" t="str"/>
+      <x:c r="N8" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -1484,6 +2331,9 @@
       <x:c r="M9" s="11" t="str">
         <x:v>Espacio disponible</x:v>
       </x:c>
+      <x:c r="N9" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -1521,6 +2371,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M10" s="11" t="str"/>
+      <x:c r="N10" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -1558,6 +2411,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M11" s="11" t="str"/>
+      <x:c r="N11" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -1595,6 +2451,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M12" s="11" t="str"/>
+      <x:c r="N12" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -1632,6 +2491,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M13" s="11" t="str"/>
+      <x:c r="N13" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -1669,6 +2531,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M14" s="11" t="str"/>
+      <x:c r="N14" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -1706,6 +2571,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M15" s="11" t="str"/>
+      <x:c r="N15" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -1743,6 +2611,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M16" s="11" t="str"/>
+      <x:c r="N16" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -1780,6 +2651,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M17" s="11" t="str"/>
+      <x:c r="N17" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
@@ -1819,6 +2693,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M18" s="11" t="str"/>
+      <x:c r="N18" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -1856,6 +2733,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M19" s="11" t="str"/>
+      <x:c r="N19" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -1893,6 +2773,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M20" s="11" t="str"/>
+      <x:c r="N20" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -1930,6 +2813,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M21" s="11" t="str"/>
+      <x:c r="N21" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -1969,6 +2855,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M22" s="11" t="str"/>
+      <x:c r="N22" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -2006,6 +2895,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M23" s="11" t="str"/>
+      <x:c r="N23" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
@@ -2037,6 +2929,9 @@
       <x:c r="M24" s="11" t="str">
         <x:v>Espacio disponible</x:v>
       </x:c>
+      <x:c r="N24" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
@@ -2074,6 +2969,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M25" s="11" t="str"/>
+      <x:c r="N25" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -2111,6 +3009,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M26" s="11" t="str"/>
+      <x:c r="N26" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" t="str">
@@ -2141,6 +3042,9 @@
       </x:c>
       <x:c r="M27" t="str">
         <x:v>Espacio disponible</x:v>
+      </x:c>
+      <x:c r="N27" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2377,7 +3281,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05c3115e59984aa8"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refc14cba555b43ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2457,6 +3361,9 @@
       <x:c r="Q1" s="10" t="str">
         <x:v>Mes_Cosecha</x:v>
       </x:c>
+      <x:c r="R1" s="23" t="str">
+        <x:v>Evento_Agricola</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -2506,6 +3413,9 @@
       <x:c r="Q2" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R2" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -2555,6 +3465,9 @@
       <x:c r="Q3" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
+      <x:c r="R3" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -2604,6 +3517,9 @@
       <x:c r="Q4" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R4" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -2653,6 +3569,9 @@
       <x:c r="Q5" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
+      <x:c r="R5" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -2702,6 +3621,9 @@
       <x:c r="Q6" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
+      <x:c r="R6" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -2751,6 +3673,9 @@
       <x:c r="Q7" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R7" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -2799,6 +3724,9 @@
       <x:c r="P8" s="11" t="str"/>
       <x:c r="Q8" s="11" t="str">
         <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="R8" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -2841,6 +3769,9 @@
       <x:c r="Q9" s="11" t="str">
         <x:v>Sin fecha</x:v>
       </x:c>
+      <x:c r="R9" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -2890,6 +3821,9 @@
       <x:c r="Q10" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R10" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -2939,6 +3873,9 @@
       <x:c r="Q11" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R11" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -2988,6 +3925,9 @@
       <x:c r="Q12" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R12" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -3037,6 +3977,9 @@
       <x:c r="Q13" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R13" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -3086,6 +4029,9 @@
       <x:c r="Q14" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R14" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -3135,6 +4081,9 @@
       <x:c r="Q15" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R15" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -3184,6 +4133,9 @@
       <x:c r="Q16" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R16" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -3233,6 +4185,9 @@
       <x:c r="Q17" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R17" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
@@ -3284,6 +4239,9 @@
       <x:c r="Q18" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R18" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -3333,6 +4291,9 @@
       <x:c r="Q19" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R19" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -3382,6 +4343,9 @@
       <x:c r="Q20" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R20" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -3431,6 +4395,9 @@
       <x:c r="Q21" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R21" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -3482,6 +4449,9 @@
       <x:c r="Q22" s="11" t="str">
         <x:v>2026-08</x:v>
       </x:c>
+      <x:c r="R22" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -3530,6 +4500,9 @@
       <x:c r="P23" s="11" t="str"/>
       <x:c r="Q23" s="11" t="str">
         <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="R23" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -3572,6 +4545,9 @@
       <x:c r="Q24" s="11" t="str">
         <x:v>Sin fecha</x:v>
       </x:c>
+      <x:c r="R24" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
@@ -3621,6 +4597,9 @@
       <x:c r="Q25" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R25" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -3669,6 +4648,9 @@
       <x:c r="P26" s="11" t="str"/>
       <x:c r="Q26" s="11" t="str">
         <x:v>2026-07</x:v>
+      </x:c>
+      <x:c r="R26" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -3711,6 +4693,9 @@
       <x:c r="Q27" t="str">
         <x:v>Sin fecha</x:v>
       </x:c>
+      <x:c r="R27" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="K28" s="18"/>
@@ -3946,7 +4931,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcfb2610916084ac5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24f9597babe14961"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4026,7 +5011,947 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R424b526d81824a0b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc327f05eb480415e"/>
   </x:tableParts>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="17.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.959999084472656" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="43.34000015258789" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="51.68000030517578" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>ID_Insumo</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>Nombre</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>Tipo</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>Disponible</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>Uso_Principal</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>Restricciones/Notas</x:v>
+      </x:c>
+      <x:c r="G1" s="24" t="str">
+        <x:v>Compra_Requerida</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>INS_COBRE</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>Cobre</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>Hongos y bacterias en manejo preventivo/correctivo</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>Evitar mezclar sin validar compatibilidad; aplicar temprano/tarde</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>INS_NEEM</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>Neem</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>Control preventivo de insectos blandos</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>Evitar sol fuerte; repetir según presión de plaga</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>INS_JABON_POTASICO</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Jabón Potásico</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Control de insectos blandos y limpieza foliar</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>Probar en pocas hojas antes de aplicar general</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>INS_MISTRAL</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Control fitosanitario según etiqueta</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Usar dosis de etiqueta; no aplicar en horas de calor</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>INS_BICARBONATO</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Bicarbonato de Sodio</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Apoyo preventivo contra hongos superficiales</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>No abusar; puede quemar hojas si se concentra</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>INS_CAL_DOLOMITA</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>Cal Dolomita</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>Corrección de suelo y aporte de calcio/magnesio</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>No aplicar pegado al tronco; incorporar superficialmente</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>INS_CENIZA</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>Ceniza</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>Aporte de potasio y minerales; enmienda suave</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>Usar moderado; puede subir pH</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>INS_MELASA</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>Melasa</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>Activación biológica en mezclas y compost</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>Usar dosis baja; evitar exceso de azúcar</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>INS_COMPOST</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Compost</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>Materia orgánica y mejora del suelo</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>Aplicar maduro; evitar contacto directo con cuello</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>INS_HENO</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>Heno</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>Cobertura/mulch para humedad y protección de suelo</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>Mantener separado del tronco para evitar hongos</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>INS_GALLINAZA</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>Gallinaza</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>Abono orgánico alto en nitrógeno</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>Debe estar compostada; riesgo de quemar raíces</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
+        <x:v>INS_YARAMILA</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>Fertilización granulada de suelo</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>Usar dosis controlada; evitar excesos de nitrógeno</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="str">
+        <x:v>INS_CALCIO_BORO</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>Calcio Boro</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>Floración, cuajado y llenado temprano</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>Aplicar temprano/tarde; no mezclar sin validar</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="str">
+        <x:v>INS_MULTIMINERAL</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>Multimineral</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>Corrección/apoyo nutricional foliar</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="str">
+        <x:v>Respetar dosis; evitar estrés fuerte</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11" t="str">
+        <x:v>INS_FOLIAR_7425</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>Foliar 7-4-25</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>Apoyo potasio/foliar en desarrollo y llenado</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>Usar según etapa; evitar exceso</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11" t="str">
+        <x:v>INS_PAS80</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>PAS-80</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>Coadyuvante</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>Mejorar adherencia/cobertura de aplicaciones foliares</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>Usar dosis baja según etiqueta</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="28.399999618530273" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.460000038146973" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.149999618530273" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.210000038146973" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.479999542236328" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.729999542236328" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="35.2599983215332" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>Arbol_ID</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>Finca_ID</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>Finca</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>Icono</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>Estado_Fenologico</x:v>
+      </x:c>
+      <x:c r="G1" s="24" t="str">
+        <x:v>Trasplante</x:v>
+      </x:c>
+      <x:c r="H1" s="24" t="str">
+        <x:v>Estado_Sanitario</x:v>
+      </x:c>
+      <x:c r="I1" s="24" t="str">
+        <x:v>Evento_Agricola</x:v>
+      </x:c>
+      <x:c r="J1" s="24" t="str">
+        <x:v>Notas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>🍎</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>Llenado</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str">
+        <x:v>Poda y manejo de chupones en seguimiento</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>ARB_GUAYABITA_MORAVIA</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>Guayabita del Perú</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H3" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str">
+        <x:v>Guayabita del Perú está en Moravia</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>Floración</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
+        <x:v>Diferente a Guayabita del Perú</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>ARB_GUANABANA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Guanábana</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Fructificación</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>Atención</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str">
+        <x:v>Puntos negros en frutos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>ARB_NARANJA_WASH_FRAILES</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Naranja Washington</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>🍊</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>Trasplante 2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>ARB_NARANJA_VALENCIA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>Naranja Valencia</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>🍊</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>Trasplante 2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>ARB_LIMON_MANDARINA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>Limón mandarina</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>🍋</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>Trasplante 2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>ARB_LIMON_MESINO_FRAILES</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>Limón mesino</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>🍋</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str">
+        <x:v>Trasplante 2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>ARB_LIMON_DULCE_FRAILES</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>Limón dulce</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>🍋</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str">
+        <x:v>Trasplante 2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>ARB_MANDARINA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>Mandarina</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>🍊</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>Brotes</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str">
+        <x:v>Trasplante 2025</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>ARB_ANONA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>Anona</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>Recuperación</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H12" s="11" t="str">
+        <x:v>Estrés</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str">
+        <x:v>Defoliación/recuperación</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
+        <x:v>ARB_NISPERO_FRAILES</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>Níspero</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>Establecimiento</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>Reciente</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="J13" s="11" t="str">
+        <x:v>Árbol joven</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="str">
+        <x:v>ARB_DURAZNO_FRAILES</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>Durazno</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>🌸</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H14" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I14" s="11" t="str">
+        <x:v>Poda</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>Mango peludo</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>🥭</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H15" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I15" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="J15" s="11" t="str">
+        <x:v>Mango 10 años</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11" t="str">
+        <x:v>ARB_MAMON_CHINO_FRAILES</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>Mamón chino</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>Recuperación</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H16" s="11" t="str">
+        <x:v>Atención</x:v>
+      </x:c>
+      <x:c r="I16" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="J16" s="11" t="str">
+        <x:v>Afectación por viento</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>
--- a/FincaOS_Data.xlsx
+++ b/FincaOS_Data.xlsx
@@ -2,16 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="R9aad752ec9a94537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R4227a49d0f304110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="R9dd6a40f9cb141f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="Rc586b383e229446b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R7b4481c77f444a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="Ra67245b67036419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rec6e71267c9e4fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="8" r:id="R92d437cfcdcb4aa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arboles" sheetId="9" r:id="R4f69b264cfb94400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventosAgricolas" sheetId="10" r:id="Rcf79399ec49c4a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="Ra43604a3c683445d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R973cb70a12954716"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="Rb7a45f49bd824085"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="R1509134335564d4c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R40779fc320d0450d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="Rc7bde972848c4607"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="R0ad2d651e18d4b60"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camas" sheetId="8" r:id="R255ab1e13d80424d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="9" r:id="Ra859057da49d4c2c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arboles" sheetId="10" r:id="R3eecabfe036047e6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventosAgricolas" sheetId="11" r:id="Rfedd0e27ffb64ab5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HistorialResumen" sheetId="12" r:id="R25f0607c196541be"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -57,7 +59,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="0F3D25"/>
+        <x:fgColor rgb="14532D"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -405,7 +407,7 @@
       </x:c>
       <x:c r="B5" t="n">
         <x:f>COUNTIF(Unidades!E:E,"Activa")</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -414,7 +416,7 @@
       </x:c>
       <x:c r="B6" t="n">
         <x:f>COUNTIF(VistaCultivos!H:H,"CUL_DISPONIBLE")</x:f>
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -444,25 +446,529 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="23.420000076293945" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="11.84000015258789" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15.069999694824219" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="15.069999694824219" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="4.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16.81999969482422" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13.729999542236328" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="32.29999923706055" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>Arbol_ID</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>Finca_ID</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>Finca_Nombre</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>Arbol_Nombre</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>Especie</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>Icono</x:v>
+      </x:c>
+      <x:c r="G1" s="24" t="str">
+        <x:v>Estado_Fenologico</x:v>
+      </x:c>
+      <x:c r="H1" s="24" t="str">
+        <x:v>Fecha_Trasplante</x:v>
+      </x:c>
+      <x:c r="I1" s="24" t="str">
+        <x:v>Estado_Sanitario</x:v>
+      </x:c>
+      <x:c r="J1" s="24" t="str">
+        <x:v>Notas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>Manzano</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>🍎</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>Llenado de fruto</x:v>
+      </x:c>
+      <x:c r="H2" s="14"/>
+      <x:c r="I2" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str">
+        <x:v>Poda y amarre previos; revisar chupones</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>ARB_GUAYABITA_MORAVIA</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>Guayabita del Perú</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
+        <x:v>Guayabita del Perú</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>🍈</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H3" s="14"/>
+      <x:c r="I3" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str">
+        <x:v>Unidad distinta de Guayaba Frailes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>🍐</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H4" s="14"/>
+      <x:c r="I4" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
+        <x:v>Guayaba en Frailes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>ARB_GUANABANA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Guanábana</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Guanábana</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>🍈</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>Fructificación</x:v>
+      </x:c>
+      <x:c r="H5" s="14"/>
+      <x:c r="I5" s="11" t="str">
+        <x:v>Atención</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str">
+        <x:v>Puntos negros en frutos</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>Mango</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Mango</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>🥭</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H6" s="14"/>
+      <x:c r="I6" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
+        <x:v>Mango peludo adulto</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="11" t="str">
+        <x:v>ARB_ANONA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B7" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C7" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>Anona</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>Anona</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>🍈</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>Estrés / recuperación</x:v>
+      </x:c>
+      <x:c r="H7" s="14"/>
+      <x:c r="I7" s="11" t="str">
+        <x:v>Atención</x:v>
+      </x:c>
+      <x:c r="J7" s="11" t="str">
+        <x:v>Historial de defoliación</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="11" t="str">
+        <x:v>ARB_NISPERO_FRAILES</x:v>
+      </x:c>
+      <x:c r="B8" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>Níspero</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>Níspero</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H8" s="14" t="n">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>Árbol joven</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>ARB_MANDARINA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>Mandarina</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>Mandarina</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>🍊</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H9" s="14" t="n">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str">
+        <x:v>Trasplante reciente en Frailes</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>ARB_LIMON_DULCE_FRAILES</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>Limón dulce</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>Limón</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>🍋</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H10" s="14" t="n">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str">
+        <x:v>Cítrico joven</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>ARB_NARANJA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>Naranja</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>Naranja</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>🍊</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H11" s="14" t="n">
+        <x:v>45853</x:v>
+      </x:c>
+      <x:c r="I11" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str">
+        <x:v>Cítrico joven</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>ARB_CARAMBOLA_FRAILES</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>Carambola</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>Carambola</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>⭐</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="H12" s="14"/>
+      <x:c r="I12" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="J12" s="11" t="str"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="H13" s="18"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="H14" s="18"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="H15" s="18"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="H16" s="18"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="H17" s="18"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="H18" s="18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="H19" s="18"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="H20" s="18"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="H21" s="18"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="H22" s="18"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="H23" s="18"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="H24" s="18"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="H25" s="18"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="H26" s="18"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="H27" s="18"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="H28" s="18"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="H29" s="18"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="H30" s="18"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="H31" s="18"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="H32" s="18"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="H33" s="18"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="H34" s="18"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="H35" s="18"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="H36" s="18"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="H37" s="18"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="H38" s="18"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="H39" s="18"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="H40" s="18"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="H41" s="18"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="H42" s="18"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="H43" s="18"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="H44" s="18"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="H45" s="18"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="H46" s="18"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="H47" s="18"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="H48" s="18"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="H49" s="18"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="H50" s="18"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="8.210000038146973" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16.290000915527344" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13.729999542236328" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="9.5600004196167" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="21.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="18.84000015258789" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="11.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="6.460000038146973" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="11.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="10.09000015258789" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="5.650000095367432" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="21.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="11.569999694824219" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="15.609999656677246" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="13.460000038146973" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="11.039999961853027" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="31.6299991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="10.09000015258789" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="10.359999656677246" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="21.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.319999694824219" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="12.109999656677246" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.729999542236328" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="15.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="13.460000038146973" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="15.34000015258789" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="14.130000114440918" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="19.649999618530273" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="13.1899995803833" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="21.270000457763672" hidden="0" customWidth="1"/>
+    <x:col min="20" max="20" width="23.420000076293945" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -473,54 +979,57 @@
         <x:v>Tipo_Evento</x:v>
       </x:c>
       <x:c r="C1" s="24" t="str">
-        <x:v>ID_Insumo</x:v>
+        <x:v>Objeto_Tipo</x:v>
       </x:c>
       <x:c r="D1" s="24" t="str">
-        <x:v>Nombre_Insumo</x:v>
+        <x:v>Finca_ID</x:v>
       </x:c>
       <x:c r="E1" s="24" t="str">
-        <x:v>Target_Tipo</x:v>
+        <x:v>Cama_ID</x:v>
       </x:c>
       <x:c r="F1" s="24" t="str">
-        <x:v>Target_ID</x:v>
+        <x:v>Siembra_ID</x:v>
       </x:c>
       <x:c r="G1" s="24" t="str">
-        <x:v>Target_Label</x:v>
+        <x:v>Arbol_ID</x:v>
       </x:c>
       <x:c r="H1" s="24" t="str">
-        <x:v>Finca_ID</x:v>
+        <x:v>Cultivo_Nombre</x:v>
       </x:c>
       <x:c r="I1" s="24" t="str">
-        <x:v>Finca</x:v>
+        <x:v>Arbol_Nombre</x:v>
       </x:c>
       <x:c r="J1" s="24" t="str">
-        <x:v>Unidad_ID</x:v>
+        <x:v>Insumo_ID</x:v>
       </x:c>
       <x:c r="K1" s="24" t="str">
-        <x:v>Unidad</x:v>
+        <x:v>Insumo_Nombre</x:v>
       </x:c>
       <x:c r="L1" s="24" t="str">
-        <x:v>Cultivo_ID</x:v>
+        <x:v>Fecha_Programada</x:v>
       </x:c>
       <x:c r="M1" s="24" t="str">
-        <x:v>Cultivo</x:v>
+        <x:v>Fecha_Realizada</x:v>
       </x:c>
       <x:c r="N1" s="24" t="str">
-        <x:v>Arbol_ID</x:v>
+        <x:v>Estado</x:v>
       </x:c>
       <x:c r="O1" s="24" t="str">
-        <x:v>Arbol</x:v>
+        <x:v>Cantidad_Aplicada</x:v>
       </x:c>
       <x:c r="P1" s="24" t="str">
-        <x:v>Fecha_Programada</x:v>
+        <x:v>Unidad_Cantidad</x:v>
       </x:c>
       <x:c r="Q1" s="24" t="str">
-        <x:v>Fecha_Realizada</x:v>
+        <x:v>Momento_Aplicacion</x:v>
       </x:c>
       <x:c r="R1" s="24" t="str">
-        <x:v>Estado</x:v>
+        <x:v>Frecuencia_Dias</x:v>
       </x:c>
       <x:c r="S1" s="24" t="str">
+        <x:v>Proxima_Fecha_Calculada</x:v>
+      </x:c>
+      <x:c r="T1" s="24" t="str">
         <x:v>Notas</x:v>
       </x:c>
     </x:row>
@@ -532,49 +1041,52 @@
         <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>INS_COBRE</x:v>
+        <x:v>Cultivo</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Cobre</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Cultivo</x:v>
+        <x:v>UNI_FRA_CAMA_01</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>SIE_FRA_003</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str">
-        <x:v>Cama Frailes 1 - Pepino</x:v>
-      </x:c>
+      <x:c r="G2" s="11" t="str"/>
       <x:c r="H2" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="I2" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
+        <x:v>Pepino</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str"/>
       <x:c r="J2" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_01</x:v>
+        <x:v>INS_COBRE</x:v>
       </x:c>
       <x:c r="K2" s="11" t="str">
-        <x:v>Cama Frailes 1</x:v>
-      </x:c>
-      <x:c r="L2" s="11" t="str">
-        <x:v>CUL_PEPINO</x:v>
-      </x:c>
-      <x:c r="M2" s="11" t="str">
-        <x:v>Pepino</x:v>
-      </x:c>
-      <x:c r="N2" s="11" t="str"/>
-      <x:c r="O2" s="11" t="str"/>
-      <x:c r="P2" s="14"/>
-      <x:c r="Q2" s="14" t="n">
+        <x:v>Cobre</x:v>
+      </x:c>
+      <x:c r="L2" s="14"/>
+      <x:c r="M2" s="14" t="n">
         <x:v>46152</x:v>
       </x:c>
-      <x:c r="R2" s="11" t="str">
-        <x:v>Pendiente</x:v>
-      </x:c>
-      <x:c r="S2" s="11" t="str">
-        <x:v>Ejemplo: control fitosanitario con cobre</x:v>
+      <x:c r="N2" s="11" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="O2" s="11" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="P2" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="Q2" s="11" t="str">
+        <x:v>Alta humedad</x:v>
+      </x:c>
+      <x:c r="R2" s="11" t="n">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="S2" s="14" t="n">
+        <x:v>46166</x:v>
+      </x:c>
+      <x:c r="T2" s="11" t="str">
+        <x:v>Control realizado en pepino</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -585,49 +1097,50 @@
         <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>INS_MISTRAL</x:v>
+        <x:v>Cultivo</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Mistral</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Cultivo</x:v>
+        <x:v>UNI_FRA_CAMA_01</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>SIE_FRA_003</x:v>
       </x:c>
-      <x:c r="G3" s="11" t="str">
-        <x:v>Cama Frailes 1 - Pepino</x:v>
-      </x:c>
+      <x:c r="G3" s="11" t="str"/>
       <x:c r="H3" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="I3" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
+        <x:v>Pepino</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str"/>
       <x:c r="J3" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_01</x:v>
+        <x:v>INS_MISTRAL</x:v>
       </x:c>
       <x:c r="K3" s="11" t="str">
-        <x:v>Cama Frailes 1</x:v>
-      </x:c>
-      <x:c r="L3" s="11" t="str">
-        <x:v>CUL_PEPINO</x:v>
-      </x:c>
-      <x:c r="M3" s="11" t="str">
-        <x:v>Pepino</x:v>
-      </x:c>
-      <x:c r="N3" s="11" t="str"/>
-      <x:c r="O3" s="11" t="str"/>
-      <x:c r="P3" s="14" t="n">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="L3" s="14" t="n">
         <x:v>46188</x:v>
       </x:c>
-      <x:c r="Q3" s="14"/>
-      <x:c r="R3" s="11" t="str">
+      <x:c r="M3" s="14"/>
+      <x:c r="N3" s="11" t="str">
         <x:v>No empezado</x:v>
       </x:c>
-      <x:c r="S3" s="11" t="str">
-        <x:v>Próximo control fitosanitario</x:v>
+      <x:c r="O3" s="11" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="P3" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="Q3" s="11" t="str">
+        <x:v>Preventivo</x:v>
+      </x:c>
+      <x:c r="R3" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S3" s="14"/>
+      <x:c r="T3" s="11" t="str">
+        <x:v>Programado para pepino</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -638,45 +1151,50 @@
         <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str"/>
+      <x:c r="F4" s="11" t="str"/>
+      <x:c r="G4" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str"/>
+      <x:c r="I4" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str">
         <x:v>INS_CAL_DOLOMITA</x:v>
       </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>Cal Dolomita</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="str">
-        <x:v>Arbol</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="str">
-        <x:v>ARB_GUAYABA_FRAILES</x:v>
-      </x:c>
-      <x:c r="G4" s="11" t="str">
-        <x:v>Guayaba - Frailes</x:v>
-      </x:c>
-      <x:c r="H4" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="I4" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str"/>
-      <x:c r="K4" s="11" t="str"/>
-      <x:c r="L4" s="11" t="str"/>
-      <x:c r="M4" s="11" t="str"/>
+      <x:c r="K4" s="11" t="str">
+        <x:v>Cal dolomita</x:v>
+      </x:c>
+      <x:c r="L4" s="14"/>
+      <x:c r="M4" s="14" t="n">
+        <x:v>46172</x:v>
+      </x:c>
       <x:c r="N4" s="11" t="str">
-        <x:v>ARB_GUAYABA_FRAILES</x:v>
+        <x:v>Completado</x:v>
       </x:c>
       <x:c r="O4" s="11" t="str">
-        <x:v>Guayaba</x:v>
-      </x:c>
-      <x:c r="P4" s="14"/>
-      <x:c r="Q4" s="14" t="n">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="R4" s="11" t="str">
-        <x:v>Completado</x:v>
-      </x:c>
-      <x:c r="S4" s="11" t="str">
-        <x:v>Aplicación de cal dolomita</x:v>
+        <x:v>Según tamaño</x:v>
+      </x:c>
+      <x:c r="P4" s="11" t="str">
+        <x:v>kg/árbol</x:v>
+      </x:c>
+      <x:c r="Q4" s="11" t="str">
+        <x:v>Vegetativo / enmienda</x:v>
+      </x:c>
+      <x:c r="R4" s="11" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="S4" s="14" t="n">
+        <x:v>46352</x:v>
+      </x:c>
+      <x:c r="T4" s="11" t="str">
+        <x:v>Aplicación de corona</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -687,45 +1205,50 @@
         <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str"/>
+      <x:c r="F5" s="11" t="str"/>
+      <x:c r="G5" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str"/>
+      <x:c r="I5" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str">
         <x:v>INS_YARAMILA</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
+      <x:c r="K5" s="11" t="str">
         <x:v>YaraMila</x:v>
       </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>Arbol</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
-        <x:v>ARB_GUAYABA_FRAILES</x:v>
-      </x:c>
-      <x:c r="G5" s="11" t="str">
-        <x:v>Guayaba - Frailes</x:v>
-      </x:c>
-      <x:c r="H5" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="I5" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="J5" s="11" t="str"/>
-      <x:c r="K5" s="11" t="str"/>
-      <x:c r="L5" s="11" t="str"/>
-      <x:c r="M5" s="11" t="str"/>
+      <x:c r="L5" s="14"/>
+      <x:c r="M5" s="14" t="n">
+        <x:v>46179</x:v>
+      </x:c>
       <x:c r="N5" s="11" t="str">
-        <x:v>ARB_GUAYABA_FRAILES</x:v>
+        <x:v>Completado</x:v>
       </x:c>
       <x:c r="O5" s="11" t="str">
-        <x:v>Guayaba</x:v>
-      </x:c>
-      <x:c r="P5" s="14"/>
-      <x:c r="Q5" s="14" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="R5" s="11" t="str">
-        <x:v>Completado</x:v>
-      </x:c>
-      <x:c r="S5" s="11" t="str">
-        <x:v>Aplicación de YaraMila</x:v>
+        <x:v>Bajo según tamaño</x:v>
+      </x:c>
+      <x:c r="P5" s="11" t="str">
+        <x:v>g/árbol</x:v>
+      </x:c>
+      <x:c r="Q5" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="R5" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="S5" s="14" t="n">
+        <x:v>46239</x:v>
+      </x:c>
+      <x:c r="T5" s="11" t="str">
+        <x:v>Fertilización de tierra</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -736,45 +1259,48 @@
         <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str"/>
+      <x:c r="F6" s="11" t="str"/>
+      <x:c r="G6" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str"/>
+      <x:c r="I6" s="11" t="str">
+        <x:v>Mango</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str">
         <x:v>INS_MISTRAL</x:v>
       </x:c>
-      <x:c r="D6" s="11" t="str">
+      <x:c r="K6" s="11" t="str">
         <x:v>Mistral</x:v>
       </x:c>
-      <x:c r="E6" s="11" t="str">
-        <x:v>Arbol</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="str">
-        <x:v>ARB_MANGO_FRAILES</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="str">
-        <x:v>Mango peludo - Frailes</x:v>
-      </x:c>
-      <x:c r="H6" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="I6" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="str"/>
-      <x:c r="K6" s="11" t="str"/>
-      <x:c r="L6" s="11" t="str"/>
-      <x:c r="M6" s="11" t="str"/>
+      <x:c r="L6" s="14" t="n">
+        <x:v>46264</x:v>
+      </x:c>
+      <x:c r="M6" s="14"/>
       <x:c r="N6" s="11" t="str">
-        <x:v>ARB_MANGO_FRAILES</x:v>
+        <x:v>No empezado</x:v>
       </x:c>
       <x:c r="O6" s="11" t="str">
-        <x:v>Mango peludo</x:v>
-      </x:c>
-      <x:c r="P6" s="14" t="n">
-        <x:v>46264</x:v>
-      </x:c>
-      <x:c r="Q6" s="14"/>
-      <x:c r="R6" s="11" t="str">
-        <x:v>No empezado</x:v>
-      </x:c>
-      <x:c r="S6" s="11" t="str">
-        <x:v>Control fitosanitario programado</x:v>
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="P6" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="Q6" s="11" t="str">
+        <x:v>Preventivo</x:v>
+      </x:c>
+      <x:c r="R6" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S6" s="14"/>
+      <x:c r="T6" s="11" t="str">
+        <x:v>Control programado</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -784,41 +1310,40 @@
       <x:c r="B7" s="11" t="str">
         <x:v>Poda</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="str"/>
-      <x:c r="D7" s="11" t="str"/>
-      <x:c r="E7" s="11" t="str">
-        <x:v>Arbol</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="str">
+      <x:c r="C7" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str"/>
+      <x:c r="F7" s="11" t="str"/>
+      <x:c r="G7" s="11" t="str">
         <x:v>ARB_MANGO_FRAILES</x:v>
       </x:c>
-      <x:c r="G7" s="11" t="str">
-        <x:v>Mango peludo - Frailes</x:v>
-      </x:c>
-      <x:c r="H7" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
+      <x:c r="H7" s="11" t="str"/>
       <x:c r="I7" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Mango</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
-      <x:c r="L7" s="11" t="str"/>
-      <x:c r="M7" s="11" t="str"/>
+      <x:c r="L7" s="14" t="n">
+        <x:v>46295</x:v>
+      </x:c>
+      <x:c r="M7" s="14"/>
       <x:c r="N7" s="11" t="str">
-        <x:v>ARB_MANGO_FRAILES</x:v>
-      </x:c>
-      <x:c r="O7" s="11" t="str">
-        <x:v>Mango peludo</x:v>
-      </x:c>
-      <x:c r="P7" s="14" t="n">
-        <x:v>46295</x:v>
-      </x:c>
-      <x:c r="Q7" s="14"/>
-      <x:c r="R7" s="11" t="str">
         <x:v>No empezado</x:v>
       </x:c>
-      <x:c r="S7" s="11" t="str">
+      <x:c r="O7" s="11" t="str"/>
+      <x:c r="P7" s="11" t="str"/>
+      <x:c r="Q7" s="11" t="str">
+        <x:v>Postcosecha / formación</x:v>
+      </x:c>
+      <x:c r="R7" s="11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" s="14"/>
+      <x:c r="T7" s="11" t="str">
         <x:v>Poda programada</x:v>
       </x:c>
     </x:row>
@@ -827,417 +1352,1181 @@
         <x:v>EVT_007</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C8" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str"/>
+      <x:c r="F8" s="11" t="str"/>
+      <x:c r="G8" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str"/>
+      <x:c r="I8" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str">
+        <x:v>INS_MISTRAL</x:v>
+      </x:c>
+      <x:c r="K8" s="11" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="L8" s="14"/>
+      <x:c r="M8" s="14" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="N8" s="11" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="O8" s="11" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="P8" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="Q8" s="11" t="str">
+        <x:v>Llenado / prevención</x:v>
+      </x:c>
+      <x:c r="R8" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="S8" s="14" t="n">
+        <x:v>46196</x:v>
+      </x:c>
+      <x:c r="T8" s="11" t="str">
+        <x:v>Control aplicado hoy</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>EVT_008</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C9" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str"/>
+      <x:c r="F9" s="11" t="str"/>
+      <x:c r="G9" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str"/>
+      <x:c r="I9" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="J9" s="11" t="str">
+        <x:v>INS_YARAMILA</x:v>
+      </x:c>
+      <x:c r="K9" s="11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="L9" s="14"/>
+      <x:c r="M9" s="14" t="n">
+        <x:v>46127</x:v>
+      </x:c>
+      <x:c r="N9" s="11" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="O9" s="11" t="str">
+        <x:v>Bajo según tamaño</x:v>
+      </x:c>
+      <x:c r="P9" s="11" t="str">
+        <x:v>g/árbol</x:v>
+      </x:c>
+      <x:c r="Q9" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="R9" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="S9" s="14" t="n">
+        <x:v>46187</x:v>
+      </x:c>
+      <x:c r="T9" s="11" t="str">
+        <x:v>Fertilización previa</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>EVT_009</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str"/>
+      <x:c r="F10" s="11" t="str"/>
+      <x:c r="G10" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str"/>
+      <x:c r="I10" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="J10" s="11" t="str">
+        <x:v>INS_YARAMILA</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="L10" s="14"/>
+      <x:c r="M10" s="14" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="N10" s="11" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="O10" s="11" t="str">
+        <x:v>Bajo según tamaño</x:v>
+      </x:c>
+      <x:c r="P10" s="11" t="str">
+        <x:v>g/árbol</x:v>
+      </x:c>
+      <x:c r="Q10" s="11" t="str">
+        <x:v>Llenado</x:v>
+      </x:c>
+      <x:c r="R10" s="11" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="S10" s="14" t="n">
+        <x:v>46234</x:v>
+      </x:c>
+      <x:c r="T10" s="11" t="str">
+        <x:v>Refuerzo de tierra</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>EVT_010</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str"/>
+      <x:c r="F11" s="11" t="str"/>
+      <x:c r="G11" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
+      <x:c r="H11" s="11" t="str"/>
+      <x:c r="I11" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="J11" s="11" t="str">
+        <x:v>INS_NEEM</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="str">
+        <x:v>Neem</x:v>
+      </x:c>
+      <x:c r="L11" s="14" t="n">
+        <x:v>46193</x:v>
+      </x:c>
+      <x:c r="M11" s="14"/>
+      <x:c r="N11" s="11" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="O11" s="11" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="P11" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="Q11" s="11" t="str">
+        <x:v>Preventivo</x:v>
+      </x:c>
+      <x:c r="R11" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="S11" s="14"/>
+      <x:c r="T11" s="11" t="str">
+        <x:v>Pendiente en guayaba</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>EVT_011</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>Cultivo</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>UNI_FRA_CAMA_05</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>SIE_FRA_014</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str"/>
+      <x:c r="H12" s="11" t="str">
+        <x:v>Arúgula</x:v>
+      </x:c>
+      <x:c r="I12" s="11" t="str"/>
+      <x:c r="J12" s="11" t="str">
+        <x:v>INS_JABON_POTASICO</x:v>
+      </x:c>
+      <x:c r="K12" s="11" t="str">
+        <x:v>Jabón potásico</x:v>
+      </x:c>
+      <x:c r="L12" s="14" t="n">
+        <x:v>46185</x:v>
+      </x:c>
+      <x:c r="M12" s="14"/>
+      <x:c r="N12" s="11" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="O12" s="11" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="P12" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="Q12" s="11" t="str">
+        <x:v>Presencia plaga blanda</x:v>
+      </x:c>
+      <x:c r="R12" s="11" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="S12" s="14"/>
+      <x:c r="T12" s="11" t="str">
+        <x:v>Control pendiente en arúgula</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
+        <x:v>EVT_012</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
         <x:v>Abono foliar</x:v>
       </x:c>
-      <x:c r="C8" s="11" t="str">
+      <x:c r="C13" s="11" t="str">
+        <x:v>Cultivo</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>UNI_FRA_CAMA_02</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>SIE_FRA_007</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str"/>
+      <x:c r="H13" s="11" t="str">
+        <x:v>Tomate cherry</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str"/>
+      <x:c r="J13" s="11" t="str">
         <x:v>INS_CALCIO_BORO</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="str">
+      <x:c r="K13" s="11" t="str">
         <x:v>Calcio Boro</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>Arbol</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="str">
-        <x:v>ARB_MANZANO_MORAVIA</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="str">
-        <x:v>Manzano tico - Moravia</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="str">
-        <x:v>Moravia</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str"/>
-      <x:c r="K8" s="11" t="str"/>
-      <x:c r="L8" s="11" t="str"/>
-      <x:c r="M8" s="11" t="str"/>
-      <x:c r="N8" s="11" t="str">
-        <x:v>ARB_MANZANO_MORAVIA</x:v>
-      </x:c>
-      <x:c r="O8" s="11" t="str">
+      <x:c r="L13" s="14" t="n">
+        <x:v>46191</x:v>
+      </x:c>
+      <x:c r="M13" s="14"/>
+      <x:c r="N13" s="11" t="str">
+        <x:v>No empezado</x:v>
+      </x:c>
+      <x:c r="O13" s="11" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="P13" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="Q13" s="11" t="str">
+        <x:v>Floración</x:v>
+      </x:c>
+      <x:c r="R13" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="S13" s="14"/>
+      <x:c r="T13" s="11" t="str">
+        <x:v>Apoyo floración/cuaje</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="L14" s="18"/>
+      <x:c r="M14" s="18"/>
+      <x:c r="S14" s="18"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="L15" s="18"/>
+      <x:c r="M15" s="18"/>
+      <x:c r="S15" s="18"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="L16" s="18"/>
+      <x:c r="M16" s="18"/>
+      <x:c r="S16" s="18"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="L17" s="18"/>
+      <x:c r="M17" s="18"/>
+      <x:c r="S17" s="18"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="L18" s="18"/>
+      <x:c r="M18" s="18"/>
+      <x:c r="S18" s="18"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="L19" s="18"/>
+      <x:c r="M19" s="18"/>
+      <x:c r="S19" s="18"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="L20" s="18"/>
+      <x:c r="M20" s="18"/>
+      <x:c r="S20" s="18"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="L21" s="18"/>
+      <x:c r="M21" s="18"/>
+      <x:c r="S21" s="18"/>
+    </x:row>
+    <x:row r="22">
+      <x:c r="L22" s="18"/>
+      <x:c r="M22" s="18"/>
+      <x:c r="S22" s="18"/>
+    </x:row>
+    <x:row r="23">
+      <x:c r="L23" s="18"/>
+      <x:c r="M23" s="18"/>
+      <x:c r="S23" s="18"/>
+    </x:row>
+    <x:row r="24">
+      <x:c r="L24" s="18"/>
+      <x:c r="M24" s="18"/>
+      <x:c r="S24" s="18"/>
+    </x:row>
+    <x:row r="25">
+      <x:c r="L25" s="18"/>
+      <x:c r="M25" s="18"/>
+      <x:c r="S25" s="18"/>
+    </x:row>
+    <x:row r="26">
+      <x:c r="L26" s="18"/>
+      <x:c r="M26" s="18"/>
+      <x:c r="S26" s="18"/>
+    </x:row>
+    <x:row r="27">
+      <x:c r="L27" s="18"/>
+      <x:c r="M27" s="18"/>
+      <x:c r="S27" s="18"/>
+    </x:row>
+    <x:row r="28">
+      <x:c r="L28" s="18"/>
+      <x:c r="M28" s="18"/>
+      <x:c r="S28" s="18"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="L29" s="18"/>
+      <x:c r="M29" s="18"/>
+      <x:c r="S29" s="18"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="L30" s="18"/>
+      <x:c r="M30" s="18"/>
+      <x:c r="S30" s="18"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="L31" s="18"/>
+      <x:c r="M31" s="18"/>
+      <x:c r="S31" s="18"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="L32" s="18"/>
+      <x:c r="M32" s="18"/>
+      <x:c r="S32" s="18"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="L33" s="18"/>
+      <x:c r="M33" s="18"/>
+      <x:c r="S33" s="18"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="L34" s="18"/>
+      <x:c r="M34" s="18"/>
+      <x:c r="S34" s="18"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="L35" s="18"/>
+      <x:c r="M35" s="18"/>
+      <x:c r="S35" s="18"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="L36" s="18"/>
+      <x:c r="M36" s="18"/>
+      <x:c r="S36" s="18"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="L37" s="18"/>
+      <x:c r="M37" s="18"/>
+      <x:c r="S37" s="18"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="L38" s="18"/>
+      <x:c r="M38" s="18"/>
+      <x:c r="S38" s="18"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="L39" s="18"/>
+      <x:c r="M39" s="18"/>
+      <x:c r="S39" s="18"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="L40" s="18"/>
+      <x:c r="M40" s="18"/>
+      <x:c r="S40" s="18"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="L41" s="18"/>
+      <x:c r="M41" s="18"/>
+      <x:c r="S41" s="18"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="L42" s="18"/>
+      <x:c r="M42" s="18"/>
+      <x:c r="S42" s="18"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="L43" s="18"/>
+      <x:c r="M43" s="18"/>
+      <x:c r="S43" s="18"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="L44" s="18"/>
+      <x:c r="M44" s="18"/>
+      <x:c r="S44" s="18"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="L45" s="18"/>
+      <x:c r="M45" s="18"/>
+      <x:c r="S45" s="18"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="L46" s="18"/>
+      <x:c r="M46" s="18"/>
+      <x:c r="S46" s="18"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="L47" s="18"/>
+      <x:c r="M47" s="18"/>
+      <x:c r="S47" s="18"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="L48" s="18"/>
+      <x:c r="M48" s="18"/>
+      <x:c r="S48" s="18"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="L49" s="18"/>
+      <x:c r="M49" s="18"/>
+      <x:c r="S49" s="18"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="L50" s="18"/>
+      <x:c r="M50" s="18"/>
+      <x:c r="S50" s="18"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="L51" s="18"/>
+      <x:c r="M51" s="18"/>
+      <x:c r="S51" s="18"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="L52" s="18"/>
+      <x:c r="M52" s="18"/>
+      <x:c r="S52" s="18"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="L53" s="18"/>
+      <x:c r="M53" s="18"/>
+      <x:c r="S53" s="18"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="L54" s="18"/>
+      <x:c r="M54" s="18"/>
+      <x:c r="S54" s="18"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="L55" s="18"/>
+      <x:c r="M55" s="18"/>
+      <x:c r="S55" s="18"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="L56" s="18"/>
+      <x:c r="M56" s="18"/>
+      <x:c r="S56" s="18"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="L57" s="18"/>
+      <x:c r="M57" s="18"/>
+      <x:c r="S57" s="18"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="L58" s="18"/>
+      <x:c r="M58" s="18"/>
+      <x:c r="S58" s="18"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="L59" s="18"/>
+      <x:c r="M59" s="18"/>
+      <x:c r="S59" s="18"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="L60" s="18"/>
+      <x:c r="M60" s="18"/>
+      <x:c r="S60" s="18"/>
+    </x:row>
+    <x:row r="61">
+      <x:c r="L61" s="18"/>
+      <x:c r="M61" s="18"/>
+      <x:c r="S61" s="18"/>
+    </x:row>
+    <x:row r="62">
+      <x:c r="L62" s="18"/>
+      <x:c r="M62" s="18"/>
+      <x:c r="S62" s="18"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="L63" s="18"/>
+      <x:c r="M63" s="18"/>
+      <x:c r="S63" s="18"/>
+    </x:row>
+    <x:row r="64">
+      <x:c r="L64" s="18"/>
+      <x:c r="M64" s="18"/>
+      <x:c r="S64" s="18"/>
+    </x:row>
+    <x:row r="65">
+      <x:c r="L65" s="18"/>
+      <x:c r="M65" s="18"/>
+      <x:c r="S65" s="18"/>
+    </x:row>
+    <x:row r="66">
+      <x:c r="L66" s="18"/>
+      <x:c r="M66" s="18"/>
+      <x:c r="S66" s="18"/>
+    </x:row>
+    <x:row r="67">
+      <x:c r="L67" s="18"/>
+      <x:c r="M67" s="18"/>
+      <x:c r="S67" s="18"/>
+    </x:row>
+    <x:row r="68">
+      <x:c r="L68" s="18"/>
+      <x:c r="M68" s="18"/>
+      <x:c r="S68" s="18"/>
+    </x:row>
+    <x:row r="69">
+      <x:c r="L69" s="18"/>
+      <x:c r="M69" s="18"/>
+      <x:c r="S69" s="18"/>
+    </x:row>
+    <x:row r="70">
+      <x:c r="L70" s="18"/>
+      <x:c r="M70" s="18"/>
+      <x:c r="S70" s="18"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="L71" s="18"/>
+      <x:c r="M71" s="18"/>
+      <x:c r="S71" s="18"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="L72" s="18"/>
+      <x:c r="M72" s="18"/>
+      <x:c r="S72" s="18"/>
+    </x:row>
+    <x:row r="73">
+      <x:c r="L73" s="18"/>
+      <x:c r="M73" s="18"/>
+      <x:c r="S73" s="18"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="L74" s="18"/>
+      <x:c r="M74" s="18"/>
+      <x:c r="S74" s="18"/>
+    </x:row>
+    <x:row r="75">
+      <x:c r="L75" s="18"/>
+      <x:c r="M75" s="18"/>
+      <x:c r="S75" s="18"/>
+    </x:row>
+    <x:row r="76">
+      <x:c r="L76" s="18"/>
+      <x:c r="M76" s="18"/>
+      <x:c r="S76" s="18"/>
+    </x:row>
+    <x:row r="77">
+      <x:c r="L77" s="18"/>
+      <x:c r="M77" s="18"/>
+      <x:c r="S77" s="18"/>
+    </x:row>
+    <x:row r="78">
+      <x:c r="L78" s="18"/>
+      <x:c r="M78" s="18"/>
+      <x:c r="S78" s="18"/>
+    </x:row>
+    <x:row r="79">
+      <x:c r="L79" s="18"/>
+      <x:c r="M79" s="18"/>
+      <x:c r="S79" s="18"/>
+    </x:row>
+    <x:row r="80">
+      <x:c r="L80" s="18"/>
+      <x:c r="M80" s="18"/>
+      <x:c r="S80" s="18"/>
+    </x:row>
+    <x:row r="81">
+      <x:c r="L81" s="18"/>
+      <x:c r="M81" s="18"/>
+      <x:c r="S81" s="18"/>
+    </x:row>
+    <x:row r="82">
+      <x:c r="L82" s="18"/>
+      <x:c r="M82" s="18"/>
+      <x:c r="S82" s="18"/>
+    </x:row>
+    <x:row r="83">
+      <x:c r="L83" s="18"/>
+      <x:c r="M83" s="18"/>
+      <x:c r="S83" s="18"/>
+    </x:row>
+    <x:row r="84">
+      <x:c r="L84" s="18"/>
+      <x:c r="M84" s="18"/>
+      <x:c r="S84" s="18"/>
+    </x:row>
+    <x:row r="85">
+      <x:c r="L85" s="18"/>
+      <x:c r="M85" s="18"/>
+      <x:c r="S85" s="18"/>
+    </x:row>
+    <x:row r="86">
+      <x:c r="L86" s="18"/>
+      <x:c r="M86" s="18"/>
+      <x:c r="S86" s="18"/>
+    </x:row>
+    <x:row r="87">
+      <x:c r="L87" s="18"/>
+      <x:c r="M87" s="18"/>
+      <x:c r="S87" s="18"/>
+    </x:row>
+    <x:row r="88">
+      <x:c r="L88" s="18"/>
+      <x:c r="M88" s="18"/>
+      <x:c r="S88" s="18"/>
+    </x:row>
+    <x:row r="89">
+      <x:c r="L89" s="18"/>
+      <x:c r="M89" s="18"/>
+      <x:c r="S89" s="18"/>
+    </x:row>
+    <x:row r="90">
+      <x:c r="L90" s="18"/>
+      <x:c r="M90" s="18"/>
+      <x:c r="S90" s="18"/>
+    </x:row>
+    <x:row r="91">
+      <x:c r="L91" s="18"/>
+      <x:c r="M91" s="18"/>
+      <x:c r="S91" s="18"/>
+    </x:row>
+    <x:row r="92">
+      <x:c r="L92" s="18"/>
+      <x:c r="M92" s="18"/>
+      <x:c r="S92" s="18"/>
+    </x:row>
+    <x:row r="93">
+      <x:c r="L93" s="18"/>
+      <x:c r="M93" s="18"/>
+      <x:c r="S93" s="18"/>
+    </x:row>
+    <x:row r="94">
+      <x:c r="L94" s="18"/>
+      <x:c r="M94" s="18"/>
+      <x:c r="S94" s="18"/>
+    </x:row>
+    <x:row r="95">
+      <x:c r="L95" s="18"/>
+      <x:c r="M95" s="18"/>
+      <x:c r="S95" s="18"/>
+    </x:row>
+    <x:row r="96">
+      <x:c r="L96" s="18"/>
+      <x:c r="M96" s="18"/>
+      <x:c r="S96" s="18"/>
+    </x:row>
+    <x:row r="97">
+      <x:c r="L97" s="18"/>
+      <x:c r="M97" s="18"/>
+      <x:c r="S97" s="18"/>
+    </x:row>
+    <x:row r="98">
+      <x:c r="L98" s="18"/>
+      <x:c r="M98" s="18"/>
+      <x:c r="S98" s="18"/>
+    </x:row>
+    <x:row r="99">
+      <x:c r="L99" s="18"/>
+      <x:c r="M99" s="18"/>
+      <x:c r="S99" s="18"/>
+    </x:row>
+    <x:row r="100">
+      <x:c r="L100" s="18"/>
+      <x:c r="M100" s="18"/>
+      <x:c r="S100" s="18"/>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="N2:N100">
+      <x:formula1>"No empezado,Pendiente,Completado,Cancelado"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="10.770000457763672" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.960000038146973" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19.520000457763672" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="11.170000076293945" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="35.66999816894531" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="24" t="str">
+        <x:v>Objeto</x:v>
+      </x:c>
+      <x:c r="B1" s="24" t="str">
+        <x:v>Tipo</x:v>
+      </x:c>
+      <x:c r="C1" s="24" t="str">
+        <x:v>Insumo</x:v>
+      </x:c>
+      <x:c r="D1" s="24" t="str">
+        <x:v>Cantidad_Eventos_2026</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>Ultima_Fecha</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>Notas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="11" t="str">
         <x:v>Manzano tico</x:v>
       </x:c>
-      <x:c r="P8" s="14" t="n">
-        <x:v>46193</x:v>
-      </x:c>
-      <x:c r="Q8" s="14"/>
-      <x:c r="R8" s="11" t="str">
-        <x:v>No empezado</x:v>
-      </x:c>
-      <x:c r="S8" s="11" t="str">
-        <x:v>Apoyo foliar en llenado</x:v>
-      </x:c>
+      <x:c r="B2" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C2" s="11" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E2" s="14" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>Ejemplo: se acumula desde EventosAgricolas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="B3" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E3" s="14" t="n">
+        <x:v>46174</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>Permite ver frecuencia anual</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="B4" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C4" s="11" t="str">
+        <x:v>Cal dolomita</x:v>
+      </x:c>
+      <x:c r="D4" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E4" s="14" t="n">
+        <x:v>46172</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>Aplicación de enmienda</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="11" t="str">
+        <x:v>Guayaba</x:v>
+      </x:c>
+      <x:c r="B5" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C5" s="11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E5" s="14" t="n">
+        <x:v>46179</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Fertilización</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="11" t="str">
+        <x:v>Pepino</x:v>
+      </x:c>
+      <x:c r="B6" s="11" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C6" s="11" t="str">
+        <x:v>Cobre</x:v>
+      </x:c>
+      <x:c r="D6" s="11" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="n">
+        <x:v>46152</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>Historial por cultivo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="E7" s="18"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="E8" s="18"/>
     </x:row>
     <x:row r="9">
-      <x:c r="P9" s="18"/>
-      <x:c r="Q9" s="18"/>
+      <x:c r="E9" s="18"/>
     </x:row>
     <x:row r="10">
-      <x:c r="P10" s="18"/>
-      <x:c r="Q10" s="18"/>
+      <x:c r="E10" s="18"/>
     </x:row>
     <x:row r="11">
-      <x:c r="P11" s="18"/>
-      <x:c r="Q11" s="18"/>
+      <x:c r="E11" s="18"/>
     </x:row>
     <x:row r="12">
-      <x:c r="P12" s="18"/>
-      <x:c r="Q12" s="18"/>
+      <x:c r="E12" s="18"/>
     </x:row>
     <x:row r="13">
-      <x:c r="P13" s="18"/>
-      <x:c r="Q13" s="18"/>
+      <x:c r="E13" s="18"/>
     </x:row>
     <x:row r="14">
-      <x:c r="P14" s="18"/>
-      <x:c r="Q14" s="18"/>
+      <x:c r="E14" s="18"/>
     </x:row>
     <x:row r="15">
-      <x:c r="P15" s="18"/>
-      <x:c r="Q15" s="18"/>
+      <x:c r="E15" s="18"/>
     </x:row>
     <x:row r="16">
-      <x:c r="P16" s="18"/>
-      <x:c r="Q16" s="18"/>
+      <x:c r="E16" s="18"/>
     </x:row>
     <x:row r="17">
-      <x:c r="P17" s="18"/>
-      <x:c r="Q17" s="18"/>
+      <x:c r="E17" s="18"/>
     </x:row>
     <x:row r="18">
-      <x:c r="P18" s="18"/>
-      <x:c r="Q18" s="18"/>
+      <x:c r="E18" s="18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="P19" s="18"/>
-      <x:c r="Q19" s="18"/>
+      <x:c r="E19" s="18"/>
     </x:row>
     <x:row r="20">
-      <x:c r="P20" s="18"/>
-      <x:c r="Q20" s="18"/>
+      <x:c r="E20" s="18"/>
     </x:row>
     <x:row r="21">
-      <x:c r="P21" s="18"/>
-      <x:c r="Q21" s="18"/>
+      <x:c r="E21" s="18"/>
     </x:row>
     <x:row r="22">
-      <x:c r="P22" s="18"/>
-      <x:c r="Q22" s="18"/>
+      <x:c r="E22" s="18"/>
     </x:row>
     <x:row r="23">
-      <x:c r="P23" s="18"/>
-      <x:c r="Q23" s="18"/>
+      <x:c r="E23" s="18"/>
     </x:row>
     <x:row r="24">
-      <x:c r="P24" s="18"/>
-      <x:c r="Q24" s="18"/>
+      <x:c r="E24" s="18"/>
     </x:row>
     <x:row r="25">
-      <x:c r="P25" s="18"/>
-      <x:c r="Q25" s="18"/>
+      <x:c r="E25" s="18"/>
     </x:row>
     <x:row r="26">
-      <x:c r="P26" s="18"/>
-      <x:c r="Q26" s="18"/>
+      <x:c r="E26" s="18"/>
     </x:row>
     <x:row r="27">
-      <x:c r="P27" s="18"/>
-      <x:c r="Q27" s="18"/>
+      <x:c r="E27" s="18"/>
     </x:row>
     <x:row r="28">
-      <x:c r="P28" s="18"/>
-      <x:c r="Q28" s="18"/>
+      <x:c r="E28" s="18"/>
     </x:row>
     <x:row r="29">
-      <x:c r="P29" s="18"/>
-      <x:c r="Q29" s="18"/>
+      <x:c r="E29" s="18"/>
     </x:row>
     <x:row r="30">
-      <x:c r="P30" s="18"/>
-      <x:c r="Q30" s="18"/>
+      <x:c r="E30" s="18"/>
     </x:row>
     <x:row r="31">
-      <x:c r="P31" s="18"/>
-      <x:c r="Q31" s="18"/>
+      <x:c r="E31" s="18"/>
     </x:row>
     <x:row r="32">
-      <x:c r="P32" s="18"/>
-      <x:c r="Q32" s="18"/>
+      <x:c r="E32" s="18"/>
     </x:row>
     <x:row r="33">
-      <x:c r="P33" s="18"/>
-      <x:c r="Q33" s="18"/>
+      <x:c r="E33" s="18"/>
     </x:row>
     <x:row r="34">
-      <x:c r="P34" s="18"/>
-      <x:c r="Q34" s="18"/>
+      <x:c r="E34" s="18"/>
     </x:row>
     <x:row r="35">
-      <x:c r="P35" s="18"/>
-      <x:c r="Q35" s="18"/>
+      <x:c r="E35" s="18"/>
     </x:row>
     <x:row r="36">
-      <x:c r="P36" s="18"/>
-      <x:c r="Q36" s="18"/>
+      <x:c r="E36" s="18"/>
     </x:row>
     <x:row r="37">
-      <x:c r="P37" s="18"/>
-      <x:c r="Q37" s="18"/>
+      <x:c r="E37" s="18"/>
     </x:row>
     <x:row r="38">
-      <x:c r="P38" s="18"/>
-      <x:c r="Q38" s="18"/>
+      <x:c r="E38" s="18"/>
     </x:row>
     <x:row r="39">
-      <x:c r="P39" s="18"/>
-      <x:c r="Q39" s="18"/>
+      <x:c r="E39" s="18"/>
     </x:row>
     <x:row r="40">
-      <x:c r="P40" s="18"/>
-      <x:c r="Q40" s="18"/>
+      <x:c r="E40" s="18"/>
     </x:row>
     <x:row r="41">
-      <x:c r="P41" s="18"/>
-      <x:c r="Q41" s="18"/>
+      <x:c r="E41" s="18"/>
     </x:row>
     <x:row r="42">
-      <x:c r="P42" s="18"/>
-      <x:c r="Q42" s="18"/>
+      <x:c r="E42" s="18"/>
     </x:row>
     <x:row r="43">
-      <x:c r="P43" s="18"/>
-      <x:c r="Q43" s="18"/>
+      <x:c r="E43" s="18"/>
     </x:row>
     <x:row r="44">
-      <x:c r="P44" s="18"/>
-      <x:c r="Q44" s="18"/>
+      <x:c r="E44" s="18"/>
     </x:row>
     <x:row r="45">
-      <x:c r="P45" s="18"/>
-      <x:c r="Q45" s="18"/>
+      <x:c r="E45" s="18"/>
     </x:row>
     <x:row r="46">
-      <x:c r="P46" s="18"/>
-      <x:c r="Q46" s="18"/>
+      <x:c r="E46" s="18"/>
     </x:row>
     <x:row r="47">
-      <x:c r="P47" s="18"/>
-      <x:c r="Q47" s="18"/>
+      <x:c r="E47" s="18"/>
     </x:row>
     <x:row r="48">
-      <x:c r="P48" s="18"/>
-      <x:c r="Q48" s="18"/>
+      <x:c r="E48" s="18"/>
     </x:row>
     <x:row r="49">
-      <x:c r="P49" s="18"/>
-      <x:c r="Q49" s="18"/>
+      <x:c r="E49" s="18"/>
     </x:row>
     <x:row r="50">
-      <x:c r="P50" s="18"/>
-      <x:c r="Q50" s="18"/>
+      <x:c r="E50" s="18"/>
     </x:row>
     <x:row r="51">
-      <x:c r="P51" s="18"/>
-      <x:c r="Q51" s="18"/>
+      <x:c r="E51" s="18"/>
     </x:row>
     <x:row r="52">
-      <x:c r="P52" s="18"/>
-      <x:c r="Q52" s="18"/>
+      <x:c r="E52" s="18"/>
     </x:row>
     <x:row r="53">
-      <x:c r="P53" s="18"/>
-      <x:c r="Q53" s="18"/>
+      <x:c r="E53" s="18"/>
     </x:row>
     <x:row r="54">
-      <x:c r="P54" s="18"/>
-      <x:c r="Q54" s="18"/>
+      <x:c r="E54" s="18"/>
     </x:row>
     <x:row r="55">
-      <x:c r="P55" s="18"/>
-      <x:c r="Q55" s="18"/>
+      <x:c r="E55" s="18"/>
     </x:row>
     <x:row r="56">
-      <x:c r="P56" s="18"/>
-      <x:c r="Q56" s="18"/>
+      <x:c r="E56" s="18"/>
     </x:row>
     <x:row r="57">
-      <x:c r="P57" s="18"/>
-      <x:c r="Q57" s="18"/>
+      <x:c r="E57" s="18"/>
     </x:row>
     <x:row r="58">
-      <x:c r="P58" s="18"/>
-      <x:c r="Q58" s="18"/>
+      <x:c r="E58" s="18"/>
     </x:row>
     <x:row r="59">
-      <x:c r="P59" s="18"/>
-      <x:c r="Q59" s="18"/>
+      <x:c r="E59" s="18"/>
     </x:row>
     <x:row r="60">
-      <x:c r="P60" s="18"/>
-      <x:c r="Q60" s="18"/>
+      <x:c r="E60" s="18"/>
     </x:row>
     <x:row r="61">
-      <x:c r="P61" s="18"/>
-      <x:c r="Q61" s="18"/>
+      <x:c r="E61" s="18"/>
     </x:row>
     <x:row r="62">
-      <x:c r="P62" s="18"/>
-      <x:c r="Q62" s="18"/>
+      <x:c r="E62" s="18"/>
     </x:row>
     <x:row r="63">
-      <x:c r="P63" s="18"/>
-      <x:c r="Q63" s="18"/>
+      <x:c r="E63" s="18"/>
     </x:row>
     <x:row r="64">
-      <x:c r="P64" s="18"/>
-      <x:c r="Q64" s="18"/>
+      <x:c r="E64" s="18"/>
     </x:row>
     <x:row r="65">
-      <x:c r="P65" s="18"/>
-      <x:c r="Q65" s="18"/>
+      <x:c r="E65" s="18"/>
     </x:row>
     <x:row r="66">
-      <x:c r="P66" s="18"/>
-      <x:c r="Q66" s="18"/>
+      <x:c r="E66" s="18"/>
     </x:row>
     <x:row r="67">
-      <x:c r="P67" s="18"/>
-      <x:c r="Q67" s="18"/>
+      <x:c r="E67" s="18"/>
     </x:row>
     <x:row r="68">
-      <x:c r="P68" s="18"/>
-      <x:c r="Q68" s="18"/>
+      <x:c r="E68" s="18"/>
     </x:row>
     <x:row r="69">
-      <x:c r="P69" s="18"/>
-      <x:c r="Q69" s="18"/>
+      <x:c r="E69" s="18"/>
     </x:row>
     <x:row r="70">
-      <x:c r="P70" s="18"/>
-      <x:c r="Q70" s="18"/>
+      <x:c r="E70" s="18"/>
     </x:row>
     <x:row r="71">
-      <x:c r="P71" s="18"/>
-      <x:c r="Q71" s="18"/>
+      <x:c r="E71" s="18"/>
     </x:row>
     <x:row r="72">
-      <x:c r="P72" s="18"/>
-      <x:c r="Q72" s="18"/>
+      <x:c r="E72" s="18"/>
     </x:row>
     <x:row r="73">
-      <x:c r="P73" s="18"/>
-      <x:c r="Q73" s="18"/>
+      <x:c r="E73" s="18"/>
     </x:row>
     <x:row r="74">
-      <x:c r="P74" s="18"/>
-      <x:c r="Q74" s="18"/>
+      <x:c r="E74" s="18"/>
     </x:row>
     <x:row r="75">
-      <x:c r="P75" s="18"/>
-      <x:c r="Q75" s="18"/>
+      <x:c r="E75" s="18"/>
     </x:row>
     <x:row r="76">
-      <x:c r="P76" s="18"/>
-      <x:c r="Q76" s="18"/>
+      <x:c r="E76" s="18"/>
     </x:row>
     <x:row r="77">
-      <x:c r="P77" s="18"/>
-      <x:c r="Q77" s="18"/>
+      <x:c r="E77" s="18"/>
     </x:row>
     <x:row r="78">
-      <x:c r="P78" s="18"/>
-      <x:c r="Q78" s="18"/>
+      <x:c r="E78" s="18"/>
     </x:row>
     <x:row r="79">
-      <x:c r="P79" s="18"/>
-      <x:c r="Q79" s="18"/>
+      <x:c r="E79" s="18"/>
     </x:row>
     <x:row r="80">
-      <x:c r="P80" s="18"/>
-      <x:c r="Q80" s="18"/>
+      <x:c r="E80" s="18"/>
     </x:row>
     <x:row r="81">
-      <x:c r="P81" s="18"/>
-      <x:c r="Q81" s="18"/>
+      <x:c r="E81" s="18"/>
     </x:row>
     <x:row r="82">
-      <x:c r="P82" s="18"/>
-      <x:c r="Q82" s="18"/>
+      <x:c r="E82" s="18"/>
     </x:row>
     <x:row r="83">
-      <x:c r="P83" s="18"/>
-      <x:c r="Q83" s="18"/>
+      <x:c r="E83" s="18"/>
     </x:row>
     <x:row r="84">
-      <x:c r="P84" s="18"/>
-      <x:c r="Q84" s="18"/>
+      <x:c r="E84" s="18"/>
     </x:row>
     <x:row r="85">
-      <x:c r="P85" s="18"/>
-      <x:c r="Q85" s="18"/>
+      <x:c r="E85" s="18"/>
     </x:row>
     <x:row r="86">
-      <x:c r="P86" s="18"/>
-      <x:c r="Q86" s="18"/>
+      <x:c r="E86" s="18"/>
     </x:row>
     <x:row r="87">
-      <x:c r="P87" s="18"/>
-      <x:c r="Q87" s="18"/>
+      <x:c r="E87" s="18"/>
     </x:row>
     <x:row r="88">
-      <x:c r="P88" s="18"/>
-      <x:c r="Q88" s="18"/>
+      <x:c r="E88" s="18"/>
     </x:row>
     <x:row r="89">
-      <x:c r="P89" s="18"/>
-      <x:c r="Q89" s="18"/>
+      <x:c r="E89" s="18"/>
     </x:row>
     <x:row r="90">
-      <x:c r="P90" s="18"/>
-      <x:c r="Q90" s="18"/>
+      <x:c r="E90" s="18"/>
     </x:row>
     <x:row r="91">
-      <x:c r="P91" s="18"/>
-      <x:c r="Q91" s="18"/>
+      <x:c r="E91" s="18"/>
     </x:row>
     <x:row r="92">
-      <x:c r="P92" s="18"/>
-      <x:c r="Q92" s="18"/>
+      <x:c r="E92" s="18"/>
     </x:row>
     <x:row r="93">
-      <x:c r="P93" s="18"/>
-      <x:c r="Q93" s="18"/>
+      <x:c r="E93" s="18"/>
     </x:row>
     <x:row r="94">
-      <x:c r="P94" s="18"/>
-      <x:c r="Q94" s="18"/>
+      <x:c r="E94" s="18"/>
     </x:row>
     <x:row r="95">
-      <x:c r="P95" s="18"/>
-      <x:c r="Q95" s="18"/>
+      <x:c r="E95" s="18"/>
     </x:row>
     <x:row r="96">
-      <x:c r="P96" s="18"/>
-      <x:c r="Q96" s="18"/>
+      <x:c r="E96" s="18"/>
     </x:row>
     <x:row r="97">
-      <x:c r="P97" s="18"/>
-      <x:c r="Q97" s="18"/>
+      <x:c r="E97" s="18"/>
     </x:row>
     <x:row r="98">
-      <x:c r="P98" s="18"/>
-      <x:c r="Q98" s="18"/>
+      <x:c r="E98" s="18"/>
     </x:row>
     <x:row r="99">
-      <x:c r="P99" s="18"/>
-      <x:c r="Q99" s="18"/>
+      <x:c r="E99" s="18"/>
     </x:row>
     <x:row r="100">
-      <x:c r="P100" s="18"/>
-      <x:c r="Q100" s="18"/>
+      <x:c r="E100" s="18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1299,7 +2588,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c2aa61fcde94ed2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb2f9b23aff645a9"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1424,10 +2713,10 @@
         <x:v>Cama</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Activa</x:v>
+        <x:v>No activa</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Espacio disponible</x:v>
+        <x:v>Sin cultivos activos</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1487,7 +2776,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4a4299ed9a4465"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9af87fcfa28946dd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1953,7 +3242,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92f6337ef8614c14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06ae80cc640c42cc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2017,9 +3306,6 @@
       <x:c r="M1" s="10" t="str">
         <x:v>Notas</x:v>
       </x:c>
-      <x:c r="N1" s="23" t="str">
-        <x:v>Evento_Agricola</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -2057,9 +3343,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M2" s="11" t="str"/>
-      <x:c r="N2" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -2097,9 +3380,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M3" s="11" t="str"/>
-      <x:c r="N3" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -2137,9 +3417,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M4" s="11" t="str"/>
-      <x:c r="N4" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -2177,9 +3454,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M5" s="11" t="str"/>
-      <x:c r="N5" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -2217,9 +3491,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M6" s="11" t="str"/>
-      <x:c r="N6" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -2257,9 +3528,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M7" s="11" t="str"/>
-      <x:c r="N7" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -2297,9 +3565,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M8" s="11" t="str"/>
-      <x:c r="N8" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -2331,9 +3596,6 @@
       <x:c r="M9" s="11" t="str">
         <x:v>Espacio disponible</x:v>
       </x:c>
-      <x:c r="N9" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -2371,9 +3633,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M10" s="11" t="str"/>
-      <x:c r="N10" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -2411,9 +3670,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M11" s="11" t="str"/>
-      <x:c r="N11" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -2451,9 +3707,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M12" s="11" t="str"/>
-      <x:c r="N12" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -2491,9 +3744,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M13" s="11" t="str"/>
-      <x:c r="N13" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -2531,9 +3781,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M14" s="11" t="str"/>
-      <x:c r="N14" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -2571,9 +3818,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M15" s="11" t="str"/>
-      <x:c r="N15" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -2611,9 +3855,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M16" s="11" t="str"/>
-      <x:c r="N16" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -2651,9 +3892,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M17" s="11" t="str"/>
-      <x:c r="N17" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
@@ -2693,9 +3931,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M18" s="11" t="str"/>
-      <x:c r="N18" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -2733,9 +3968,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M19" s="11" t="str"/>
-      <x:c r="N19" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -2773,9 +4005,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M20" s="11" t="str"/>
-      <x:c r="N20" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -2813,9 +4042,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M21" s="11" t="str"/>
-      <x:c r="N21" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -2855,9 +4081,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M22" s="11" t="str"/>
-      <x:c r="N22" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -2895,9 +4118,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M23" s="11" t="str"/>
-      <x:c r="N23" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
@@ -2929,9 +4149,6 @@
       <x:c r="M24" s="11" t="str">
         <x:v>Espacio disponible</x:v>
       </x:c>
-      <x:c r="N24" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
@@ -2969,9 +4186,6 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M25" s="11" t="str"/>
-      <x:c r="N25" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -3009,279 +4223,11 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M26" s="11" t="str"/>
-      <x:c r="N26" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>SIE_FRA_018</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>UNI_FRA_CAMA_04</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>CUL_DISPONIBLE</x:v>
-      </x:c>
-      <x:c r="E27" s="18"/>
-      <x:c r="F27" s="18"/>
-      <x:c r="G27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H27" t="str">
-        <x:v>Disponible</x:v>
-      </x:c>
-      <x:c r="I27" s="18"/>
-      <x:c r="J27" s="18"/>
-      <x:c r="K27" s="18"/>
-      <x:c r="L27" t="str">
-        <x:v>Completa</x:v>
-      </x:c>
-      <x:c r="M27" t="str">
-        <x:v>Espacio disponible</x:v>
-      </x:c>
-      <x:c r="N27" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="E28" s="18"/>
-      <x:c r="F28" s="18"/>
-      <x:c r="I28" s="18"/>
-      <x:c r="J28" s="18"/>
-      <x:c r="K28" s="18"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="E29" s="18"/>
-      <x:c r="F29" s="18"/>
-      <x:c r="I29" s="18"/>
-      <x:c r="J29" s="18"/>
-      <x:c r="K29" s="18"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="E30" s="18"/>
-      <x:c r="F30" s="18"/>
-      <x:c r="I30" s="18"/>
-      <x:c r="J30" s="18"/>
-      <x:c r="K30" s="18"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="E31" s="18"/>
-      <x:c r="F31" s="18"/>
-      <x:c r="I31" s="18"/>
-      <x:c r="J31" s="18"/>
-      <x:c r="K31" s="18"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="E32" s="18"/>
-      <x:c r="F32" s="18"/>
-      <x:c r="I32" s="18"/>
-      <x:c r="J32" s="18"/>
-      <x:c r="K32" s="18"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="E33" s="18"/>
-      <x:c r="F33" s="18"/>
-      <x:c r="I33" s="18"/>
-      <x:c r="J33" s="18"/>
-      <x:c r="K33" s="18"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="E34" s="18"/>
-      <x:c r="F34" s="18"/>
-      <x:c r="I34" s="18"/>
-      <x:c r="J34" s="18"/>
-      <x:c r="K34" s="18"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="E35" s="18"/>
-      <x:c r="F35" s="18"/>
-      <x:c r="I35" s="18"/>
-      <x:c r="J35" s="18"/>
-      <x:c r="K35" s="18"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="E36" s="18"/>
-      <x:c r="F36" s="18"/>
-      <x:c r="I36" s="18"/>
-      <x:c r="J36" s="18"/>
-      <x:c r="K36" s="18"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="E37" s="18"/>
-      <x:c r="F37" s="18"/>
-      <x:c r="I37" s="18"/>
-      <x:c r="J37" s="18"/>
-      <x:c r="K37" s="18"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="E38" s="18"/>
-      <x:c r="F38" s="18"/>
-      <x:c r="I38" s="18"/>
-      <x:c r="J38" s="18"/>
-      <x:c r="K38" s="18"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="E39" s="18"/>
-      <x:c r="F39" s="18"/>
-      <x:c r="I39" s="18"/>
-      <x:c r="J39" s="18"/>
-      <x:c r="K39" s="18"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="E40" s="18"/>
-      <x:c r="F40" s="18"/>
-      <x:c r="I40" s="18"/>
-      <x:c r="J40" s="18"/>
-      <x:c r="K40" s="18"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="E41" s="18"/>
-      <x:c r="F41" s="18"/>
-      <x:c r="I41" s="18"/>
-      <x:c r="J41" s="18"/>
-      <x:c r="K41" s="18"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="E42" s="18"/>
-      <x:c r="F42" s="18"/>
-      <x:c r="I42" s="18"/>
-      <x:c r="J42" s="18"/>
-      <x:c r="K42" s="18"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="E43" s="18"/>
-      <x:c r="F43" s="18"/>
-      <x:c r="I43" s="18"/>
-      <x:c r="J43" s="18"/>
-      <x:c r="K43" s="18"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="E44" s="18"/>
-      <x:c r="F44" s="18"/>
-      <x:c r="I44" s="18"/>
-      <x:c r="J44" s="18"/>
-      <x:c r="K44" s="18"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="E45" s="18"/>
-      <x:c r="F45" s="18"/>
-      <x:c r="I45" s="18"/>
-      <x:c r="J45" s="18"/>
-      <x:c r="K45" s="18"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="E46" s="18"/>
-      <x:c r="F46" s="18"/>
-      <x:c r="I46" s="18"/>
-      <x:c r="J46" s="18"/>
-      <x:c r="K46" s="18"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="E47" s="18"/>
-      <x:c r="F47" s="18"/>
-      <x:c r="I47" s="18"/>
-      <x:c r="J47" s="18"/>
-      <x:c r="K47" s="18"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="E48" s="18"/>
-      <x:c r="F48" s="18"/>
-      <x:c r="I48" s="18"/>
-      <x:c r="J48" s="18"/>
-      <x:c r="K48" s="18"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="E49" s="18"/>
-      <x:c r="F49" s="18"/>
-      <x:c r="I49" s="18"/>
-      <x:c r="J49" s="18"/>
-      <x:c r="K49" s="18"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="E50" s="18"/>
-      <x:c r="F50" s="18"/>
-      <x:c r="I50" s="18"/>
-      <x:c r="J50" s="18"/>
-      <x:c r="K50" s="18"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="E51" s="18"/>
-      <x:c r="F51" s="18"/>
-      <x:c r="I51" s="18"/>
-      <x:c r="J51" s="18"/>
-      <x:c r="K51" s="18"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="E52" s="18"/>
-      <x:c r="F52" s="18"/>
-      <x:c r="I52" s="18"/>
-      <x:c r="J52" s="18"/>
-      <x:c r="K52" s="18"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="E53" s="18"/>
-      <x:c r="F53" s="18"/>
-      <x:c r="I53" s="18"/>
-      <x:c r="J53" s="18"/>
-      <x:c r="K53" s="18"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="E54" s="18"/>
-      <x:c r="F54" s="18"/>
-      <x:c r="I54" s="18"/>
-      <x:c r="J54" s="18"/>
-      <x:c r="K54" s="18"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="E55" s="18"/>
-      <x:c r="F55" s="18"/>
-      <x:c r="I55" s="18"/>
-      <x:c r="J55" s="18"/>
-      <x:c r="K55" s="18"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="E56" s="18"/>
-      <x:c r="F56" s="18"/>
-      <x:c r="I56" s="18"/>
-      <x:c r="J56" s="18"/>
-      <x:c r="K56" s="18"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="E57" s="18"/>
-      <x:c r="F57" s="18"/>
-      <x:c r="I57" s="18"/>
-      <x:c r="J57" s="18"/>
-      <x:c r="K57" s="18"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="E58" s="18"/>
-      <x:c r="F58" s="18"/>
-      <x:c r="I58" s="18"/>
-      <x:c r="J58" s="18"/>
-      <x:c r="K58" s="18"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="E59" s="18"/>
-      <x:c r="F59" s="18"/>
-      <x:c r="I59" s="18"/>
-      <x:c r="J59" s="18"/>
-      <x:c r="K59" s="18"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="E60" s="18"/>
-      <x:c r="F60" s="18"/>
-      <x:c r="I60" s="18"/>
-      <x:c r="J60" s="18"/>
-      <x:c r="K60" s="18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refc14cba555b43ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e133099af24394"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3361,9 +4307,6 @@
       <x:c r="Q1" s="10" t="str">
         <x:v>Mes_Cosecha</x:v>
       </x:c>
-      <x:c r="R1" s="23" t="str">
-        <x:v>Evento_Agricola</x:v>
-      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -3413,9 +4356,6 @@
       <x:c r="Q2" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
-      <x:c r="R2" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -3465,9 +4405,6 @@
       <x:c r="Q3" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
-      <x:c r="R3" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -3517,9 +4454,6 @@
       <x:c r="Q4" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
-      <x:c r="R4" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -3569,9 +4503,6 @@
       <x:c r="Q5" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
-      <x:c r="R5" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -3621,9 +4552,6 @@
       <x:c r="Q6" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
-      <x:c r="R6" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -3673,9 +4601,6 @@
       <x:c r="Q7" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
-      <x:c r="R7" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -3724,9 +4649,6 @@
       <x:c r="P8" s="11" t="str"/>
       <x:c r="Q8" s="11" t="str">
         <x:v>2026-06</x:v>
-      </x:c>
-      <x:c r="R8" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -3769,9 +4691,6 @@
       <x:c r="Q9" s="11" t="str">
         <x:v>Sin fecha</x:v>
       </x:c>
-      <x:c r="R9" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -3821,9 +4740,6 @@
       <x:c r="Q10" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
-      <x:c r="R10" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -3873,9 +4789,6 @@
       <x:c r="Q11" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R11" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -3925,9 +4838,6 @@
       <x:c r="Q12" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
-      <x:c r="R12" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -3977,9 +4887,6 @@
       <x:c r="Q13" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R13" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -4029,9 +4936,6 @@
       <x:c r="Q14" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R14" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -4081,9 +4985,6 @@
       <x:c r="Q15" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
-      <x:c r="R15" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -4133,9 +5034,6 @@
       <x:c r="Q16" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R16" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -4185,9 +5083,6 @@
       <x:c r="Q17" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R17" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
@@ -4239,9 +5134,6 @@
       <x:c r="Q18" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R18" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -4291,9 +5183,6 @@
       <x:c r="Q19" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R19" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -4343,9 +5232,6 @@
       <x:c r="Q20" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
-      <x:c r="R20" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -4395,9 +5281,6 @@
       <x:c r="Q21" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R21" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -4449,9 +5332,6 @@
       <x:c r="Q22" s="11" t="str">
         <x:v>2026-08</x:v>
       </x:c>
-      <x:c r="R22" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -4500,9 +5380,6 @@
       <x:c r="P23" s="11" t="str"/>
       <x:c r="Q23" s="11" t="str">
         <x:v>2026-06</x:v>
-      </x:c>
-      <x:c r="R23" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -4545,9 +5422,6 @@
       <x:c r="Q24" s="11" t="str">
         <x:v>Sin fecha</x:v>
       </x:c>
-      <x:c r="R24" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
@@ -4597,9 +5471,6 @@
       <x:c r="Q25" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
-      <x:c r="R25" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -4649,289 +5520,11 @@
       <x:c r="Q26" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
-      <x:c r="R26" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27">
-      <x:c r="A27" t="str">
-        <x:v>SIE_FRA_018</x:v>
-      </x:c>
-      <x:c r="B27" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="C27" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="D27" t="str">
-        <x:v>Cama Frailes 4</x:v>
-      </x:c>
-      <x:c r="E27" t="str">
-        <x:v>UNI_FRA_CAMA_04</x:v>
-      </x:c>
-      <x:c r="F27" t="str">
-        <x:v>Activa</x:v>
-      </x:c>
-      <x:c r="G27" t="str">
-        <x:v>Disponible</x:v>
-      </x:c>
-      <x:c r="H27" t="str">
-        <x:v>CUL_DISPONIBLE</x:v>
-      </x:c>
-      <x:c r="I27" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="J27" t="str">
-        <x:v>Disponible</x:v>
-      </x:c>
-      <x:c r="K27" s="18"/>
-      <x:c r="L27" s="18"/>
-      <x:c r="M27" s="18"/>
-      <x:c r="N27" s="18"/>
-      <x:c r="O27" s="18"/>
-      <x:c r="P27"/>
-      <x:c r="Q27" t="str">
-        <x:v>Sin fecha</x:v>
-      </x:c>
-      <x:c r="R27" s="11" t="str">
-        <x:v>Ver EventosAgricolas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28">
-      <x:c r="K28" s="18"/>
-      <x:c r="L28" s="18"/>
-      <x:c r="M28" s="18"/>
-      <x:c r="N28" s="18"/>
-      <x:c r="O28" s="18"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="K29" s="18"/>
-      <x:c r="L29" s="18"/>
-      <x:c r="M29" s="18"/>
-      <x:c r="N29" s="18"/>
-      <x:c r="O29" s="18"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="K30" s="18"/>
-      <x:c r="L30" s="18"/>
-      <x:c r="M30" s="18"/>
-      <x:c r="N30" s="18"/>
-      <x:c r="O30" s="18"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="K31" s="18"/>
-      <x:c r="L31" s="18"/>
-      <x:c r="M31" s="18"/>
-      <x:c r="N31" s="18"/>
-      <x:c r="O31" s="18"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="K32" s="18"/>
-      <x:c r="L32" s="18"/>
-      <x:c r="M32" s="18"/>
-      <x:c r="N32" s="18"/>
-      <x:c r="O32" s="18"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="K33" s="18"/>
-      <x:c r="L33" s="18"/>
-      <x:c r="M33" s="18"/>
-      <x:c r="N33" s="18"/>
-      <x:c r="O33" s="18"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="K34" s="18"/>
-      <x:c r="L34" s="18"/>
-      <x:c r="M34" s="18"/>
-      <x:c r="N34" s="18"/>
-      <x:c r="O34" s="18"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="K35" s="18"/>
-      <x:c r="L35" s="18"/>
-      <x:c r="M35" s="18"/>
-      <x:c r="N35" s="18"/>
-      <x:c r="O35" s="18"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="K36" s="18"/>
-      <x:c r="L36" s="18"/>
-      <x:c r="M36" s="18"/>
-      <x:c r="N36" s="18"/>
-      <x:c r="O36" s="18"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="K37" s="18"/>
-      <x:c r="L37" s="18"/>
-      <x:c r="M37" s="18"/>
-      <x:c r="N37" s="18"/>
-      <x:c r="O37" s="18"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="K38" s="18"/>
-      <x:c r="L38" s="18"/>
-      <x:c r="M38" s="18"/>
-      <x:c r="N38" s="18"/>
-      <x:c r="O38" s="18"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="K39" s="18"/>
-      <x:c r="L39" s="18"/>
-      <x:c r="M39" s="18"/>
-      <x:c r="N39" s="18"/>
-      <x:c r="O39" s="18"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="K40" s="18"/>
-      <x:c r="L40" s="18"/>
-      <x:c r="M40" s="18"/>
-      <x:c r="N40" s="18"/>
-      <x:c r="O40" s="18"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="K41" s="18"/>
-      <x:c r="L41" s="18"/>
-      <x:c r="M41" s="18"/>
-      <x:c r="N41" s="18"/>
-      <x:c r="O41" s="18"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="K42" s="18"/>
-      <x:c r="L42" s="18"/>
-      <x:c r="M42" s="18"/>
-      <x:c r="N42" s="18"/>
-      <x:c r="O42" s="18"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="K43" s="18"/>
-      <x:c r="L43" s="18"/>
-      <x:c r="M43" s="18"/>
-      <x:c r="N43" s="18"/>
-      <x:c r="O43" s="18"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="K44" s="18"/>
-      <x:c r="L44" s="18"/>
-      <x:c r="M44" s="18"/>
-      <x:c r="N44" s="18"/>
-      <x:c r="O44" s="18"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="K45" s="18"/>
-      <x:c r="L45" s="18"/>
-      <x:c r="M45" s="18"/>
-      <x:c r="N45" s="18"/>
-      <x:c r="O45" s="18"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="K46" s="18"/>
-      <x:c r="L46" s="18"/>
-      <x:c r="M46" s="18"/>
-      <x:c r="N46" s="18"/>
-      <x:c r="O46" s="18"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="K47" s="18"/>
-      <x:c r="L47" s="18"/>
-      <x:c r="M47" s="18"/>
-      <x:c r="N47" s="18"/>
-      <x:c r="O47" s="18"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="K48" s="18"/>
-      <x:c r="L48" s="18"/>
-      <x:c r="M48" s="18"/>
-      <x:c r="N48" s="18"/>
-      <x:c r="O48" s="18"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="K49" s="18"/>
-      <x:c r="L49" s="18"/>
-      <x:c r="M49" s="18"/>
-      <x:c r="N49" s="18"/>
-      <x:c r="O49" s="18"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="K50" s="18"/>
-      <x:c r="L50" s="18"/>
-      <x:c r="M50" s="18"/>
-      <x:c r="N50" s="18"/>
-      <x:c r="O50" s="18"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="K51" s="18"/>
-      <x:c r="L51" s="18"/>
-      <x:c r="M51" s="18"/>
-      <x:c r="N51" s="18"/>
-      <x:c r="O51" s="18"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="K52" s="18"/>
-      <x:c r="L52" s="18"/>
-      <x:c r="M52" s="18"/>
-      <x:c r="N52" s="18"/>
-      <x:c r="O52" s="18"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="K53" s="18"/>
-      <x:c r="L53" s="18"/>
-      <x:c r="M53" s="18"/>
-      <x:c r="N53" s="18"/>
-      <x:c r="O53" s="18"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="K54" s="18"/>
-      <x:c r="L54" s="18"/>
-      <x:c r="M54" s="18"/>
-      <x:c r="N54" s="18"/>
-      <x:c r="O54" s="18"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="K55" s="18"/>
-      <x:c r="L55" s="18"/>
-      <x:c r="M55" s="18"/>
-      <x:c r="N55" s="18"/>
-      <x:c r="O55" s="18"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="K56" s="18"/>
-      <x:c r="L56" s="18"/>
-      <x:c r="M56" s="18"/>
-      <x:c r="N56" s="18"/>
-      <x:c r="O56" s="18"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="K57" s="18"/>
-      <x:c r="L57" s="18"/>
-      <x:c r="M57" s="18"/>
-      <x:c r="N57" s="18"/>
-      <x:c r="O57" s="18"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="K58" s="18"/>
-      <x:c r="L58" s="18"/>
-      <x:c r="M58" s="18"/>
-      <x:c r="N58" s="18"/>
-      <x:c r="O58" s="18"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="K59" s="18"/>
-      <x:c r="L59" s="18"/>
-      <x:c r="M59" s="18"/>
-      <x:c r="N59" s="18"/>
-      <x:c r="O59" s="18"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="K60" s="18"/>
-      <x:c r="L60" s="18"/>
-      <x:c r="M60" s="18"/>
-      <x:c r="N60" s="18"/>
-      <x:c r="O60" s="18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24f9597babe14961"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra36015e448df4c19"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4940,78 +5533,126 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="13.319999694824219" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.020000457763672" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="10" t="str">
+      <x:c r="A1" s="24" t="str">
         <x:v>Lista</x:v>
       </x:c>
-      <x:c r="B1" s="10" t="str">
+      <x:c r="B1" s="24" t="str">
         <x:v>Valor</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Estados_Unidad</x:v>
+        <x:v>Tipo_Evento</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Activa</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Estados_Unidad</x:v>
+        <x:v>Tipo_Evento</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>No activa</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>Estados_Cultivo</x:v>
+        <x:v>Tipo_Evento</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Crecimiento</x:v>
+        <x:v>Poda</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>Estados_Cultivo</x:v>
+        <x:v>Tipo_Evento</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Floración</x:v>
+        <x:v>Abono foliar</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>Estados_Cultivo</x:v>
+        <x:v>Estado_Evento</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Disponible</x:v>
+        <x:v>No empezado</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>Estados_Cultivo</x:v>
+        <x:v>Estado_Evento</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Cosechado</x:v>
+        <x:v>Pendiente</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>Estados_Cultivo</x:v>
+        <x:v>Estado_Evento</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Sin fecha</x:v>
+        <x:v>Completado</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="11" t="str">
+        <x:v>Objeto_Tipo</x:v>
+      </x:c>
+      <x:c r="B9" s="11" t="str">
+        <x:v>Cultivo</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>Objeto_Tipo</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Árbol</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>Objeto_Tipo</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>Cama</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>Estado_Sanitario</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
+        <x:v>Estado_Sanitario</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>Atención</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="str">
+        <x:v>Estado_Sanitario</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>Estrés</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc327f05eb480415e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51aaf7bf38bd4985"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5020,405 +5661,181 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="17.899999618530273" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.959999084472656" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.609999656677246" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="43.34000015258789" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="51.68000030517578" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15.75" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="16.959999084472656" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.59000015258789" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="10.359999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.400000095367432" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22.479999542236328" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="24" t="str">
-        <x:v>ID_Insumo</x:v>
+        <x:v>Unidad_ID</x:v>
       </x:c>
       <x:c r="B1" s="24" t="str">
-        <x:v>Nombre</x:v>
+        <x:v>Finca_ID</x:v>
       </x:c>
       <x:c r="C1" s="24" t="str">
-        <x:v>Tipo</x:v>
+        <x:v>Unidad_Nombre</x:v>
       </x:c>
       <x:c r="D1" s="24" t="str">
-        <x:v>Disponible</x:v>
+        <x:v>Tipo_Unidad</x:v>
       </x:c>
       <x:c r="E1" s="24" t="str">
-        <x:v>Uso_Principal</x:v>
+        <x:v>Estado</x:v>
       </x:c>
       <x:c r="F1" s="24" t="str">
-        <x:v>Restricciones/Notas</x:v>
-      </x:c>
-      <x:c r="G1" s="24" t="str">
-        <x:v>Compra_Requerida</x:v>
+        <x:v>Notas</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>INS_COBRE</x:v>
+        <x:v>UNI_MOR_CAMA_01</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Cobre</x:v>
+        <x:v>FIN_MORAVIA</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Cama Moravia 1</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Hongos y bacterias en manejo preventivo/correctivo</x:v>
+        <x:v>Activa</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>Evitar mezclar sin validar compatibilidad; aplicar temprano/tarde</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>Incluye espacios disponibles</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>INS_NEEM</x:v>
+        <x:v>UNI_FRA_CAMA_01</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Neem</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Cama Frailes 1</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Control preventivo de insectos blandos</x:v>
-      </x:c>
-      <x:c r="F3" s="11" t="str">
-        <x:v>Evitar sol fuerte; repetir según presión de plaga</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="F3" s="11"/>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>INS_JABON_POTASICO</x:v>
+        <x:v>UNI_FRA_CAMA_02</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Jabón Potásico</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Cama Frailes 2</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Control de insectos blandos y limpieza foliar</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="str">
-        <x:v>Probar en pocas hojas antes de aplicar general</x:v>
-      </x:c>
-      <x:c r="G4" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="F4" s="11"/>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>INS_MISTRAL</x:v>
+        <x:v>UNI_FRA_CAMA_03</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Mistral</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Cama Frailes 3</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>Control fitosanitario según etiqueta</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
-        <x:v>Usar dosis de etiqueta; no aplicar en horas de calor</x:v>
-      </x:c>
-      <x:c r="G5" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="F5" s="11"/>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>INS_BICARBONATO</x:v>
+        <x:v>UNI_FRA_CAMA_04</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Bicarbonato de Sodio</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Cama Frailes 4</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Apoyo preventivo contra hongos superficiales</x:v>
+        <x:v>No activa</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>No abusar; puede quemar hojas si se concentra</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>Sin cultivos activos</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>INS_CAL_DOLOMITA</x:v>
+        <x:v>UNI_FRA_CAMA_05</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Cal Dolomita</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>Cama Frailes 5</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Corrección de suelo y aporte de calcio/magnesio</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="str">
-        <x:v>No aplicar pegado al tronco; incorporar superficialmente</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="F7" s="11"/>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>INS_CENIZA</x:v>
+        <x:v>UNI_FRA_CAMA_06</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Ceniza</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>Cama Frailes 6</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Aporte de potasio y minerales; enmienda suave</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="str">
-        <x:v>Usar moderado; puede subir pH</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="F8" s="11"/>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
-        <x:v>INS_MELASA</x:v>
+        <x:v>UNI_FRA_CAMA_07</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Melasa</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>Cama Frailes 7</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Cama</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>Activación biológica en mezclas y compost</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="str">
-        <x:v>Usar dosis baja; evitar exceso de azúcar</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="11" t="str">
-        <x:v>INS_COMPOST</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>Compost</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="str">
-        <x:v>Materia orgánica y mejora del suelo</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="str">
-        <x:v>Aplicar maduro; evitar contacto directo con cuello</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>INS_HENO</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>Heno</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="str">
-        <x:v>Cobertura/mulch para humedad y protección de suelo</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="str">
-        <x:v>Mantener separado del tronco para evitar hongos</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11" t="str">
-        <x:v>INS_GALLINAZA</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>Gallinaza</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="str">
-        <x:v>Abono orgánico alto en nitrógeno</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="str">
-        <x:v>Debe estar compostada; riesgo de quemar raíces</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="11" t="str">
-        <x:v>INS_YARAMILA</x:v>
-      </x:c>
-      <x:c r="B13" s="11" t="str">
-        <x:v>YaraMila</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="D13" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="str">
-        <x:v>Fertilización granulada de suelo</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="str">
-        <x:v>Usar dosis controlada; evitar excesos de nitrógeno</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="11" t="str">
-        <x:v>INS_CALCIO_BORO</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="str">
-        <x:v>Calcio Boro</x:v>
-      </x:c>
-      <x:c r="C14" s="11" t="str">
-        <x:v>Abono foliar</x:v>
-      </x:c>
-      <x:c r="D14" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E14" s="11" t="str">
-        <x:v>Floración, cuajado y llenado temprano</x:v>
-      </x:c>
-      <x:c r="F14" s="11" t="str">
-        <x:v>Aplicar temprano/tarde; no mezclar sin validar</x:v>
-      </x:c>
-      <x:c r="G14" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="11" t="str">
-        <x:v>INS_MULTIMINERAL</x:v>
-      </x:c>
-      <x:c r="B15" s="11" t="str">
-        <x:v>Multimineral</x:v>
-      </x:c>
-      <x:c r="C15" s="11" t="str">
-        <x:v>Abono foliar</x:v>
-      </x:c>
-      <x:c r="D15" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E15" s="11" t="str">
-        <x:v>Corrección/apoyo nutricional foliar</x:v>
-      </x:c>
-      <x:c r="F15" s="11" t="str">
-        <x:v>Respetar dosis; evitar estrés fuerte</x:v>
-      </x:c>
-      <x:c r="G15" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="11" t="str">
-        <x:v>INS_FOLIAR_7425</x:v>
-      </x:c>
-      <x:c r="B16" s="11" t="str">
-        <x:v>Foliar 7-4-25</x:v>
-      </x:c>
-      <x:c r="C16" s="11" t="str">
-        <x:v>Abono foliar</x:v>
-      </x:c>
-      <x:c r="D16" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E16" s="11" t="str">
-        <x:v>Apoyo potasio/foliar en desarrollo y llenado</x:v>
-      </x:c>
-      <x:c r="F16" s="11" t="str">
-        <x:v>Usar según etapa; evitar exceso</x:v>
-      </x:c>
-      <x:c r="G16" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="11" t="str">
-        <x:v>INS_PAS80</x:v>
-      </x:c>
-      <x:c r="B17" s="11" t="str">
-        <x:v>PAS-80</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="str">
-        <x:v>Coadyuvante</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="str">
-        <x:v>Mejorar adherencia/cobertura de aplicaciones foliares</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="str">
-        <x:v>Usar dosis baja según etiqueta</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="F9" s="11"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5429,526 +5846,612 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="28.399999618530273" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="6.460000038146973" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="16.149999618530273" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="4.440000057220459" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="15.210000038146973" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="8.479999542236328" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.729999542236328" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="35.2599983215332" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.81999969482422" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="38.4900016784668" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="41.04999923706055" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15.75" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="25.979999542236328" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="15.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="42.2599983215332" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="13.1899995803833" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="24" t="str">
-        <x:v>Arbol_ID</x:v>
+        <x:v>ID_Insumo</x:v>
       </x:c>
       <x:c r="B1" s="24" t="str">
-        <x:v>Finca_ID</x:v>
+        <x:v>Nombre</x:v>
       </x:c>
       <x:c r="C1" s="24" t="str">
-        <x:v>Finca</x:v>
+        <x:v>Tipo</x:v>
       </x:c>
       <x:c r="D1" s="24" t="str">
-        <x:v>Arbol</x:v>
+        <x:v>Disponible</x:v>
       </x:c>
       <x:c r="E1" s="24" t="str">
-        <x:v>Icono</x:v>
+        <x:v>Uso_Principal</x:v>
       </x:c>
       <x:c r="F1" s="24" t="str">
-        <x:v>Estado_Fenologico</x:v>
+        <x:v>Restricciones/Notas</x:v>
       </x:c>
       <x:c r="G1" s="24" t="str">
-        <x:v>Trasplante</x:v>
+        <x:v>Compra_Requerida</x:v>
       </x:c>
       <x:c r="H1" s="24" t="str">
-        <x:v>Estado_Sanitario</x:v>
+        <x:v>Cantidad_Guia</x:v>
       </x:c>
       <x:c r="I1" s="24" t="str">
-        <x:v>Evento_Agricola</x:v>
+        <x:v>Unidad_Medida</x:v>
       </x:c>
       <x:c r="J1" s="24" t="str">
-        <x:v>Notas</x:v>
+        <x:v>Momento_Aplicacion</x:v>
+      </x:c>
+      <x:c r="K1" s="24" t="str">
+        <x:v>Frecuencia_Dias</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>ARB_MANZANO_MORAVIA</x:v>
+        <x:v>INS_COBRE</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
+        <x:v>Cobre</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Moravia</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Manzano tico</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>🍎</x:v>
+        <x:v>Hongos/bacteriosis preventivo</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>Llenado</x:v>
+        <x:v>Evitar mezcla incompatible; aplicar temprano/tarde</x:v>
       </x:c>
       <x:c r="G2" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H2" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Según etiqueta</x:v>
       </x:c>
       <x:c r="I2" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>ml/L o g/L</x:v>
       </x:c>
       <x:c r="J2" s="11" t="str">
-        <x:v>Poda y manejo de chupones en seguimiento</x:v>
+        <x:v>Alta humedad / prevención hongos</x:v>
+      </x:c>
+      <x:c r="K2" s="11" t="n">
+        <x:v>14</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>ARB_GUAYABITA_MORAVIA</x:v>
+        <x:v>INS_NEEM</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
+        <x:v>Neem</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Moravia</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Guayabita del Perú</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>🌳</x:v>
+        <x:v>Insectos chupadores / preventivo suave</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>No aplicar con sol fuerte; verificar etiqueta</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Según etiqueta</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>ml/L</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str">
-        <x:v>Guayabita del Perú está en Moravia</x:v>
+        <x:v>Preventivo / presión baja de plaga</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="n">
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>ARB_GUAYABA_FRAILES</x:v>
+        <x:v>INS_JABON_POTASICO</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Jabón potásico</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Guayaba</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>🌳</x:v>
+        <x:v>Insectos blandos y limpieza de melaza</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>Floración</x:v>
+        <x:v>Probar en pocas hojas primero</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Según etiqueta</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>ml/L</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str">
-        <x:v>Diferente a Guayabita del Perú</x:v>
+        <x:v>Presencia de áfidos/cochinilla/mosca blanca</x:v>
+      </x:c>
+      <x:c r="K4" s="11" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>ARB_GUANABANA_FRAILES</x:v>
+        <x:v>INS_MISTRAL</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Mistral</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>Guanábana</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>🌳</x:v>
+        <x:v>Control fitosanitario correctivo/preventivo</x:v>
       </x:c>
       <x:c r="F5" s="11" t="str">
-        <x:v>Fructificación</x:v>
+        <x:v>Usar solo cuando corresponda; respetar etiqueta</x:v>
       </x:c>
       <x:c r="G5" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H5" s="11" t="str">
-        <x:v>Atención</x:v>
+        <x:v>Según etiqueta</x:v>
       </x:c>
       <x:c r="I5" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>ml/L o g/L</x:v>
       </x:c>
       <x:c r="J5" s="11" t="str">
-        <x:v>Puntos negros en frutos</x:v>
+        <x:v>Presión sanitaria / calendario preventivo</x:v>
+      </x:c>
+      <x:c r="K5" s="11" t="n">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>ARB_NARANJA_WASH_FRAILES</x:v>
+        <x:v>INS_BICARBONATO</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Bicarbonato de sodio</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Naranja Washington</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>🍊</x:v>
+        <x:v>Apoyo preventivo en hongos superficiales</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>Evitar exceso; puede quemar hojas</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>Jul 2025</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Baja dosis</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>g/L</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str">
-        <x:v>Trasplante 2025</x:v>
+        <x:v>Prevención ligera / humedad alta</x:v>
+      </x:c>
+      <x:c r="K6" s="11" t="n">
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>ARB_NARANJA_VALENCIA_FRAILES</x:v>
+        <x:v>INS_CAL_DOLOMITA</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Cal dolomita</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Naranja Valencia</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>🍊</x:v>
+        <x:v>Enmienda de suelo, calcio/magnesio</x:v>
       </x:c>
       <x:c r="F7" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>No tocar tronco; ideal corona con distancia</x:v>
       </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>Jul 2025</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H7" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Según tamaño/edad del árbol</x:v>
       </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>kg/árbol o g/cama</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str">
-        <x:v>Trasplante 2025</x:v>
+        <x:v>Postcosecha / enmienda de corona</x:v>
+      </x:c>
+      <x:c r="K7" s="11" t="n">
+        <x:v>180</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>ARB_LIMON_MANDARINA_FRAILES</x:v>
+        <x:v>INS_CENIZA</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Ceniza</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Limón mandarina</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>🍋</x:v>
+        <x:v>Potasio/enmienda ligera</x:v>
       </x:c>
       <x:c r="F8" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>Usar moderado; no exceder en suelos alcalinos</x:v>
       </x:c>
       <x:c r="G8" s="11" t="str">
-        <x:v>Jul 2025</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H8" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Puñado controlado</x:v>
       </x:c>
       <x:c r="I8" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>g/cama o g/árbol</x:v>
       </x:c>
       <x:c r="J8" s="11" t="str">
-        <x:v>Trasplante 2025</x:v>
+        <x:v>Postcosecha / crecimiento</x:v>
+      </x:c>
+      <x:c r="K8" s="11" t="n">
+        <x:v>45</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
-        <x:v>ARB_LIMON_MESINO_FRAILES</x:v>
+        <x:v>INS_MELASA</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Melasa</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Limón mesino</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>🍋</x:v>
+        <x:v>Apoyo microbiológico / mezcla compost</x:v>
       </x:c>
       <x:c r="F9" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>No exceder; evitar atraer hormigas</x:v>
       </x:c>
       <x:c r="G9" s="11" t="str">
-        <x:v>Jul 2025</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H9" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Baja dosis</x:v>
       </x:c>
       <x:c r="I9" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>ml/L</x:v>
       </x:c>
       <x:c r="J9" s="11" t="str">
-        <x:v>Trasplante 2025</x:v>
+        <x:v>Activación biológica / compost</x:v>
+      </x:c>
+      <x:c r="K9" s="11" t="n">
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
-        <x:v>ARB_LIMON_DULCE_FRAILES</x:v>
+        <x:v>INS_COMPOST</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Compost</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D10" s="11" t="str">
-        <x:v>Limón dulce</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>🍋</x:v>
+        <x:v>Materia orgánica y estructura de suelo</x:v>
       </x:c>
       <x:c r="F10" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>No cubrir pegado al tronco</x:v>
       </x:c>
       <x:c r="G10" s="11" t="str">
-        <x:v>Jul 2025</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H10" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Capa superficial</x:v>
       </x:c>
       <x:c r="I10" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>kg/cama o kg/árbol</x:v>
       </x:c>
       <x:c r="J10" s="11" t="str">
-        <x:v>Trasplante 2025</x:v>
+        <x:v>Siembra / postcosecha / mantenimiento</x:v>
+      </x:c>
+      <x:c r="K10" s="11" t="n">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
-        <x:v>ARB_MANDARINA_FRAILES</x:v>
+        <x:v>INS_HENO</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Heno</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>Mandarina</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>🍊</x:v>
+        <x:v>Cobertura/mulch y humedad</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>Brotes</x:v>
+        <x:v>No tocar base del tronco</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>Jul 2025</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Capa de cobertura</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>Abono foliar</x:v>
+        <x:v>cm de cobertura</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str">
-        <x:v>Trasplante 2025</x:v>
+        <x:v>Época seca / conservación humedad</x:v>
+      </x:c>
+      <x:c r="K11" s="11" t="n">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
-        <x:v>ARB_ANONA_FRAILES</x:v>
+        <x:v>INS_GALLINAZA</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Gallinaza</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>Anona</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>🌳</x:v>
+        <x:v>Nitrógeno y fertilidad de suelo</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>Recuperación</x:v>
+        <x:v>Debe estar compostada; puede quemar</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>Estrés</x:v>
+        <x:v>Muy moderado</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>g/cama o g/árbol</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str">
-        <x:v>Defoliación/recuperación</x:v>
+        <x:v>Vegetativo / recuperación</x:v>
+      </x:c>
+      <x:c r="K12" s="11" t="n">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
-        <x:v>ARB_NISPERO_FRAILES</x:v>
+        <x:v>INS_YARAMILA</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>YaraMila</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D13" s="11" t="str">
-        <x:v>Níspero</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>🌳</x:v>
+        <x:v>Fertilización NPK para crecimiento/fructificación</x:v>
       </x:c>
       <x:c r="F13" s="11" t="str">
-        <x:v>Establecimiento</x:v>
+        <x:v>Evitar estrés hídrico; ajustar a tamaño del árbol</x:v>
       </x:c>
       <x:c r="G13" s="11" t="str">
-        <x:v>Reciente</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H13" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Según tamaño/edad; iniciar bajo</x:v>
       </x:c>
       <x:c r="I13" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>g/árbol o g/cama</x:v>
       </x:c>
       <x:c r="J13" s="11" t="str">
-        <x:v>Árbol joven</x:v>
+        <x:v>Vegetativo / postcosecha / prefloración según cultivo</x:v>
+      </x:c>
+      <x:c r="K13" s="11" t="n">
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
-        <x:v>ARB_DURAZNO_FRAILES</x:v>
+        <x:v>INS_CALCIO_BORO</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Calcio Boro</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono foliar</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>Durazno</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>🌸</x:v>
+        <x:v>Floración, cuajado y llenado temprano</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>No aplicar con calor fuerte; revisar mezcla</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Según etiqueta</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str">
-        <x:v>Poda</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="str"/>
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str">
+        <x:v>Floración / cuajado / llenado temprano</x:v>
+      </x:c>
+      <x:c r="K14" s="11" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
-        <x:v>ARB_MANGO_FRAILES</x:v>
+        <x:v>INS_MULTIMINERAL</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Multimineral</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono foliar</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>Mango peludo</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>🥭</x:v>
+        <x:v>Micronutrientes y apoyo general</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>Vegetativo</x:v>
+        <x:v>No mezclar sin validar compatibilidad</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>Bueno</x:v>
+        <x:v>Según etiqueta</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>ml/L</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str">
-        <x:v>Mango 10 años</x:v>
+        <x:v>Vegetativo / recuperación / soporte general</x:v>
+      </x:c>
+      <x:c r="K15" s="11" t="n">
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
-        <x:v>ARB_MAMON_CHINO_FRAILES</x:v>
+        <x:v>INS_FOLIAR_7_4_25</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Foliar 7-4-25</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>Frailes</x:v>
+        <x:v>Abono foliar</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>Mamón chino</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>🌳</x:v>
+        <x:v>Apoyo potasio/llenado</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>Recuperación</x:v>
+        <x:v>Evitar exceso; aplicar temprano/tarde</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>N/A</x:v>
+        <x:v>No</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
-        <x:v>Atención</x:v>
+        <x:v>Según etiqueta</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>ml/L</x:v>
       </x:c>
       <x:c r="J16" s="11" t="str">
-        <x:v>Afectación por viento</x:v>
+        <x:v>Llenado de fruto / desarrollo</x:v>
+      </x:c>
+      <x:c r="K16" s="11" t="n">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11" t="str">
+        <x:v>INS_PAS80</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>PAS-80</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>Coadyuvante</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>Adherente/dispersante para mezcla</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>Usar dosis indicada; no guardar mezcla vieja</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="H17" s="11" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I17" s="11" t="str">
+        <x:v>ml/L</x:v>
+      </x:c>
+      <x:c r="J17" s="11" t="str">
+        <x:v>Cuando la mezcla foliar lo requiera</x:v>
+      </x:c>
+      <x:c r="K17" s="11" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/FincaOS_Data.xlsx
+++ b/FincaOS_Data.xlsx
@@ -2,18 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="Ra43604a3c683445d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R973cb70a12954716"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="Rb7a45f49bd824085"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="R1509134335564d4c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R40779fc320d0450d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="Rc7bde972848c4607"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="R0ad2d651e18d4b60"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Camas" sheetId="8" r:id="R255ab1e13d80424d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="9" r:id="Ra859057da49d4c2c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arboles" sheetId="10" r:id="R3eecabfe036047e6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventosAgricolas" sheetId="11" r:id="Rfedd0e27ffb64ab5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HistorialResumen" sheetId="12" r:id="R25f0607c196541be"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="R9aad752ec9a94537"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R4227a49d0f304110"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="R9dd6a40f9cb141f9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="Rc586b383e229446b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R7b4481c77f444a7a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="Ra67245b67036419c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rec6e71267c9e4fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="8" r:id="R92d437cfcdcb4aa4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arboles" sheetId="9" r:id="R4f69b264cfb94400"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventosAgricolas" sheetId="10" r:id="Rcf79399ec49c4a7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -59,7 +57,7 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="14532D"/>
+        <x:fgColor rgb="0F3D25"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -407,7 +405,7 @@
       </x:c>
       <x:c r="B5" t="n">
         <x:f>COUNTIF(Unidades!E:E,"Activa")</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -416,7 +414,7 @@
       </x:c>
       <x:c r="B6" t="n">
         <x:f>COUNTIF(VistaCultivos!H:H,"CUL_DISPONIBLE")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -446,529 +444,25 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="23.420000076293945" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="11.84000015258789" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="15.069999694824219" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="15.069999694824219" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="4.440000057220459" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16.81999969482422" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="13.729999542236328" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="32.29999923706055" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="24" t="str">
-        <x:v>Arbol_ID</x:v>
-      </x:c>
-      <x:c r="B1" s="24" t="str">
-        <x:v>Finca_ID</x:v>
-      </x:c>
-      <x:c r="C1" s="24" t="str">
-        <x:v>Finca_Nombre</x:v>
-      </x:c>
-      <x:c r="D1" s="24" t="str">
-        <x:v>Arbol_Nombre</x:v>
-      </x:c>
-      <x:c r="E1" s="24" t="str">
-        <x:v>Especie</x:v>
-      </x:c>
-      <x:c r="F1" s="24" t="str">
-        <x:v>Icono</x:v>
-      </x:c>
-      <x:c r="G1" s="24" t="str">
-        <x:v>Estado_Fenologico</x:v>
-      </x:c>
-      <x:c r="H1" s="24" t="str">
-        <x:v>Fecha_Trasplante</x:v>
-      </x:c>
-      <x:c r="I1" s="24" t="str">
-        <x:v>Estado_Sanitario</x:v>
-      </x:c>
-      <x:c r="J1" s="24" t="str">
-        <x:v>Notas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="11" t="str">
-        <x:v>ARB_MANZANO_MORAVIA</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>Moravia</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>Manzano tico</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>Manzano</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
-        <x:v>🍎</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="str">
-        <x:v>Llenado de fruto</x:v>
-      </x:c>
-      <x:c r="H2" s="14"/>
-      <x:c r="I2" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J2" s="11" t="str">
-        <x:v>Poda y amarre previos; revisar chupones</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="11" t="str">
-        <x:v>ARB_GUAYABITA_MORAVIA</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="str">
-        <x:v>Moravia</x:v>
-      </x:c>
-      <x:c r="D3" s="11" t="str">
-        <x:v>Guayabita del Perú</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="str">
-        <x:v>Guayabita del Perú</x:v>
-      </x:c>
-      <x:c r="F3" s="11" t="str">
-        <x:v>🍈</x:v>
-      </x:c>
-      <x:c r="G3" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H3" s="14"/>
-      <x:c r="I3" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J3" s="11" t="str">
-        <x:v>Unidad distinta de Guayaba Frailes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="11" t="str">
-        <x:v>ARB_GUAYABA_FRAILES</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="str">
-        <x:v>Guayaba</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="str">
-        <x:v>Guayaba</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="str">
-        <x:v>🍐</x:v>
-      </x:c>
-      <x:c r="G4" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H4" s="14"/>
-      <x:c r="I4" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J4" s="11" t="str">
-        <x:v>Guayaba en Frailes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="11" t="str">
-        <x:v>ARB_GUANABANA_FRAILES</x:v>
-      </x:c>
-      <x:c r="B5" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C5" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>Guanábana</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>Guanábana</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
-        <x:v>🍈</x:v>
-      </x:c>
-      <x:c r="G5" s="11" t="str">
-        <x:v>Fructificación</x:v>
-      </x:c>
-      <x:c r="H5" s="14"/>
-      <x:c r="I5" s="11" t="str">
-        <x:v>Atención</x:v>
-      </x:c>
-      <x:c r="J5" s="11" t="str">
-        <x:v>Puntos negros en frutos</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>ARB_MANGO_FRAILES</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="str">
-        <x:v>Mango</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="str">
-        <x:v>Mango</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="str">
-        <x:v>🥭</x:v>
-      </x:c>
-      <x:c r="G6" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H6" s="14"/>
-      <x:c r="I6" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="str">
-        <x:v>Mango peludo adulto</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="11" t="str">
-        <x:v>ARB_ANONA_FRAILES</x:v>
-      </x:c>
-      <x:c r="B7" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C7" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>Anona</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>Anona</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="str">
-        <x:v>🍈</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="str">
-        <x:v>Estrés / recuperación</x:v>
-      </x:c>
-      <x:c r="H7" s="14"/>
-      <x:c r="I7" s="11" t="str">
-        <x:v>Atención</x:v>
-      </x:c>
-      <x:c r="J7" s="11" t="str">
-        <x:v>Historial de defoliación</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="11" t="str">
-        <x:v>ARB_NISPERO_FRAILES</x:v>
-      </x:c>
-      <x:c r="B8" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C8" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>Níspero</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>Níspero</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="str">
-        <x:v>🌳</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H8" s="14" t="n">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J8" s="11" t="str">
-        <x:v>Árbol joven</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>ARB_MANDARINA_FRAILES</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>Mandarina</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str">
-        <x:v>Mandarina</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="str">
-        <x:v>🍊</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H9" s="14" t="n">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="I9" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="str">
-        <x:v>Trasplante reciente en Frailes</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="11" t="str">
-        <x:v>ARB_LIMON_DULCE_FRAILES</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>Limón dulce</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="str">
-        <x:v>Limón</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="str">
-        <x:v>🍋</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H10" s="14" t="n">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="I10" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J10" s="11" t="str">
-        <x:v>Cítrico joven</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>ARB_NARANJA_FRAILES</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>Naranja</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="str">
-        <x:v>Naranja</x:v>
-      </x:c>
-      <x:c r="F11" s="11" t="str">
-        <x:v>🍊</x:v>
-      </x:c>
-      <x:c r="G11" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H11" s="14" t="n">
-        <x:v>45853</x:v>
-      </x:c>
-      <x:c r="I11" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J11" s="11" t="str">
-        <x:v>Cítrico joven</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11" t="str">
-        <x:v>ARB_CARAMBOLA_FRAILES</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="str">
-        <x:v>Frailes</x:v>
-      </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>Carambola</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="str">
-        <x:v>Carambola</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="str">
-        <x:v>⭐</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="H12" s="14"/>
-      <x:c r="I12" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-      <x:c r="J12" s="11" t="str"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="H13" s="18"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="H14" s="18"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="H15" s="18"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="H16" s="18"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="H17" s="18"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="H18" s="18"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="H19" s="18"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="H20" s="18"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="H21" s="18"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="H22" s="18"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="H23" s="18"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="H24" s="18"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="H25" s="18"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="H26" s="18"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="H27" s="18"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="H28" s="18"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="H29" s="18"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="H30" s="18"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="H31" s="18"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="H32" s="18"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="H33" s="18"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="H34" s="18"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="H35" s="18"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="H36" s="18"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="H37" s="18"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="H38" s="18"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="H39" s="18"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="H40" s="18"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="H41" s="18"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="H42" s="18"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="H43" s="18"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="H44" s="18"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="H45" s="18"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="H46" s="18"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="H47" s="18"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="H48" s="18"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="H49" s="18"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="H50" s="18"/>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
     <x:col min="1" max="1" width="8.210000038146973" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.09000015258789" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="11.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10.359999656677246" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="21.799999237060547" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="13.319999694824219" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="12.109999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="17.899999618530273" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.729999542236328" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="15.609999656677246" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="13.460000038146973" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="11.039999961853027" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="15.34000015258789" hidden="0" customWidth="1"/>
-    <x:col min="16" max="16" width="14.130000114440918" hidden="0" customWidth="1"/>
-    <x:col min="17" max="17" width="19.649999618530273" hidden="0" customWidth="1"/>
-    <x:col min="18" max="18" width="13.1899995803833" hidden="0" customWidth="1"/>
-    <x:col min="19" max="19" width="21.270000457763672" hidden="0" customWidth="1"/>
-    <x:col min="20" max="20" width="23.420000076293945" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.290000915527344" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="13.729999542236328" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="9.5600004196167" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="21.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="18.84000015258789" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="6.460000038146973" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.09000015258789" hidden="0" customWidth="1"/>
+    <x:col min="13" max="13" width="5.650000095367432" hidden="0" customWidth="1"/>
+    <x:col min="14" max="14" width="21.799999237060547" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="11.569999694824219" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="15.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="13.460000038146973" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="11.039999961853027" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="31.6299991607666" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -979,57 +473,54 @@
         <x:v>Tipo_Evento</x:v>
       </x:c>
       <x:c r="C1" s="24" t="str">
-        <x:v>Objeto_Tipo</x:v>
+        <x:v>ID_Insumo</x:v>
       </x:c>
       <x:c r="D1" s="24" t="str">
+        <x:v>Nombre_Insumo</x:v>
+      </x:c>
+      <x:c r="E1" s="24" t="str">
+        <x:v>Target_Tipo</x:v>
+      </x:c>
+      <x:c r="F1" s="24" t="str">
+        <x:v>Target_ID</x:v>
+      </x:c>
+      <x:c r="G1" s="24" t="str">
+        <x:v>Target_Label</x:v>
+      </x:c>
+      <x:c r="H1" s="24" t="str">
         <x:v>Finca_ID</x:v>
       </x:c>
-      <x:c r="E1" s="24" t="str">
-        <x:v>Cama_ID</x:v>
-      </x:c>
-      <x:c r="F1" s="24" t="str">
-        <x:v>Siembra_ID</x:v>
-      </x:c>
-      <x:c r="G1" s="24" t="str">
+      <x:c r="I1" s="24" t="str">
+        <x:v>Finca</x:v>
+      </x:c>
+      <x:c r="J1" s="24" t="str">
+        <x:v>Unidad_ID</x:v>
+      </x:c>
+      <x:c r="K1" s="24" t="str">
+        <x:v>Unidad</x:v>
+      </x:c>
+      <x:c r="L1" s="24" t="str">
+        <x:v>Cultivo_ID</x:v>
+      </x:c>
+      <x:c r="M1" s="24" t="str">
+        <x:v>Cultivo</x:v>
+      </x:c>
+      <x:c r="N1" s="24" t="str">
         <x:v>Arbol_ID</x:v>
       </x:c>
-      <x:c r="H1" s="24" t="str">
-        <x:v>Cultivo_Nombre</x:v>
-      </x:c>
-      <x:c r="I1" s="24" t="str">
-        <x:v>Arbol_Nombre</x:v>
-      </x:c>
-      <x:c r="J1" s="24" t="str">
-        <x:v>Insumo_ID</x:v>
-      </x:c>
-      <x:c r="K1" s="24" t="str">
-        <x:v>Insumo_Nombre</x:v>
-      </x:c>
-      <x:c r="L1" s="24" t="str">
+      <x:c r="O1" s="24" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="P1" s="24" t="str">
         <x:v>Fecha_Programada</x:v>
       </x:c>
-      <x:c r="M1" s="24" t="str">
+      <x:c r="Q1" s="24" t="str">
         <x:v>Fecha_Realizada</x:v>
       </x:c>
-      <x:c r="N1" s="24" t="str">
+      <x:c r="R1" s="24" t="str">
         <x:v>Estado</x:v>
       </x:c>
-      <x:c r="O1" s="24" t="str">
-        <x:v>Cantidad_Aplicada</x:v>
-      </x:c>
-      <x:c r="P1" s="24" t="str">
-        <x:v>Unidad_Cantidad</x:v>
-      </x:c>
-      <x:c r="Q1" s="24" t="str">
-        <x:v>Momento_Aplicacion</x:v>
-      </x:c>
-      <x:c r="R1" s="24" t="str">
-        <x:v>Frecuencia_Dias</x:v>
-      </x:c>
       <x:c r="S1" s="24" t="str">
-        <x:v>Proxima_Fecha_Calculada</x:v>
-      </x:c>
-      <x:c r="T1" s="24" t="str">
         <x:v>Notas</x:v>
       </x:c>
     </x:row>
@@ -1041,52 +532,49 @@
         <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
+        <x:v>INS_COBRE</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Cobre</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
         <x:v>Cultivo</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_01</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
         <x:v>SIE_FRA_003</x:v>
       </x:c>
-      <x:c r="G2" s="11" t="str"/>
+      <x:c r="G2" s="11" t="str">
+        <x:v>Cama Frailes 1 - Pepino</x:v>
+      </x:c>
       <x:c r="H2" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J2" s="11" t="str">
+        <x:v>UNI_FRA_CAMA_01</x:v>
+      </x:c>
+      <x:c r="K2" s="11" t="str">
+        <x:v>Cama Frailes 1</x:v>
+      </x:c>
+      <x:c r="L2" s="11" t="str">
+        <x:v>CUL_PEPINO</x:v>
+      </x:c>
+      <x:c r="M2" s="11" t="str">
         <x:v>Pepino</x:v>
       </x:c>
-      <x:c r="I2" s="11" t="str"/>
-      <x:c r="J2" s="11" t="str">
-        <x:v>INS_COBRE</x:v>
-      </x:c>
-      <x:c r="K2" s="11" t="str">
-        <x:v>Cobre</x:v>
-      </x:c>
-      <x:c r="L2" s="14"/>
-      <x:c r="M2" s="14" t="n">
+      <x:c r="N2" s="11" t="str"/>
+      <x:c r="O2" s="11" t="str"/>
+      <x:c r="P2" s="14"/>
+      <x:c r="Q2" s="14" t="n">
         <x:v>46152</x:v>
       </x:c>
-      <x:c r="N2" s="11" t="str">
-        <x:v>Completado</x:v>
-      </x:c>
-      <x:c r="O2" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="P2" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="Q2" s="11" t="str">
-        <x:v>Alta humedad</x:v>
-      </x:c>
-      <x:c r="R2" s="11" t="n">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="S2" s="14" t="n">
-        <x:v>46166</x:v>
-      </x:c>
-      <x:c r="T2" s="11" t="str">
-        <x:v>Control realizado en pepino</x:v>
+      <x:c r="R2" s="11" t="str">
+        <x:v>Pendiente</x:v>
+      </x:c>
+      <x:c r="S2" s="11" t="str">
+        <x:v>Ejemplo: control fitosanitario con cobre</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1097,50 +585,49 @@
         <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
+        <x:v>INS_MISTRAL</x:v>
+      </x:c>
+      <x:c r="D3" s="11" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="E3" s="11" t="str">
         <x:v>Cultivo</x:v>
-      </x:c>
-      <x:c r="D3" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E3" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_01</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
         <x:v>SIE_FRA_003</x:v>
       </x:c>
-      <x:c r="G3" s="11" t="str"/>
+      <x:c r="G3" s="11" t="str">
+        <x:v>Cama Frailes 1 - Pepino</x:v>
+      </x:c>
       <x:c r="H3" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I3" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J3" s="11" t="str">
+        <x:v>UNI_FRA_CAMA_01</x:v>
+      </x:c>
+      <x:c r="K3" s="11" t="str">
+        <x:v>Cama Frailes 1</x:v>
+      </x:c>
+      <x:c r="L3" s="11" t="str">
+        <x:v>CUL_PEPINO</x:v>
+      </x:c>
+      <x:c r="M3" s="11" t="str">
         <x:v>Pepino</x:v>
       </x:c>
-      <x:c r="I3" s="11" t="str"/>
-      <x:c r="J3" s="11" t="str">
-        <x:v>INS_MISTRAL</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="str">
-        <x:v>Mistral</x:v>
-      </x:c>
-      <x:c r="L3" s="14" t="n">
+      <x:c r="N3" s="11" t="str"/>
+      <x:c r="O3" s="11" t="str"/>
+      <x:c r="P3" s="14" t="n">
         <x:v>46188</x:v>
       </x:c>
-      <x:c r="M3" s="14"/>
-      <x:c r="N3" s="11" t="str">
+      <x:c r="Q3" s="14"/>
+      <x:c r="R3" s="11" t="str">
         <x:v>No empezado</x:v>
       </x:c>
-      <x:c r="O3" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="P3" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="Q3" s="11" t="str">
-        <x:v>Preventivo</x:v>
-      </x:c>
-      <x:c r="R3" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="S3" s="14"/>
-      <x:c r="T3" s="11" t="str">
-        <x:v>Programado para pepino</x:v>
+      <x:c r="S3" s="11" t="str">
+        <x:v>Próximo control fitosanitario</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1151,50 +638,45 @@
         <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Árbol</x:v>
+        <x:v>INS_CAL_DOLOMITA</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E4" s="11" t="str"/>
-      <x:c r="F4" s="11" t="str"/>
+        <x:v>Cal Dolomita</x:v>
+      </x:c>
+      <x:c r="E4" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
       <x:c r="G4" s="11" t="str">
+        <x:v>Guayaba - Frailes</x:v>
+      </x:c>
+      <x:c r="H4" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I4" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J4" s="11" t="str"/>
+      <x:c r="K4" s="11" t="str"/>
+      <x:c r="L4" s="11" t="str"/>
+      <x:c r="M4" s="11" t="str"/>
+      <x:c r="N4" s="11" t="str">
         <x:v>ARB_GUAYABA_FRAILES</x:v>
       </x:c>
-      <x:c r="H4" s="11" t="str"/>
-      <x:c r="I4" s="11" t="str">
+      <x:c r="O4" s="11" t="str">
         <x:v>Guayaba</x:v>
       </x:c>
-      <x:c r="J4" s="11" t="str">
-        <x:v>INS_CAL_DOLOMITA</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="str">
-        <x:v>Cal dolomita</x:v>
-      </x:c>
-      <x:c r="L4" s="14"/>
-      <x:c r="M4" s="14" t="n">
+      <x:c r="P4" s="14"/>
+      <x:c r="Q4" s="14" t="n">
         <x:v>46172</x:v>
       </x:c>
-      <x:c r="N4" s="11" t="str">
+      <x:c r="R4" s="11" t="str">
         <x:v>Completado</x:v>
       </x:c>
-      <x:c r="O4" s="11" t="str">
-        <x:v>Según tamaño</x:v>
-      </x:c>
-      <x:c r="P4" s="11" t="str">
-        <x:v>kg/árbol</x:v>
-      </x:c>
-      <x:c r="Q4" s="11" t="str">
-        <x:v>Vegetativo / enmienda</x:v>
-      </x:c>
-      <x:c r="R4" s="11" t="n">
-        <x:v>180</x:v>
-      </x:c>
-      <x:c r="S4" s="14" t="n">
-        <x:v>46352</x:v>
-      </x:c>
-      <x:c r="T4" s="11" t="str">
-        <x:v>Aplicación de corona</x:v>
+      <x:c r="S4" s="11" t="str">
+        <x:v>Aplicación de cal dolomita</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1205,50 +687,45 @@
         <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Árbol</x:v>
+        <x:v>INS_YARAMILA</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str"/>
-      <x:c r="F5" s="11" t="str"/>
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
+      </x:c>
       <x:c r="G5" s="11" t="str">
+        <x:v>Guayaba - Frailes</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J5" s="11" t="str"/>
+      <x:c r="K5" s="11" t="str"/>
+      <x:c r="L5" s="11" t="str"/>
+      <x:c r="M5" s="11" t="str"/>
+      <x:c r="N5" s="11" t="str">
         <x:v>ARB_GUAYABA_FRAILES</x:v>
       </x:c>
-      <x:c r="H5" s="11" t="str"/>
-      <x:c r="I5" s="11" t="str">
+      <x:c r="O5" s="11" t="str">
         <x:v>Guayaba</x:v>
       </x:c>
-      <x:c r="J5" s="11" t="str">
-        <x:v>INS_YARAMILA</x:v>
-      </x:c>
-      <x:c r="K5" s="11" t="str">
-        <x:v>YaraMila</x:v>
-      </x:c>
-      <x:c r="L5" s="14"/>
-      <x:c r="M5" s="14" t="n">
+      <x:c r="P5" s="14"/>
+      <x:c r="Q5" s="14" t="n">
         <x:v>46179</x:v>
       </x:c>
-      <x:c r="N5" s="11" t="str">
+      <x:c r="R5" s="11" t="str">
         <x:v>Completado</x:v>
       </x:c>
-      <x:c r="O5" s="11" t="str">
-        <x:v>Bajo según tamaño</x:v>
-      </x:c>
-      <x:c r="P5" s="11" t="str">
-        <x:v>g/árbol</x:v>
-      </x:c>
-      <x:c r="Q5" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="R5" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="S5" s="14" t="n">
-        <x:v>46239</x:v>
-      </x:c>
-      <x:c r="T5" s="11" t="str">
-        <x:v>Fertilización de tierra</x:v>
+      <x:c r="S5" s="11" t="str">
+        <x:v>Aplicación de YaraMila</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1259,48 +736,45 @@
         <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Árbol</x:v>
+        <x:v>INS_MISTRAL</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E6" s="11" t="str"/>
-      <x:c r="F6" s="11" t="str"/>
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="E6" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F6" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
       <x:c r="G6" s="11" t="str">
+        <x:v>Mango peludo - Frailes</x:v>
+      </x:c>
+      <x:c r="H6" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="I6" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="J6" s="11" t="str"/>
+      <x:c r="K6" s="11" t="str"/>
+      <x:c r="L6" s="11" t="str"/>
+      <x:c r="M6" s="11" t="str"/>
+      <x:c r="N6" s="11" t="str">
         <x:v>ARB_MANGO_FRAILES</x:v>
       </x:c>
-      <x:c r="H6" s="11" t="str"/>
-      <x:c r="I6" s="11" t="str">
-        <x:v>Mango</x:v>
-      </x:c>
-      <x:c r="J6" s="11" t="str">
-        <x:v>INS_MISTRAL</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="str">
-        <x:v>Mistral</x:v>
-      </x:c>
-      <x:c r="L6" s="14" t="n">
+      <x:c r="O6" s="11" t="str">
+        <x:v>Mango peludo</x:v>
+      </x:c>
+      <x:c r="P6" s="14" t="n">
         <x:v>46264</x:v>
       </x:c>
-      <x:c r="M6" s="14"/>
-      <x:c r="N6" s="11" t="str">
+      <x:c r="Q6" s="14"/>
+      <x:c r="R6" s="11" t="str">
         <x:v>No empezado</x:v>
       </x:c>
-      <x:c r="O6" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="P6" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="Q6" s="11" t="str">
-        <x:v>Preventivo</x:v>
-      </x:c>
-      <x:c r="R6" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="S6" s="14"/>
-      <x:c r="T6" s="11" t="str">
-        <x:v>Control programado</x:v>
+      <x:c r="S6" s="11" t="str">
+        <x:v>Control fitosanitario programado</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1310,40 +784,41 @@
       <x:c r="B7" s="11" t="str">
         <x:v>Poda</x:v>
       </x:c>
-      <x:c r="C7" s="11" t="str">
-        <x:v>Árbol</x:v>
-      </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="str"/>
-      <x:c r="F7" s="11" t="str"/>
+      <x:c r="C7" s="11" t="str"/>
+      <x:c r="D7" s="11" t="str"/>
+      <x:c r="E7" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
       <x:c r="G7" s="11" t="str">
-        <x:v>ARB_MANGO_FRAILES</x:v>
-      </x:c>
-      <x:c r="H7" s="11" t="str"/>
+        <x:v>Mango peludo - Frailes</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
       <x:c r="I7" s="11" t="str">
-        <x:v>Mango</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="J7" s="11" t="str"/>
       <x:c r="K7" s="11" t="str"/>
-      <x:c r="L7" s="14" t="n">
+      <x:c r="L7" s="11" t="str"/>
+      <x:c r="M7" s="11" t="str"/>
+      <x:c r="N7" s="11" t="str">
+        <x:v>ARB_MANGO_FRAILES</x:v>
+      </x:c>
+      <x:c r="O7" s="11" t="str">
+        <x:v>Mango peludo</x:v>
+      </x:c>
+      <x:c r="P7" s="14" t="n">
         <x:v>46295</x:v>
       </x:c>
-      <x:c r="M7" s="14"/>
-      <x:c r="N7" s="11" t="str">
+      <x:c r="Q7" s="14"/>
+      <x:c r="R7" s="11" t="str">
         <x:v>No empezado</x:v>
       </x:c>
-      <x:c r="O7" s="11" t="str"/>
-      <x:c r="P7" s="11" t="str"/>
-      <x:c r="Q7" s="11" t="str">
-        <x:v>Postcosecha / formación</x:v>
-      </x:c>
-      <x:c r="R7" s="11" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S7" s="14"/>
-      <x:c r="T7" s="11" t="str">
+      <x:c r="S7" s="11" t="str">
         <x:v>Poda programada</x:v>
       </x:c>
     </x:row>
@@ -1352,1181 +827,417 @@
         <x:v>EVT_007</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Abono foliar</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Árbol</x:v>
+        <x:v>INS_CALCIO_BORO</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
+        <x:v>Calcio Boro</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>Manzano tico - Moravia</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
         <x:v>FIN_MORAVIA</x:v>
       </x:c>
-      <x:c r="E8" s="11" t="str"/>
-      <x:c r="F8" s="11" t="str"/>
-      <x:c r="G8" s="11" t="str">
+      <x:c r="I8" s="11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="J8" s="11" t="str"/>
+      <x:c r="K8" s="11" t="str"/>
+      <x:c r="L8" s="11" t="str"/>
+      <x:c r="M8" s="11" t="str"/>
+      <x:c r="N8" s="11" t="str">
         <x:v>ARB_MANZANO_MORAVIA</x:v>
       </x:c>
-      <x:c r="H8" s="11" t="str"/>
-      <x:c r="I8" s="11" t="str">
+      <x:c r="O8" s="11" t="str">
         <x:v>Manzano tico</x:v>
       </x:c>
-      <x:c r="J8" s="11" t="str">
-        <x:v>INS_MISTRAL</x:v>
-      </x:c>
-      <x:c r="K8" s="11" t="str">
-        <x:v>Mistral</x:v>
-      </x:c>
-      <x:c r="L8" s="14"/>
-      <x:c r="M8" s="14" t="n">
-        <x:v>46181</x:v>
-      </x:c>
-      <x:c r="N8" s="11" t="str">
-        <x:v>Completado</x:v>
-      </x:c>
-      <x:c r="O8" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="P8" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="Q8" s="11" t="str">
-        <x:v>Llenado / prevención</x:v>
-      </x:c>
-      <x:c r="R8" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="S8" s="14" t="n">
-        <x:v>46196</x:v>
-      </x:c>
-      <x:c r="T8" s="11" t="str">
-        <x:v>Control aplicado hoy</x:v>
+      <x:c r="P8" s="14" t="n">
+        <x:v>46193</x:v>
+      </x:c>
+      <x:c r="Q8" s="14"/>
+      <x:c r="R8" s="11" t="str">
+        <x:v>No empezado</x:v>
+      </x:c>
+      <x:c r="S8" s="11" t="str">
+        <x:v>Apoyo foliar en llenado</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>EVT_008</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="C9" s="11" t="str">
-        <x:v>Árbol</x:v>
-      </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str"/>
-      <x:c r="F9" s="11" t="str"/>
-      <x:c r="G9" s="11" t="str">
-        <x:v>ARB_MANZANO_MORAVIA</x:v>
-      </x:c>
-      <x:c r="H9" s="11" t="str"/>
-      <x:c r="I9" s="11" t="str">
-        <x:v>Manzano tico</x:v>
-      </x:c>
-      <x:c r="J9" s="11" t="str">
-        <x:v>INS_YARAMILA</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="str">
-        <x:v>YaraMila</x:v>
-      </x:c>
-      <x:c r="L9" s="14"/>
-      <x:c r="M9" s="14" t="n">
-        <x:v>46127</x:v>
-      </x:c>
-      <x:c r="N9" s="11" t="str">
-        <x:v>Completado</x:v>
-      </x:c>
-      <x:c r="O9" s="11" t="str">
-        <x:v>Bajo según tamaño</x:v>
-      </x:c>
-      <x:c r="P9" s="11" t="str">
-        <x:v>g/árbol</x:v>
-      </x:c>
-      <x:c r="Q9" s="11" t="str">
-        <x:v>Vegetativo</x:v>
-      </x:c>
-      <x:c r="R9" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="S9" s="14" t="n">
-        <x:v>46187</x:v>
-      </x:c>
-      <x:c r="T9" s="11" t="str">
-        <x:v>Fertilización previa</x:v>
-      </x:c>
+      <x:c r="P9" s="18"/>
+      <x:c r="Q9" s="18"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="11" t="str">
-        <x:v>EVT_009</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="C10" s="11" t="str">
-        <x:v>Árbol</x:v>
-      </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="str"/>
-      <x:c r="F10" s="11" t="str"/>
-      <x:c r="G10" s="11" t="str">
-        <x:v>ARB_MANZANO_MORAVIA</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="str"/>
-      <x:c r="I10" s="11" t="str">
-        <x:v>Manzano tico</x:v>
-      </x:c>
-      <x:c r="J10" s="11" t="str">
-        <x:v>INS_YARAMILA</x:v>
-      </x:c>
-      <x:c r="K10" s="11" t="str">
-        <x:v>YaraMila</x:v>
-      </x:c>
-      <x:c r="L10" s="14"/>
-      <x:c r="M10" s="14" t="n">
-        <x:v>46174</x:v>
-      </x:c>
-      <x:c r="N10" s="11" t="str">
-        <x:v>Completado</x:v>
-      </x:c>
-      <x:c r="O10" s="11" t="str">
-        <x:v>Bajo según tamaño</x:v>
-      </x:c>
-      <x:c r="P10" s="11" t="str">
-        <x:v>g/árbol</x:v>
-      </x:c>
-      <x:c r="Q10" s="11" t="str">
-        <x:v>Llenado</x:v>
-      </x:c>
-      <x:c r="R10" s="11" t="n">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="S10" s="14" t="n">
-        <x:v>46234</x:v>
-      </x:c>
-      <x:c r="T10" s="11" t="str">
-        <x:v>Refuerzo de tierra</x:v>
-      </x:c>
+      <x:c r="P10" s="18"/>
+      <x:c r="Q10" s="18"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>EVT_010</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
-      </x:c>
-      <x:c r="C11" s="11" t="str">
-        <x:v>Árbol</x:v>
-      </x:c>
-      <x:c r="D11" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E11" s="11" t="str"/>
-      <x:c r="F11" s="11" t="str"/>
-      <x:c r="G11" s="11" t="str">
-        <x:v>ARB_GUAYABA_FRAILES</x:v>
-      </x:c>
-      <x:c r="H11" s="11" t="str"/>
-      <x:c r="I11" s="11" t="str">
-        <x:v>Guayaba</x:v>
-      </x:c>
-      <x:c r="J11" s="11" t="str">
-        <x:v>INS_NEEM</x:v>
-      </x:c>
-      <x:c r="K11" s="11" t="str">
-        <x:v>Neem</x:v>
-      </x:c>
-      <x:c r="L11" s="14" t="n">
-        <x:v>46193</x:v>
-      </x:c>
-      <x:c r="M11" s="14"/>
-      <x:c r="N11" s="11" t="str">
-        <x:v>Pendiente</x:v>
-      </x:c>
-      <x:c r="O11" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="P11" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="Q11" s="11" t="str">
-        <x:v>Preventivo</x:v>
-      </x:c>
-      <x:c r="R11" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S11" s="14"/>
-      <x:c r="T11" s="11" t="str">
-        <x:v>Pendiente en guayaba</x:v>
-      </x:c>
+      <x:c r="P11" s="18"/>
+      <x:c r="Q11" s="18"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="11" t="str">
-        <x:v>EVT_011</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
-      </x:c>
-      <x:c r="C12" s="11" t="str">
-        <x:v>Cultivo</x:v>
-      </x:c>
-      <x:c r="D12" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E12" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_05</x:v>
-      </x:c>
-      <x:c r="F12" s="11" t="str">
-        <x:v>SIE_FRA_014</x:v>
-      </x:c>
-      <x:c r="G12" s="11" t="str"/>
-      <x:c r="H12" s="11" t="str">
-        <x:v>Arúgula</x:v>
-      </x:c>
-      <x:c r="I12" s="11" t="str"/>
-      <x:c r="J12" s="11" t="str">
-        <x:v>INS_JABON_POTASICO</x:v>
-      </x:c>
-      <x:c r="K12" s="11" t="str">
-        <x:v>Jabón potásico</x:v>
-      </x:c>
-      <x:c r="L12" s="14" t="n">
-        <x:v>46185</x:v>
-      </x:c>
-      <x:c r="M12" s="14"/>
-      <x:c r="N12" s="11" t="str">
-        <x:v>Pendiente</x:v>
-      </x:c>
-      <x:c r="O12" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="P12" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="Q12" s="11" t="str">
-        <x:v>Presencia plaga blanda</x:v>
-      </x:c>
-      <x:c r="R12" s="11" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="S12" s="14"/>
-      <x:c r="T12" s="11" t="str">
-        <x:v>Control pendiente en arúgula</x:v>
-      </x:c>
+      <x:c r="P12" s="18"/>
+      <x:c r="Q12" s="18"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="11" t="str">
-        <x:v>EVT_012</x:v>
-      </x:c>
-      <x:c r="B13" s="11" t="str">
-        <x:v>Abono foliar</x:v>
-      </x:c>
-      <x:c r="C13" s="11" t="str">
-        <x:v>Cultivo</x:v>
-      </x:c>
-      <x:c r="D13" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_02</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="str">
-        <x:v>SIE_FRA_007</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="str"/>
-      <x:c r="H13" s="11" t="str">
-        <x:v>Tomate cherry</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="str"/>
-      <x:c r="J13" s="11" t="str">
-        <x:v>INS_CALCIO_BORO</x:v>
-      </x:c>
-      <x:c r="K13" s="11" t="str">
-        <x:v>Calcio Boro</x:v>
-      </x:c>
-      <x:c r="L13" s="14" t="n">
-        <x:v>46191</x:v>
-      </x:c>
-      <x:c r="M13" s="14"/>
-      <x:c r="N13" s="11" t="str">
-        <x:v>No empezado</x:v>
-      </x:c>
-      <x:c r="O13" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="P13" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="Q13" s="11" t="str">
-        <x:v>Floración</x:v>
-      </x:c>
-      <x:c r="R13" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="S13" s="14"/>
-      <x:c r="T13" s="11" t="str">
-        <x:v>Apoyo floración/cuaje</x:v>
-      </x:c>
+      <x:c r="P13" s="18"/>
+      <x:c r="Q13" s="18"/>
     </x:row>
     <x:row r="14">
-      <x:c r="L14" s="18"/>
-      <x:c r="M14" s="18"/>
-      <x:c r="S14" s="18"/>
+      <x:c r="P14" s="18"/>
+      <x:c r="Q14" s="18"/>
     </x:row>
     <x:row r="15">
-      <x:c r="L15" s="18"/>
-      <x:c r="M15" s="18"/>
-      <x:c r="S15" s="18"/>
+      <x:c r="P15" s="18"/>
+      <x:c r="Q15" s="18"/>
     </x:row>
     <x:row r="16">
-      <x:c r="L16" s="18"/>
-      <x:c r="M16" s="18"/>
-      <x:c r="S16" s="18"/>
+      <x:c r="P16" s="18"/>
+      <x:c r="Q16" s="18"/>
     </x:row>
     <x:row r="17">
-      <x:c r="L17" s="18"/>
-      <x:c r="M17" s="18"/>
-      <x:c r="S17" s="18"/>
+      <x:c r="P17" s="18"/>
+      <x:c r="Q17" s="18"/>
     </x:row>
     <x:row r="18">
-      <x:c r="L18" s="18"/>
-      <x:c r="M18" s="18"/>
-      <x:c r="S18" s="18"/>
+      <x:c r="P18" s="18"/>
+      <x:c r="Q18" s="18"/>
     </x:row>
     <x:row r="19">
-      <x:c r="L19" s="18"/>
-      <x:c r="M19" s="18"/>
-      <x:c r="S19" s="18"/>
+      <x:c r="P19" s="18"/>
+      <x:c r="Q19" s="18"/>
     </x:row>
     <x:row r="20">
-      <x:c r="L20" s="18"/>
-      <x:c r="M20" s="18"/>
-      <x:c r="S20" s="18"/>
+      <x:c r="P20" s="18"/>
+      <x:c r="Q20" s="18"/>
     </x:row>
     <x:row r="21">
-      <x:c r="L21" s="18"/>
-      <x:c r="M21" s="18"/>
-      <x:c r="S21" s="18"/>
+      <x:c r="P21" s="18"/>
+      <x:c r="Q21" s="18"/>
     </x:row>
     <x:row r="22">
-      <x:c r="L22" s="18"/>
-      <x:c r="M22" s="18"/>
-      <x:c r="S22" s="18"/>
+      <x:c r="P22" s="18"/>
+      <x:c r="Q22" s="18"/>
     </x:row>
     <x:row r="23">
-      <x:c r="L23" s="18"/>
-      <x:c r="M23" s="18"/>
-      <x:c r="S23" s="18"/>
+      <x:c r="P23" s="18"/>
+      <x:c r="Q23" s="18"/>
     </x:row>
     <x:row r="24">
-      <x:c r="L24" s="18"/>
-      <x:c r="M24" s="18"/>
-      <x:c r="S24" s="18"/>
+      <x:c r="P24" s="18"/>
+      <x:c r="Q24" s="18"/>
     </x:row>
     <x:row r="25">
-      <x:c r="L25" s="18"/>
-      <x:c r="M25" s="18"/>
-      <x:c r="S25" s="18"/>
+      <x:c r="P25" s="18"/>
+      <x:c r="Q25" s="18"/>
     </x:row>
     <x:row r="26">
-      <x:c r="L26" s="18"/>
-      <x:c r="M26" s="18"/>
-      <x:c r="S26" s="18"/>
+      <x:c r="P26" s="18"/>
+      <x:c r="Q26" s="18"/>
     </x:row>
     <x:row r="27">
-      <x:c r="L27" s="18"/>
-      <x:c r="M27" s="18"/>
-      <x:c r="S27" s="18"/>
+      <x:c r="P27" s="18"/>
+      <x:c r="Q27" s="18"/>
     </x:row>
     <x:row r="28">
-      <x:c r="L28" s="18"/>
-      <x:c r="M28" s="18"/>
-      <x:c r="S28" s="18"/>
+      <x:c r="P28" s="18"/>
+      <x:c r="Q28" s="18"/>
     </x:row>
     <x:row r="29">
-      <x:c r="L29" s="18"/>
-      <x:c r="M29" s="18"/>
-      <x:c r="S29" s="18"/>
+      <x:c r="P29" s="18"/>
+      <x:c r="Q29" s="18"/>
     </x:row>
     <x:row r="30">
-      <x:c r="L30" s="18"/>
-      <x:c r="M30" s="18"/>
-      <x:c r="S30" s="18"/>
+      <x:c r="P30" s="18"/>
+      <x:c r="Q30" s="18"/>
     </x:row>
     <x:row r="31">
-      <x:c r="L31" s="18"/>
-      <x:c r="M31" s="18"/>
-      <x:c r="S31" s="18"/>
+      <x:c r="P31" s="18"/>
+      <x:c r="Q31" s="18"/>
     </x:row>
     <x:row r="32">
-      <x:c r="L32" s="18"/>
-      <x:c r="M32" s="18"/>
-      <x:c r="S32" s="18"/>
+      <x:c r="P32" s="18"/>
+      <x:c r="Q32" s="18"/>
     </x:row>
     <x:row r="33">
-      <x:c r="L33" s="18"/>
-      <x:c r="M33" s="18"/>
-      <x:c r="S33" s="18"/>
+      <x:c r="P33" s="18"/>
+      <x:c r="Q33" s="18"/>
     </x:row>
     <x:row r="34">
-      <x:c r="L34" s="18"/>
-      <x:c r="M34" s="18"/>
-      <x:c r="S34" s="18"/>
+      <x:c r="P34" s="18"/>
+      <x:c r="Q34" s="18"/>
     </x:row>
     <x:row r="35">
-      <x:c r="L35" s="18"/>
-      <x:c r="M35" s="18"/>
-      <x:c r="S35" s="18"/>
+      <x:c r="P35" s="18"/>
+      <x:c r="Q35" s="18"/>
     </x:row>
     <x:row r="36">
-      <x:c r="L36" s="18"/>
-      <x:c r="M36" s="18"/>
-      <x:c r="S36" s="18"/>
+      <x:c r="P36" s="18"/>
+      <x:c r="Q36" s="18"/>
     </x:row>
     <x:row r="37">
-      <x:c r="L37" s="18"/>
-      <x:c r="M37" s="18"/>
-      <x:c r="S37" s="18"/>
+      <x:c r="P37" s="18"/>
+      <x:c r="Q37" s="18"/>
     </x:row>
     <x:row r="38">
-      <x:c r="L38" s="18"/>
-      <x:c r="M38" s="18"/>
-      <x:c r="S38" s="18"/>
+      <x:c r="P38" s="18"/>
+      <x:c r="Q38" s="18"/>
     </x:row>
     <x:row r="39">
-      <x:c r="L39" s="18"/>
-      <x:c r="M39" s="18"/>
-      <x:c r="S39" s="18"/>
+      <x:c r="P39" s="18"/>
+      <x:c r="Q39" s="18"/>
     </x:row>
     <x:row r="40">
-      <x:c r="L40" s="18"/>
-      <x:c r="M40" s="18"/>
-      <x:c r="S40" s="18"/>
+      <x:c r="P40" s="18"/>
+      <x:c r="Q40" s="18"/>
     </x:row>
     <x:row r="41">
-      <x:c r="L41" s="18"/>
-      <x:c r="M41" s="18"/>
-      <x:c r="S41" s="18"/>
+      <x:c r="P41" s="18"/>
+      <x:c r="Q41" s="18"/>
     </x:row>
     <x:row r="42">
-      <x:c r="L42" s="18"/>
-      <x:c r="M42" s="18"/>
-      <x:c r="S42" s="18"/>
+      <x:c r="P42" s="18"/>
+      <x:c r="Q42" s="18"/>
     </x:row>
     <x:row r="43">
-      <x:c r="L43" s="18"/>
-      <x:c r="M43" s="18"/>
-      <x:c r="S43" s="18"/>
+      <x:c r="P43" s="18"/>
+      <x:c r="Q43" s="18"/>
     </x:row>
     <x:row r="44">
-      <x:c r="L44" s="18"/>
-      <x:c r="M44" s="18"/>
-      <x:c r="S44" s="18"/>
+      <x:c r="P44" s="18"/>
+      <x:c r="Q44" s="18"/>
     </x:row>
     <x:row r="45">
-      <x:c r="L45" s="18"/>
-      <x:c r="M45" s="18"/>
-      <x:c r="S45" s="18"/>
+      <x:c r="P45" s="18"/>
+      <x:c r="Q45" s="18"/>
     </x:row>
     <x:row r="46">
-      <x:c r="L46" s="18"/>
-      <x:c r="M46" s="18"/>
-      <x:c r="S46" s="18"/>
+      <x:c r="P46" s="18"/>
+      <x:c r="Q46" s="18"/>
     </x:row>
     <x:row r="47">
-      <x:c r="L47" s="18"/>
-      <x:c r="M47" s="18"/>
-      <x:c r="S47" s="18"/>
+      <x:c r="P47" s="18"/>
+      <x:c r="Q47" s="18"/>
     </x:row>
     <x:row r="48">
-      <x:c r="L48" s="18"/>
-      <x:c r="M48" s="18"/>
-      <x:c r="S48" s="18"/>
+      <x:c r="P48" s="18"/>
+      <x:c r="Q48" s="18"/>
     </x:row>
     <x:row r="49">
-      <x:c r="L49" s="18"/>
-      <x:c r="M49" s="18"/>
-      <x:c r="S49" s="18"/>
+      <x:c r="P49" s="18"/>
+      <x:c r="Q49" s="18"/>
     </x:row>
     <x:row r="50">
-      <x:c r="L50" s="18"/>
-      <x:c r="M50" s="18"/>
-      <x:c r="S50" s="18"/>
+      <x:c r="P50" s="18"/>
+      <x:c r="Q50" s="18"/>
     </x:row>
     <x:row r="51">
-      <x:c r="L51" s="18"/>
-      <x:c r="M51" s="18"/>
-      <x:c r="S51" s="18"/>
+      <x:c r="P51" s="18"/>
+      <x:c r="Q51" s="18"/>
     </x:row>
     <x:row r="52">
-      <x:c r="L52" s="18"/>
-      <x:c r="M52" s="18"/>
-      <x:c r="S52" s="18"/>
+      <x:c r="P52" s="18"/>
+      <x:c r="Q52" s="18"/>
     </x:row>
     <x:row r="53">
-      <x:c r="L53" s="18"/>
-      <x:c r="M53" s="18"/>
-      <x:c r="S53" s="18"/>
+      <x:c r="P53" s="18"/>
+      <x:c r="Q53" s="18"/>
     </x:row>
     <x:row r="54">
-      <x:c r="L54" s="18"/>
-      <x:c r="M54" s="18"/>
-      <x:c r="S54" s="18"/>
+      <x:c r="P54" s="18"/>
+      <x:c r="Q54" s="18"/>
     </x:row>
     <x:row r="55">
-      <x:c r="L55" s="18"/>
-      <x:c r="M55" s="18"/>
-      <x:c r="S55" s="18"/>
+      <x:c r="P55" s="18"/>
+      <x:c r="Q55" s="18"/>
     </x:row>
     <x:row r="56">
-      <x:c r="L56" s="18"/>
-      <x:c r="M56" s="18"/>
-      <x:c r="S56" s="18"/>
+      <x:c r="P56" s="18"/>
+      <x:c r="Q56" s="18"/>
     </x:row>
     <x:row r="57">
-      <x:c r="L57" s="18"/>
-      <x:c r="M57" s="18"/>
-      <x:c r="S57" s="18"/>
+      <x:c r="P57" s="18"/>
+      <x:c r="Q57" s="18"/>
     </x:row>
     <x:row r="58">
-      <x:c r="L58" s="18"/>
-      <x:c r="M58" s="18"/>
-      <x:c r="S58" s="18"/>
+      <x:c r="P58" s="18"/>
+      <x:c r="Q58" s="18"/>
     </x:row>
     <x:row r="59">
-      <x:c r="L59" s="18"/>
-      <x:c r="M59" s="18"/>
-      <x:c r="S59" s="18"/>
+      <x:c r="P59" s="18"/>
+      <x:c r="Q59" s="18"/>
     </x:row>
     <x:row r="60">
-      <x:c r="L60" s="18"/>
-      <x:c r="M60" s="18"/>
-      <x:c r="S60" s="18"/>
+      <x:c r="P60" s="18"/>
+      <x:c r="Q60" s="18"/>
     </x:row>
     <x:row r="61">
-      <x:c r="L61" s="18"/>
-      <x:c r="M61" s="18"/>
-      <x:c r="S61" s="18"/>
+      <x:c r="P61" s="18"/>
+      <x:c r="Q61" s="18"/>
     </x:row>
     <x:row r="62">
-      <x:c r="L62" s="18"/>
-      <x:c r="M62" s="18"/>
-      <x:c r="S62" s="18"/>
+      <x:c r="P62" s="18"/>
+      <x:c r="Q62" s="18"/>
     </x:row>
     <x:row r="63">
-      <x:c r="L63" s="18"/>
-      <x:c r="M63" s="18"/>
-      <x:c r="S63" s="18"/>
+      <x:c r="P63" s="18"/>
+      <x:c r="Q63" s="18"/>
     </x:row>
     <x:row r="64">
-      <x:c r="L64" s="18"/>
-      <x:c r="M64" s="18"/>
-      <x:c r="S64" s="18"/>
+      <x:c r="P64" s="18"/>
+      <x:c r="Q64" s="18"/>
     </x:row>
     <x:row r="65">
-      <x:c r="L65" s="18"/>
-      <x:c r="M65" s="18"/>
-      <x:c r="S65" s="18"/>
+      <x:c r="P65" s="18"/>
+      <x:c r="Q65" s="18"/>
     </x:row>
     <x:row r="66">
-      <x:c r="L66" s="18"/>
-      <x:c r="M66" s="18"/>
-      <x:c r="S66" s="18"/>
+      <x:c r="P66" s="18"/>
+      <x:c r="Q66" s="18"/>
     </x:row>
     <x:row r="67">
-      <x:c r="L67" s="18"/>
-      <x:c r="M67" s="18"/>
-      <x:c r="S67" s="18"/>
+      <x:c r="P67" s="18"/>
+      <x:c r="Q67" s="18"/>
     </x:row>
     <x:row r="68">
-      <x:c r="L68" s="18"/>
-      <x:c r="M68" s="18"/>
-      <x:c r="S68" s="18"/>
+      <x:c r="P68" s="18"/>
+      <x:c r="Q68" s="18"/>
     </x:row>
     <x:row r="69">
-      <x:c r="L69" s="18"/>
-      <x:c r="M69" s="18"/>
-      <x:c r="S69" s="18"/>
+      <x:c r="P69" s="18"/>
+      <x:c r="Q69" s="18"/>
     </x:row>
     <x:row r="70">
-      <x:c r="L70" s="18"/>
-      <x:c r="M70" s="18"/>
-      <x:c r="S70" s="18"/>
+      <x:c r="P70" s="18"/>
+      <x:c r="Q70" s="18"/>
     </x:row>
     <x:row r="71">
-      <x:c r="L71" s="18"/>
-      <x:c r="M71" s="18"/>
-      <x:c r="S71" s="18"/>
+      <x:c r="P71" s="18"/>
+      <x:c r="Q71" s="18"/>
     </x:row>
     <x:row r="72">
-      <x:c r="L72" s="18"/>
-      <x:c r="M72" s="18"/>
-      <x:c r="S72" s="18"/>
+      <x:c r="P72" s="18"/>
+      <x:c r="Q72" s="18"/>
     </x:row>
     <x:row r="73">
-      <x:c r="L73" s="18"/>
-      <x:c r="M73" s="18"/>
-      <x:c r="S73" s="18"/>
+      <x:c r="P73" s="18"/>
+      <x:c r="Q73" s="18"/>
     </x:row>
     <x:row r="74">
-      <x:c r="L74" s="18"/>
-      <x:c r="M74" s="18"/>
-      <x:c r="S74" s="18"/>
+      <x:c r="P74" s="18"/>
+      <x:c r="Q74" s="18"/>
     </x:row>
     <x:row r="75">
-      <x:c r="L75" s="18"/>
-      <x:c r="M75" s="18"/>
-      <x:c r="S75" s="18"/>
+      <x:c r="P75" s="18"/>
+      <x:c r="Q75" s="18"/>
     </x:row>
     <x:row r="76">
-      <x:c r="L76" s="18"/>
-      <x:c r="M76" s="18"/>
-      <x:c r="S76" s="18"/>
+      <x:c r="P76" s="18"/>
+      <x:c r="Q76" s="18"/>
     </x:row>
     <x:row r="77">
-      <x:c r="L77" s="18"/>
-      <x:c r="M77" s="18"/>
-      <x:c r="S77" s="18"/>
+      <x:c r="P77" s="18"/>
+      <x:c r="Q77" s="18"/>
     </x:row>
     <x:row r="78">
-      <x:c r="L78" s="18"/>
-      <x:c r="M78" s="18"/>
-      <x:c r="S78" s="18"/>
+      <x:c r="P78" s="18"/>
+      <x:c r="Q78" s="18"/>
     </x:row>
     <x:row r="79">
-      <x:c r="L79" s="18"/>
-      <x:c r="M79" s="18"/>
-      <x:c r="S79" s="18"/>
+      <x:c r="P79" s="18"/>
+      <x:c r="Q79" s="18"/>
     </x:row>
     <x:row r="80">
-      <x:c r="L80" s="18"/>
-      <x:c r="M80" s="18"/>
-      <x:c r="S80" s="18"/>
+      <x:c r="P80" s="18"/>
+      <x:c r="Q80" s="18"/>
     </x:row>
     <x:row r="81">
-      <x:c r="L81" s="18"/>
-      <x:c r="M81" s="18"/>
-      <x:c r="S81" s="18"/>
+      <x:c r="P81" s="18"/>
+      <x:c r="Q81" s="18"/>
     </x:row>
     <x:row r="82">
-      <x:c r="L82" s="18"/>
-      <x:c r="M82" s="18"/>
-      <x:c r="S82" s="18"/>
+      <x:c r="P82" s="18"/>
+      <x:c r="Q82" s="18"/>
     </x:row>
     <x:row r="83">
-      <x:c r="L83" s="18"/>
-      <x:c r="M83" s="18"/>
-      <x:c r="S83" s="18"/>
+      <x:c r="P83" s="18"/>
+      <x:c r="Q83" s="18"/>
     </x:row>
     <x:row r="84">
-      <x:c r="L84" s="18"/>
-      <x:c r="M84" s="18"/>
-      <x:c r="S84" s="18"/>
+      <x:c r="P84" s="18"/>
+      <x:c r="Q84" s="18"/>
     </x:row>
     <x:row r="85">
-      <x:c r="L85" s="18"/>
-      <x:c r="M85" s="18"/>
-      <x:c r="S85" s="18"/>
+      <x:c r="P85" s="18"/>
+      <x:c r="Q85" s="18"/>
     </x:row>
     <x:row r="86">
-      <x:c r="L86" s="18"/>
-      <x:c r="M86" s="18"/>
-      <x:c r="S86" s="18"/>
+      <x:c r="P86" s="18"/>
+      <x:c r="Q86" s="18"/>
     </x:row>
     <x:row r="87">
-      <x:c r="L87" s="18"/>
-      <x:c r="M87" s="18"/>
-      <x:c r="S87" s="18"/>
+      <x:c r="P87" s="18"/>
+      <x:c r="Q87" s="18"/>
     </x:row>
     <x:row r="88">
-      <x:c r="L88" s="18"/>
-      <x:c r="M88" s="18"/>
-      <x:c r="S88" s="18"/>
+      <x:c r="P88" s="18"/>
+      <x:c r="Q88" s="18"/>
     </x:row>
     <x:row r="89">
-      <x:c r="L89" s="18"/>
-      <x:c r="M89" s="18"/>
-      <x:c r="S89" s="18"/>
+      <x:c r="P89" s="18"/>
+      <x:c r="Q89" s="18"/>
     </x:row>
     <x:row r="90">
-      <x:c r="L90" s="18"/>
-      <x:c r="M90" s="18"/>
-      <x:c r="S90" s="18"/>
+      <x:c r="P90" s="18"/>
+      <x:c r="Q90" s="18"/>
     </x:row>
     <x:row r="91">
-      <x:c r="L91" s="18"/>
-      <x:c r="M91" s="18"/>
-      <x:c r="S91" s="18"/>
+      <x:c r="P91" s="18"/>
+      <x:c r="Q91" s="18"/>
     </x:row>
     <x:row r="92">
-      <x:c r="L92" s="18"/>
-      <x:c r="M92" s="18"/>
-      <x:c r="S92" s="18"/>
+      <x:c r="P92" s="18"/>
+      <x:c r="Q92" s="18"/>
     </x:row>
     <x:row r="93">
-      <x:c r="L93" s="18"/>
-      <x:c r="M93" s="18"/>
-      <x:c r="S93" s="18"/>
+      <x:c r="P93" s="18"/>
+      <x:c r="Q93" s="18"/>
     </x:row>
     <x:row r="94">
-      <x:c r="L94" s="18"/>
-      <x:c r="M94" s="18"/>
-      <x:c r="S94" s="18"/>
+      <x:c r="P94" s="18"/>
+      <x:c r="Q94" s="18"/>
     </x:row>
     <x:row r="95">
-      <x:c r="L95" s="18"/>
-      <x:c r="M95" s="18"/>
-      <x:c r="S95" s="18"/>
+      <x:c r="P95" s="18"/>
+      <x:c r="Q95" s="18"/>
     </x:row>
     <x:row r="96">
-      <x:c r="L96" s="18"/>
-      <x:c r="M96" s="18"/>
-      <x:c r="S96" s="18"/>
+      <x:c r="P96" s="18"/>
+      <x:c r="Q96" s="18"/>
     </x:row>
     <x:row r="97">
-      <x:c r="L97" s="18"/>
-      <x:c r="M97" s="18"/>
-      <x:c r="S97" s="18"/>
+      <x:c r="P97" s="18"/>
+      <x:c r="Q97" s="18"/>
     </x:row>
     <x:row r="98">
-      <x:c r="L98" s="18"/>
-      <x:c r="M98" s="18"/>
-      <x:c r="S98" s="18"/>
+      <x:c r="P98" s="18"/>
+      <x:c r="Q98" s="18"/>
     </x:row>
     <x:row r="99">
-      <x:c r="L99" s="18"/>
-      <x:c r="M99" s="18"/>
-      <x:c r="S99" s="18"/>
+      <x:c r="P99" s="18"/>
+      <x:c r="Q99" s="18"/>
     </x:row>
     <x:row r="100">
-      <x:c r="L100" s="18"/>
-      <x:c r="M100" s="18"/>
-      <x:c r="S100" s="18"/>
-    </x:row>
-  </x:sheetData>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="N2:N100">
-      <x:formula1>"No empezado,Pendiente,Completado,Cancelado"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="10.770000457763672" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="9.960000038146973" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19.520000457763672" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.170000076293945" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="35.66999816894531" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1">
-      <x:c r="A1" s="24" t="str">
-        <x:v>Objeto</x:v>
-      </x:c>
-      <x:c r="B1" s="24" t="str">
-        <x:v>Tipo</x:v>
-      </x:c>
-      <x:c r="C1" s="24" t="str">
-        <x:v>Insumo</x:v>
-      </x:c>
-      <x:c r="D1" s="24" t="str">
-        <x:v>Cantidad_Eventos_2026</x:v>
-      </x:c>
-      <x:c r="E1" s="24" t="str">
-        <x:v>Ultima_Fecha</x:v>
-      </x:c>
-      <x:c r="F1" s="24" t="str">
-        <x:v>Notas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2">
-      <x:c r="A2" s="11" t="str">
-        <x:v>Manzano tico</x:v>
-      </x:c>
-      <x:c r="B2" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
-      </x:c>
-      <x:c r="C2" s="11" t="str">
-        <x:v>Mistral</x:v>
-      </x:c>
-      <x:c r="D2" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E2" s="14" t="n">
-        <x:v>46181</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
-        <x:v>Ejemplo: se acumula desde EventosAgricolas</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3">
-      <x:c r="A3" s="11" t="str">
-        <x:v>Manzano tico</x:v>
-      </x:c>
-      <x:c r="B3" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="C3" s="11" t="str">
-        <x:v>YaraMila</x:v>
-      </x:c>
-      <x:c r="D3" s="11" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="E3" s="14" t="n">
-        <x:v>46174</x:v>
-      </x:c>
-      <x:c r="F3" s="11" t="str">
-        <x:v>Permite ver frecuencia anual</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="11" t="str">
-        <x:v>Guayaba</x:v>
-      </x:c>
-      <x:c r="B4" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="C4" s="11" t="str">
-        <x:v>Cal dolomita</x:v>
-      </x:c>
-      <x:c r="D4" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E4" s="14" t="n">
-        <x:v>46172</x:v>
-      </x:c>
-      <x:c r="F4" s="11" t="str">
-        <x:v>Aplicación de enmienda</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5">
-      <x:c r="A5" s="11" t="str">
-        <x:v>Guayaba</x:v>
-      </x:c>
-      <x:c r="B5" s="11" t="str">
-        <x:v>Abono tierra</x:v>
-      </x:c>
-      <x:c r="C5" s="11" t="str">
-        <x:v>YaraMila</x:v>
-      </x:c>
-      <x:c r="D5" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E5" s="14" t="n">
-        <x:v>46179</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
-        <x:v>Fertilización</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6">
-      <x:c r="A6" s="11" t="str">
-        <x:v>Pepino</x:v>
-      </x:c>
-      <x:c r="B6" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
-      </x:c>
-      <x:c r="C6" s="11" t="str">
-        <x:v>Cobre</x:v>
-      </x:c>
-      <x:c r="D6" s="11" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="n">
-        <x:v>46152</x:v>
-      </x:c>
-      <x:c r="F6" s="11" t="str">
-        <x:v>Historial por cultivo</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="E7" s="18"/>
-    </x:row>
-    <x:row r="8">
-      <x:c r="E8" s="18"/>
-    </x:row>
-    <x:row r="9">
-      <x:c r="E9" s="18"/>
-    </x:row>
-    <x:row r="10">
-      <x:c r="E10" s="18"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="E11" s="18"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="E12" s="18"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="E13" s="18"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="E14" s="18"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="E15" s="18"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="E16" s="18"/>
-    </x:row>
-    <x:row r="17">
-      <x:c r="E17" s="18"/>
-    </x:row>
-    <x:row r="18">
-      <x:c r="E18" s="18"/>
-    </x:row>
-    <x:row r="19">
-      <x:c r="E19" s="18"/>
-    </x:row>
-    <x:row r="20">
-      <x:c r="E20" s="18"/>
-    </x:row>
-    <x:row r="21">
-      <x:c r="E21" s="18"/>
-    </x:row>
-    <x:row r="22">
-      <x:c r="E22" s="18"/>
-    </x:row>
-    <x:row r="23">
-      <x:c r="E23" s="18"/>
-    </x:row>
-    <x:row r="24">
-      <x:c r="E24" s="18"/>
-    </x:row>
-    <x:row r="25">
-      <x:c r="E25" s="18"/>
-    </x:row>
-    <x:row r="26">
-      <x:c r="E26" s="18"/>
-    </x:row>
-    <x:row r="27">
-      <x:c r="E27" s="18"/>
-    </x:row>
-    <x:row r="28">
-      <x:c r="E28" s="18"/>
-    </x:row>
-    <x:row r="29">
-      <x:c r="E29" s="18"/>
-    </x:row>
-    <x:row r="30">
-      <x:c r="E30" s="18"/>
-    </x:row>
-    <x:row r="31">
-      <x:c r="E31" s="18"/>
-    </x:row>
-    <x:row r="32">
-      <x:c r="E32" s="18"/>
-    </x:row>
-    <x:row r="33">
-      <x:c r="E33" s="18"/>
-    </x:row>
-    <x:row r="34">
-      <x:c r="E34" s="18"/>
-    </x:row>
-    <x:row r="35">
-      <x:c r="E35" s="18"/>
-    </x:row>
-    <x:row r="36">
-      <x:c r="E36" s="18"/>
-    </x:row>
-    <x:row r="37">
-      <x:c r="E37" s="18"/>
-    </x:row>
-    <x:row r="38">
-      <x:c r="E38" s="18"/>
-    </x:row>
-    <x:row r="39">
-      <x:c r="E39" s="18"/>
-    </x:row>
-    <x:row r="40">
-      <x:c r="E40" s="18"/>
-    </x:row>
-    <x:row r="41">
-      <x:c r="E41" s="18"/>
-    </x:row>
-    <x:row r="42">
-      <x:c r="E42" s="18"/>
-    </x:row>
-    <x:row r="43">
-      <x:c r="E43" s="18"/>
-    </x:row>
-    <x:row r="44">
-      <x:c r="E44" s="18"/>
-    </x:row>
-    <x:row r="45">
-      <x:c r="E45" s="18"/>
-    </x:row>
-    <x:row r="46">
-      <x:c r="E46" s="18"/>
-    </x:row>
-    <x:row r="47">
-      <x:c r="E47" s="18"/>
-    </x:row>
-    <x:row r="48">
-      <x:c r="E48" s="18"/>
-    </x:row>
-    <x:row r="49">
-      <x:c r="E49" s="18"/>
-    </x:row>
-    <x:row r="50">
-      <x:c r="E50" s="18"/>
-    </x:row>
-    <x:row r="51">
-      <x:c r="E51" s="18"/>
-    </x:row>
-    <x:row r="52">
-      <x:c r="E52" s="18"/>
-    </x:row>
-    <x:row r="53">
-      <x:c r="E53" s="18"/>
-    </x:row>
-    <x:row r="54">
-      <x:c r="E54" s="18"/>
-    </x:row>
-    <x:row r="55">
-      <x:c r="E55" s="18"/>
-    </x:row>
-    <x:row r="56">
-      <x:c r="E56" s="18"/>
-    </x:row>
-    <x:row r="57">
-      <x:c r="E57" s="18"/>
-    </x:row>
-    <x:row r="58">
-      <x:c r="E58" s="18"/>
-    </x:row>
-    <x:row r="59">
-      <x:c r="E59" s="18"/>
-    </x:row>
-    <x:row r="60">
-      <x:c r="E60" s="18"/>
-    </x:row>
-    <x:row r="61">
-      <x:c r="E61" s="18"/>
-    </x:row>
-    <x:row r="62">
-      <x:c r="E62" s="18"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="E63" s="18"/>
-    </x:row>
-    <x:row r="64">
-      <x:c r="E64" s="18"/>
-    </x:row>
-    <x:row r="65">
-      <x:c r="E65" s="18"/>
-    </x:row>
-    <x:row r="66">
-      <x:c r="E66" s="18"/>
-    </x:row>
-    <x:row r="67">
-      <x:c r="E67" s="18"/>
-    </x:row>
-    <x:row r="68">
-      <x:c r="E68" s="18"/>
-    </x:row>
-    <x:row r="69">
-      <x:c r="E69" s="18"/>
-    </x:row>
-    <x:row r="70">
-      <x:c r="E70" s="18"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="E71" s="18"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="E72" s="18"/>
-    </x:row>
-    <x:row r="73">
-      <x:c r="E73" s="18"/>
-    </x:row>
-    <x:row r="74">
-      <x:c r="E74" s="18"/>
-    </x:row>
-    <x:row r="75">
-      <x:c r="E75" s="18"/>
-    </x:row>
-    <x:row r="76">
-      <x:c r="E76" s="18"/>
-    </x:row>
-    <x:row r="77">
-      <x:c r="E77" s="18"/>
-    </x:row>
-    <x:row r="78">
-      <x:c r="E78" s="18"/>
-    </x:row>
-    <x:row r="79">
-      <x:c r="E79" s="18"/>
-    </x:row>
-    <x:row r="80">
-      <x:c r="E80" s="18"/>
-    </x:row>
-    <x:row r="81">
-      <x:c r="E81" s="18"/>
-    </x:row>
-    <x:row r="82">
-      <x:c r="E82" s="18"/>
-    </x:row>
-    <x:row r="83">
-      <x:c r="E83" s="18"/>
-    </x:row>
-    <x:row r="84">
-      <x:c r="E84" s="18"/>
-    </x:row>
-    <x:row r="85">
-      <x:c r="E85" s="18"/>
-    </x:row>
-    <x:row r="86">
-      <x:c r="E86" s="18"/>
-    </x:row>
-    <x:row r="87">
-      <x:c r="E87" s="18"/>
-    </x:row>
-    <x:row r="88">
-      <x:c r="E88" s="18"/>
-    </x:row>
-    <x:row r="89">
-      <x:c r="E89" s="18"/>
-    </x:row>
-    <x:row r="90">
-      <x:c r="E90" s="18"/>
-    </x:row>
-    <x:row r="91">
-      <x:c r="E91" s="18"/>
-    </x:row>
-    <x:row r="92">
-      <x:c r="E92" s="18"/>
-    </x:row>
-    <x:row r="93">
-      <x:c r="E93" s="18"/>
-    </x:row>
-    <x:row r="94">
-      <x:c r="E94" s="18"/>
-    </x:row>
-    <x:row r="95">
-      <x:c r="E95" s="18"/>
-    </x:row>
-    <x:row r="96">
-      <x:c r="E96" s="18"/>
-    </x:row>
-    <x:row r="97">
-      <x:c r="E97" s="18"/>
-    </x:row>
-    <x:row r="98">
-      <x:c r="E98" s="18"/>
-    </x:row>
-    <x:row r="99">
-      <x:c r="E99" s="18"/>
-    </x:row>
-    <x:row r="100">
-      <x:c r="E100" s="18"/>
+      <x:c r="P100" s="18"/>
+      <x:c r="Q100" s="18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2588,7 +1299,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcb2f9b23aff645a9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c2aa61fcde94ed2"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -2713,10 +1424,10 @@
         <x:v>Cama</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>No activa</x:v>
+        <x:v>Activa</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Sin cultivos activos</x:v>
+        <x:v>Espacio disponible</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -2776,7 +1487,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9af87fcfa28946dd"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4a4299ed9a4465"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3242,7 +1953,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R06ae80cc640c42cc"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92f6337ef8614c14"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3306,6 +2017,9 @@
       <x:c r="M1" s="10" t="str">
         <x:v>Notas</x:v>
       </x:c>
+      <x:c r="N1" s="23" t="str">
+        <x:v>Evento_Agricola</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -3343,6 +2057,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M2" s="11" t="str"/>
+      <x:c r="N2" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -3380,6 +2097,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M3" s="11" t="str"/>
+      <x:c r="N3" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -3417,6 +2137,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M4" s="11" t="str"/>
+      <x:c r="N4" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -3454,6 +2177,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M5" s="11" t="str"/>
+      <x:c r="N5" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -3491,6 +2217,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M6" s="11" t="str"/>
+      <x:c r="N6" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -3528,6 +2257,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M7" s="11" t="str"/>
+      <x:c r="N7" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -3565,6 +2297,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M8" s="11" t="str"/>
+      <x:c r="N8" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -3596,6 +2331,9 @@
       <x:c r="M9" s="11" t="str">
         <x:v>Espacio disponible</x:v>
       </x:c>
+      <x:c r="N9" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -3633,6 +2371,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M10" s="11" t="str"/>
+      <x:c r="N10" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -3670,6 +2411,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M11" s="11" t="str"/>
+      <x:c r="N11" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -3707,6 +2451,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M12" s="11" t="str"/>
+      <x:c r="N12" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -3744,6 +2491,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M13" s="11" t="str"/>
+      <x:c r="N13" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -3781,6 +2531,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M14" s="11" t="str"/>
+      <x:c r="N14" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -3818,6 +2571,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M15" s="11" t="str"/>
+      <x:c r="N15" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -3855,6 +2611,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M16" s="11" t="str"/>
+      <x:c r="N16" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -3892,6 +2651,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M17" s="11" t="str"/>
+      <x:c r="N17" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
@@ -3931,6 +2693,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M18" s="11" t="str"/>
+      <x:c r="N18" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -3968,6 +2733,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M19" s="11" t="str"/>
+      <x:c r="N19" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -4005,6 +2773,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M20" s="11" t="str"/>
+      <x:c r="N20" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -4042,6 +2813,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M21" s="11" t="str"/>
+      <x:c r="N21" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -4081,6 +2855,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M22" s="11" t="str"/>
+      <x:c r="N22" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -4118,6 +2895,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M23" s="11" t="str"/>
+      <x:c r="N23" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="11" t="str">
@@ -4149,6 +2929,9 @@
       <x:c r="M24" s="11" t="str">
         <x:v>Espacio disponible</x:v>
       </x:c>
+      <x:c r="N24" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
@@ -4186,6 +2969,9 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M25" s="11" t="str"/>
+      <x:c r="N25" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -4223,11 +3009,279 @@
         <x:v>Completa</x:v>
       </x:c>
       <x:c r="M26" s="11" t="str"/>
+      <x:c r="N26" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>SIE_FRA_018</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>UNI_FRA_CAMA_04</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>CUL_DISPONIBLE</x:v>
+      </x:c>
+      <x:c r="E27" s="18"/>
+      <x:c r="F27" s="18"/>
+      <x:c r="G27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>Disponible</x:v>
+      </x:c>
+      <x:c r="I27" s="18"/>
+      <x:c r="J27" s="18"/>
+      <x:c r="K27" s="18"/>
+      <x:c r="L27" t="str">
+        <x:v>Completa</x:v>
+      </x:c>
+      <x:c r="M27" t="str">
+        <x:v>Espacio disponible</x:v>
+      </x:c>
+      <x:c r="N27" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="E28" s="18"/>
+      <x:c r="F28" s="18"/>
+      <x:c r="I28" s="18"/>
+      <x:c r="J28" s="18"/>
+      <x:c r="K28" s="18"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="E29" s="18"/>
+      <x:c r="F29" s="18"/>
+      <x:c r="I29" s="18"/>
+      <x:c r="J29" s="18"/>
+      <x:c r="K29" s="18"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="E30" s="18"/>
+      <x:c r="F30" s="18"/>
+      <x:c r="I30" s="18"/>
+      <x:c r="J30" s="18"/>
+      <x:c r="K30" s="18"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="E31" s="18"/>
+      <x:c r="F31" s="18"/>
+      <x:c r="I31" s="18"/>
+      <x:c r="J31" s="18"/>
+      <x:c r="K31" s="18"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="E32" s="18"/>
+      <x:c r="F32" s="18"/>
+      <x:c r="I32" s="18"/>
+      <x:c r="J32" s="18"/>
+      <x:c r="K32" s="18"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="E33" s="18"/>
+      <x:c r="F33" s="18"/>
+      <x:c r="I33" s="18"/>
+      <x:c r="J33" s="18"/>
+      <x:c r="K33" s="18"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="E34" s="18"/>
+      <x:c r="F34" s="18"/>
+      <x:c r="I34" s="18"/>
+      <x:c r="J34" s="18"/>
+      <x:c r="K34" s="18"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="E35" s="18"/>
+      <x:c r="F35" s="18"/>
+      <x:c r="I35" s="18"/>
+      <x:c r="J35" s="18"/>
+      <x:c r="K35" s="18"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="E36" s="18"/>
+      <x:c r="F36" s="18"/>
+      <x:c r="I36" s="18"/>
+      <x:c r="J36" s="18"/>
+      <x:c r="K36" s="18"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="E37" s="18"/>
+      <x:c r="F37" s="18"/>
+      <x:c r="I37" s="18"/>
+      <x:c r="J37" s="18"/>
+      <x:c r="K37" s="18"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="E38" s="18"/>
+      <x:c r="F38" s="18"/>
+      <x:c r="I38" s="18"/>
+      <x:c r="J38" s="18"/>
+      <x:c r="K38" s="18"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="E39" s="18"/>
+      <x:c r="F39" s="18"/>
+      <x:c r="I39" s="18"/>
+      <x:c r="J39" s="18"/>
+      <x:c r="K39" s="18"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="E40" s="18"/>
+      <x:c r="F40" s="18"/>
+      <x:c r="I40" s="18"/>
+      <x:c r="J40" s="18"/>
+      <x:c r="K40" s="18"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="E41" s="18"/>
+      <x:c r="F41" s="18"/>
+      <x:c r="I41" s="18"/>
+      <x:c r="J41" s="18"/>
+      <x:c r="K41" s="18"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="E42" s="18"/>
+      <x:c r="F42" s="18"/>
+      <x:c r="I42" s="18"/>
+      <x:c r="J42" s="18"/>
+      <x:c r="K42" s="18"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="E43" s="18"/>
+      <x:c r="F43" s="18"/>
+      <x:c r="I43" s="18"/>
+      <x:c r="J43" s="18"/>
+      <x:c r="K43" s="18"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="E44" s="18"/>
+      <x:c r="F44" s="18"/>
+      <x:c r="I44" s="18"/>
+      <x:c r="J44" s="18"/>
+      <x:c r="K44" s="18"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="E45" s="18"/>
+      <x:c r="F45" s="18"/>
+      <x:c r="I45" s="18"/>
+      <x:c r="J45" s="18"/>
+      <x:c r="K45" s="18"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="E46" s="18"/>
+      <x:c r="F46" s="18"/>
+      <x:c r="I46" s="18"/>
+      <x:c r="J46" s="18"/>
+      <x:c r="K46" s="18"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="E47" s="18"/>
+      <x:c r="F47" s="18"/>
+      <x:c r="I47" s="18"/>
+      <x:c r="J47" s="18"/>
+      <x:c r="K47" s="18"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="E48" s="18"/>
+      <x:c r="F48" s="18"/>
+      <x:c r="I48" s="18"/>
+      <x:c r="J48" s="18"/>
+      <x:c r="K48" s="18"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="E49" s="18"/>
+      <x:c r="F49" s="18"/>
+      <x:c r="I49" s="18"/>
+      <x:c r="J49" s="18"/>
+      <x:c r="K49" s="18"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="E50" s="18"/>
+      <x:c r="F50" s="18"/>
+      <x:c r="I50" s="18"/>
+      <x:c r="J50" s="18"/>
+      <x:c r="K50" s="18"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="E51" s="18"/>
+      <x:c r="F51" s="18"/>
+      <x:c r="I51" s="18"/>
+      <x:c r="J51" s="18"/>
+      <x:c r="K51" s="18"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="E52" s="18"/>
+      <x:c r="F52" s="18"/>
+      <x:c r="I52" s="18"/>
+      <x:c r="J52" s="18"/>
+      <x:c r="K52" s="18"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="E53" s="18"/>
+      <x:c r="F53" s="18"/>
+      <x:c r="I53" s="18"/>
+      <x:c r="J53" s="18"/>
+      <x:c r="K53" s="18"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="E54" s="18"/>
+      <x:c r="F54" s="18"/>
+      <x:c r="I54" s="18"/>
+      <x:c r="J54" s="18"/>
+      <x:c r="K54" s="18"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="E55" s="18"/>
+      <x:c r="F55" s="18"/>
+      <x:c r="I55" s="18"/>
+      <x:c r="J55" s="18"/>
+      <x:c r="K55" s="18"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="E56" s="18"/>
+      <x:c r="F56" s="18"/>
+      <x:c r="I56" s="18"/>
+      <x:c r="J56" s="18"/>
+      <x:c r="K56" s="18"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="E57" s="18"/>
+      <x:c r="F57" s="18"/>
+      <x:c r="I57" s="18"/>
+      <x:c r="J57" s="18"/>
+      <x:c r="K57" s="18"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="E58" s="18"/>
+      <x:c r="F58" s="18"/>
+      <x:c r="I58" s="18"/>
+      <x:c r="J58" s="18"/>
+      <x:c r="K58" s="18"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="E59" s="18"/>
+      <x:c r="F59" s="18"/>
+      <x:c r="I59" s="18"/>
+      <x:c r="J59" s="18"/>
+      <x:c r="K59" s="18"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="E60" s="18"/>
+      <x:c r="F60" s="18"/>
+      <x:c r="I60" s="18"/>
+      <x:c r="J60" s="18"/>
+      <x:c r="K60" s="18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf0e133099af24394"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refc14cba555b43ec"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4307,6 +3361,9 @@
       <x:c r="Q1" s="10" t="str">
         <x:v>Mes_Cosecha</x:v>
       </x:c>
+      <x:c r="R1" s="23" t="str">
+        <x:v>Evento_Agricola</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -4356,6 +3413,9 @@
       <x:c r="Q2" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R2" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -4405,6 +3465,9 @@
       <x:c r="Q3" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
+      <x:c r="R3" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -4454,6 +3517,9 @@
       <x:c r="Q4" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R4" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -4503,6 +3569,9 @@
       <x:c r="Q5" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
+      <x:c r="R5" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -4552,6 +3621,9 @@
       <x:c r="Q6" s="11" t="str">
         <x:v>2026-03</x:v>
       </x:c>
+      <x:c r="R6" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -4601,6 +3673,9 @@
       <x:c r="Q7" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R7" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -4649,6 +3724,9 @@
       <x:c r="P8" s="11" t="str"/>
       <x:c r="Q8" s="11" t="str">
         <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="R8" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -4691,6 +3769,9 @@
       <x:c r="Q9" s="11" t="str">
         <x:v>Sin fecha</x:v>
       </x:c>
+      <x:c r="R9" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -4740,6 +3821,9 @@
       <x:c r="Q10" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R10" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -4789,6 +3873,9 @@
       <x:c r="Q11" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R11" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -4838,6 +3925,9 @@
       <x:c r="Q12" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R12" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -4887,6 +3977,9 @@
       <x:c r="Q13" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R13" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -4936,6 +4029,9 @@
       <x:c r="Q14" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R14" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -4985,6 +4081,9 @@
       <x:c r="Q15" s="11" t="str">
         <x:v>2026-05</x:v>
       </x:c>
+      <x:c r="R15" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -5034,6 +4133,9 @@
       <x:c r="Q16" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R16" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -5083,6 +4185,9 @@
       <x:c r="Q17" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R17" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="11" t="str">
@@ -5134,6 +4239,9 @@
       <x:c r="Q18" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R18" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="11" t="str">
@@ -5183,6 +4291,9 @@
       <x:c r="Q19" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R19" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="11" t="str">
@@ -5232,6 +4343,9 @@
       <x:c r="Q20" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R20" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="11" t="str">
@@ -5281,6 +4395,9 @@
       <x:c r="Q21" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R21" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="11" t="str">
@@ -5332,6 +4449,9 @@
       <x:c r="Q22" s="11" t="str">
         <x:v>2026-08</x:v>
       </x:c>
+      <x:c r="R22" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="11" t="str">
@@ -5380,6 +4500,9 @@
       <x:c r="P23" s="11" t="str"/>
       <x:c r="Q23" s="11" t="str">
         <x:v>2026-06</x:v>
+      </x:c>
+      <x:c r="R23" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -5422,6 +4545,9 @@
       <x:c r="Q24" s="11" t="str">
         <x:v>Sin fecha</x:v>
       </x:c>
+      <x:c r="R24" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="11" t="str">
@@ -5471,6 +4597,9 @@
       <x:c r="Q25" s="11" t="str">
         <x:v>2026-06</x:v>
       </x:c>
+      <x:c r="R25" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="11" t="str">
@@ -5520,11 +4649,289 @@
       <x:c r="Q26" s="11" t="str">
         <x:v>2026-07</x:v>
       </x:c>
+      <x:c r="R26" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27">
+      <x:c r="A27" t="str">
+        <x:v>SIE_FRA_018</x:v>
+      </x:c>
+      <x:c r="B27" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="C27" t="str">
+        <x:v>FIN_FRAILES</x:v>
+      </x:c>
+      <x:c r="D27" t="str">
+        <x:v>Cama Frailes 4</x:v>
+      </x:c>
+      <x:c r="E27" t="str">
+        <x:v>UNI_FRA_CAMA_04</x:v>
+      </x:c>
+      <x:c r="F27" t="str">
+        <x:v>Activa</x:v>
+      </x:c>
+      <x:c r="G27" t="str">
+        <x:v>Disponible</x:v>
+      </x:c>
+      <x:c r="H27" t="str">
+        <x:v>CUL_DISPONIBLE</x:v>
+      </x:c>
+      <x:c r="I27" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J27" t="str">
+        <x:v>Disponible</x:v>
+      </x:c>
+      <x:c r="K27" s="18"/>
+      <x:c r="L27" s="18"/>
+      <x:c r="M27" s="18"/>
+      <x:c r="N27" s="18"/>
+      <x:c r="O27" s="18"/>
+      <x:c r="P27"/>
+      <x:c r="Q27" t="str">
+        <x:v>Sin fecha</x:v>
+      </x:c>
+      <x:c r="R27" s="11" t="str">
+        <x:v>Ver EventosAgricolas</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28">
+      <x:c r="K28" s="18"/>
+      <x:c r="L28" s="18"/>
+      <x:c r="M28" s="18"/>
+      <x:c r="N28" s="18"/>
+      <x:c r="O28" s="18"/>
+    </x:row>
+    <x:row r="29">
+      <x:c r="K29" s="18"/>
+      <x:c r="L29" s="18"/>
+      <x:c r="M29" s="18"/>
+      <x:c r="N29" s="18"/>
+      <x:c r="O29" s="18"/>
+    </x:row>
+    <x:row r="30">
+      <x:c r="K30" s="18"/>
+      <x:c r="L30" s="18"/>
+      <x:c r="M30" s="18"/>
+      <x:c r="N30" s="18"/>
+      <x:c r="O30" s="18"/>
+    </x:row>
+    <x:row r="31">
+      <x:c r="K31" s="18"/>
+      <x:c r="L31" s="18"/>
+      <x:c r="M31" s="18"/>
+      <x:c r="N31" s="18"/>
+      <x:c r="O31" s="18"/>
+    </x:row>
+    <x:row r="32">
+      <x:c r="K32" s="18"/>
+      <x:c r="L32" s="18"/>
+      <x:c r="M32" s="18"/>
+      <x:c r="N32" s="18"/>
+      <x:c r="O32" s="18"/>
+    </x:row>
+    <x:row r="33">
+      <x:c r="K33" s="18"/>
+      <x:c r="L33" s="18"/>
+      <x:c r="M33" s="18"/>
+      <x:c r="N33" s="18"/>
+      <x:c r="O33" s="18"/>
+    </x:row>
+    <x:row r="34">
+      <x:c r="K34" s="18"/>
+      <x:c r="L34" s="18"/>
+      <x:c r="M34" s="18"/>
+      <x:c r="N34" s="18"/>
+      <x:c r="O34" s="18"/>
+    </x:row>
+    <x:row r="35">
+      <x:c r="K35" s="18"/>
+      <x:c r="L35" s="18"/>
+      <x:c r="M35" s="18"/>
+      <x:c r="N35" s="18"/>
+      <x:c r="O35" s="18"/>
+    </x:row>
+    <x:row r="36">
+      <x:c r="K36" s="18"/>
+      <x:c r="L36" s="18"/>
+      <x:c r="M36" s="18"/>
+      <x:c r="N36" s="18"/>
+      <x:c r="O36" s="18"/>
+    </x:row>
+    <x:row r="37">
+      <x:c r="K37" s="18"/>
+      <x:c r="L37" s="18"/>
+      <x:c r="M37" s="18"/>
+      <x:c r="N37" s="18"/>
+      <x:c r="O37" s="18"/>
+    </x:row>
+    <x:row r="38">
+      <x:c r="K38" s="18"/>
+      <x:c r="L38" s="18"/>
+      <x:c r="M38" s="18"/>
+      <x:c r="N38" s="18"/>
+      <x:c r="O38" s="18"/>
+    </x:row>
+    <x:row r="39">
+      <x:c r="K39" s="18"/>
+      <x:c r="L39" s="18"/>
+      <x:c r="M39" s="18"/>
+      <x:c r="N39" s="18"/>
+      <x:c r="O39" s="18"/>
+    </x:row>
+    <x:row r="40">
+      <x:c r="K40" s="18"/>
+      <x:c r="L40" s="18"/>
+      <x:c r="M40" s="18"/>
+      <x:c r="N40" s="18"/>
+      <x:c r="O40" s="18"/>
+    </x:row>
+    <x:row r="41">
+      <x:c r="K41" s="18"/>
+      <x:c r="L41" s="18"/>
+      <x:c r="M41" s="18"/>
+      <x:c r="N41" s="18"/>
+      <x:c r="O41" s="18"/>
+    </x:row>
+    <x:row r="42">
+      <x:c r="K42" s="18"/>
+      <x:c r="L42" s="18"/>
+      <x:c r="M42" s="18"/>
+      <x:c r="N42" s="18"/>
+      <x:c r="O42" s="18"/>
+    </x:row>
+    <x:row r="43">
+      <x:c r="K43" s="18"/>
+      <x:c r="L43" s="18"/>
+      <x:c r="M43" s="18"/>
+      <x:c r="N43" s="18"/>
+      <x:c r="O43" s="18"/>
+    </x:row>
+    <x:row r="44">
+      <x:c r="K44" s="18"/>
+      <x:c r="L44" s="18"/>
+      <x:c r="M44" s="18"/>
+      <x:c r="N44" s="18"/>
+      <x:c r="O44" s="18"/>
+    </x:row>
+    <x:row r="45">
+      <x:c r="K45" s="18"/>
+      <x:c r="L45" s="18"/>
+      <x:c r="M45" s="18"/>
+      <x:c r="N45" s="18"/>
+      <x:c r="O45" s="18"/>
+    </x:row>
+    <x:row r="46">
+      <x:c r="K46" s="18"/>
+      <x:c r="L46" s="18"/>
+      <x:c r="M46" s="18"/>
+      <x:c r="N46" s="18"/>
+      <x:c r="O46" s="18"/>
+    </x:row>
+    <x:row r="47">
+      <x:c r="K47" s="18"/>
+      <x:c r="L47" s="18"/>
+      <x:c r="M47" s="18"/>
+      <x:c r="N47" s="18"/>
+      <x:c r="O47" s="18"/>
+    </x:row>
+    <x:row r="48">
+      <x:c r="K48" s="18"/>
+      <x:c r="L48" s="18"/>
+      <x:c r="M48" s="18"/>
+      <x:c r="N48" s="18"/>
+      <x:c r="O48" s="18"/>
+    </x:row>
+    <x:row r="49">
+      <x:c r="K49" s="18"/>
+      <x:c r="L49" s="18"/>
+      <x:c r="M49" s="18"/>
+      <x:c r="N49" s="18"/>
+      <x:c r="O49" s="18"/>
+    </x:row>
+    <x:row r="50">
+      <x:c r="K50" s="18"/>
+      <x:c r="L50" s="18"/>
+      <x:c r="M50" s="18"/>
+      <x:c r="N50" s="18"/>
+      <x:c r="O50" s="18"/>
+    </x:row>
+    <x:row r="51">
+      <x:c r="K51" s="18"/>
+      <x:c r="L51" s="18"/>
+      <x:c r="M51" s="18"/>
+      <x:c r="N51" s="18"/>
+      <x:c r="O51" s="18"/>
+    </x:row>
+    <x:row r="52">
+      <x:c r="K52" s="18"/>
+      <x:c r="L52" s="18"/>
+      <x:c r="M52" s="18"/>
+      <x:c r="N52" s="18"/>
+      <x:c r="O52" s="18"/>
+    </x:row>
+    <x:row r="53">
+      <x:c r="K53" s="18"/>
+      <x:c r="L53" s="18"/>
+      <x:c r="M53" s="18"/>
+      <x:c r="N53" s="18"/>
+      <x:c r="O53" s="18"/>
+    </x:row>
+    <x:row r="54">
+      <x:c r="K54" s="18"/>
+      <x:c r="L54" s="18"/>
+      <x:c r="M54" s="18"/>
+      <x:c r="N54" s="18"/>
+      <x:c r="O54" s="18"/>
+    </x:row>
+    <x:row r="55">
+      <x:c r="K55" s="18"/>
+      <x:c r="L55" s="18"/>
+      <x:c r="M55" s="18"/>
+      <x:c r="N55" s="18"/>
+      <x:c r="O55" s="18"/>
+    </x:row>
+    <x:row r="56">
+      <x:c r="K56" s="18"/>
+      <x:c r="L56" s="18"/>
+      <x:c r="M56" s="18"/>
+      <x:c r="N56" s="18"/>
+      <x:c r="O56" s="18"/>
+    </x:row>
+    <x:row r="57">
+      <x:c r="K57" s="18"/>
+      <x:c r="L57" s="18"/>
+      <x:c r="M57" s="18"/>
+      <x:c r="N57" s="18"/>
+      <x:c r="O57" s="18"/>
+    </x:row>
+    <x:row r="58">
+      <x:c r="K58" s="18"/>
+      <x:c r="L58" s="18"/>
+      <x:c r="M58" s="18"/>
+      <x:c r="N58" s="18"/>
+      <x:c r="O58" s="18"/>
+    </x:row>
+    <x:row r="59">
+      <x:c r="K59" s="18"/>
+      <x:c r="L59" s="18"/>
+      <x:c r="M59" s="18"/>
+      <x:c r="N59" s="18"/>
+      <x:c r="O59" s="18"/>
+    </x:row>
+    <x:row r="60">
+      <x:c r="K60" s="18"/>
+      <x:c r="L60" s="18"/>
+      <x:c r="M60" s="18"/>
+      <x:c r="N60" s="18"/>
+      <x:c r="O60" s="18"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra36015e448df4c19"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24f9597babe14961"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5533,126 +4940,78 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="13.319999694824219" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="10" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
-      <x:c r="A1" s="24" t="str">
+      <x:c r="A1" s="10" t="str">
         <x:v>Lista</x:v>
       </x:c>
-      <x:c r="B1" s="24" t="str">
+      <x:c r="B1" s="10" t="str">
         <x:v>Valor</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>Tipo_Evento</x:v>
+        <x:v>Estados_Unidad</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Activa</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>Tipo_Evento</x:v>
+        <x:v>Estados_Unidad</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>No activa</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>Tipo_Evento</x:v>
+        <x:v>Estados_Cultivo</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Poda</x:v>
+        <x:v>Crecimiento</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>Tipo_Evento</x:v>
+        <x:v>Estados_Cultivo</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Abono foliar</x:v>
+        <x:v>Floración</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>Estado_Evento</x:v>
+        <x:v>Estados_Cultivo</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>No empezado</x:v>
+        <x:v>Disponible</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>Estado_Evento</x:v>
+        <x:v>Estados_Cultivo</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Pendiente</x:v>
+        <x:v>Cosechado</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>Estado_Evento</x:v>
+        <x:v>Estados_Cultivo</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Completado</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="11" t="str">
-        <x:v>Objeto_Tipo</x:v>
-      </x:c>
-      <x:c r="B9" s="11" t="str">
-        <x:v>Cultivo</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="11" t="str">
-        <x:v>Objeto_Tipo</x:v>
-      </x:c>
-      <x:c r="B10" s="11" t="str">
-        <x:v>Árbol</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="11" t="str">
-        <x:v>Objeto_Tipo</x:v>
-      </x:c>
-      <x:c r="B11" s="11" t="str">
-        <x:v>Cama</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="11" t="str">
-        <x:v>Estado_Sanitario</x:v>
-      </x:c>
-      <x:c r="B12" s="11" t="str">
-        <x:v>Bueno</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="11" t="str">
-        <x:v>Estado_Sanitario</x:v>
-      </x:c>
-      <x:c r="B13" s="11" t="str">
-        <x:v>Atención</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="11" t="str">
-        <x:v>Estado_Sanitario</x:v>
-      </x:c>
-      <x:c r="B14" s="11" t="str">
-        <x:v>Estrés</x:v>
+        <x:v>Sin fecha</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R51aaf7bf38bd4985"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc327f05eb480415e"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5661,181 +5020,405 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="16.959999084472656" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="13.59000015258789" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.359999656677246" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="7.400000095367432" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="22.479999542236328" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="17.899999618530273" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="16.959999084472656" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.609999656677246" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="43.34000015258789" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="51.68000030517578" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="15.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="24" t="str">
-        <x:v>Unidad_ID</x:v>
+        <x:v>ID_Insumo</x:v>
       </x:c>
       <x:c r="B1" s="24" t="str">
-        <x:v>Finca_ID</x:v>
+        <x:v>Nombre</x:v>
       </x:c>
       <x:c r="C1" s="24" t="str">
-        <x:v>Unidad_Nombre</x:v>
+        <x:v>Tipo</x:v>
       </x:c>
       <x:c r="D1" s="24" t="str">
-        <x:v>Tipo_Unidad</x:v>
+        <x:v>Disponible</x:v>
       </x:c>
       <x:c r="E1" s="24" t="str">
-        <x:v>Estado</x:v>
+        <x:v>Uso_Principal</x:v>
       </x:c>
       <x:c r="F1" s="24" t="str">
-        <x:v>Notas</x:v>
+        <x:v>Restricciones/Notas</x:v>
+      </x:c>
+      <x:c r="G1" s="24" t="str">
+        <x:v>Compra_Requerida</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>UNI_MOR_CAMA_01</x:v>
+        <x:v>INS_COBRE</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>FIN_MORAVIA</x:v>
+        <x:v>Cobre</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
-        <x:v>Cama Moravia 1</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D2" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E2" s="11" t="str">
-        <x:v>Activa</x:v>
+        <x:v>Hongos y bacterias en manejo preventivo/correctivo</x:v>
       </x:c>
       <x:c r="F2" s="11" t="str">
-        <x:v>Incluye espacios disponibles</x:v>
+        <x:v>Evitar mezclar sin validar compatibilidad; aplicar temprano/tarde</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_01</x:v>
+        <x:v>INS_NEEM</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Neem</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Cama Frailes 1</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Activa</x:v>
-      </x:c>
-      <x:c r="F3" s="11"/>
+        <x:v>Control preventivo de insectos blandos</x:v>
+      </x:c>
+      <x:c r="F3" s="11" t="str">
+        <x:v>Evitar sol fuerte; repetir según presión de plaga</x:v>
+      </x:c>
+      <x:c r="G3" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_02</x:v>
+        <x:v>INS_JABON_POTASICO</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Jabón Potásico</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Cama Frailes 2</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Activa</x:v>
-      </x:c>
-      <x:c r="F4" s="11"/>
+        <x:v>Control de insectos blandos y limpieza foliar</x:v>
+      </x:c>
+      <x:c r="F4" s="11" t="str">
+        <x:v>Probar en pocas hojas antes de aplicar general</x:v>
+      </x:c>
+      <x:c r="G4" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_03</x:v>
+        <x:v>INS_MISTRAL</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Mistral</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
-        <x:v>Cama Frailes 3</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D5" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E5" s="11" t="str">
-        <x:v>Activa</x:v>
-      </x:c>
-      <x:c r="F5" s="11"/>
+        <x:v>Control fitosanitario según etiqueta</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Usar dosis de etiqueta; no aplicar en horas de calor</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_04</x:v>
+        <x:v>INS_BICARBONATO</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Bicarbonato de Sodio</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Cama Frailes 4</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>No activa</x:v>
+        <x:v>Apoyo preventivo contra hongos superficiales</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Sin cultivos activos</x:v>
+        <x:v>No abusar; puede quemar hojas si se concentra</x:v>
+      </x:c>
+      <x:c r="G6" s="11" t="str">
+        <x:v>No</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_05</x:v>
+        <x:v>INS_CAL_DOLOMITA</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Cal Dolomita</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
-        <x:v>Cama Frailes 5</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D7" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Activa</x:v>
-      </x:c>
-      <x:c r="F7" s="11"/>
+        <x:v>Corrección de suelo y aporte de calcio/magnesio</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>No aplicar pegado al tronco; incorporar superficialmente</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_06</x:v>
+        <x:v>INS_CENIZA</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Ceniza</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
-        <x:v>Cama Frailes 6</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D8" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E8" s="11" t="str">
-        <x:v>Activa</x:v>
-      </x:c>
-      <x:c r="F8" s="11"/>
+        <x:v>Aporte de potasio y minerales; enmienda suave</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>Usar moderado; puede subir pH</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
-        <x:v>UNI_FRA_CAMA_07</x:v>
+        <x:v>INS_MELASA</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>FIN_FRAILES</x:v>
+        <x:v>Melasa</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
-        <x:v>Cama Frailes 7</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="D9" s="11" t="str">
-        <x:v>Cama</x:v>
+        <x:v>Sí</x:v>
       </x:c>
       <x:c r="E9" s="11" t="str">
-        <x:v>Activa</x:v>
-      </x:c>
-      <x:c r="F9" s="11"/>
+        <x:v>Activación biológica en mezclas y compost</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>Usar dosis baja; evitar exceso de azúcar</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="11" t="str">
+        <x:v>INS_COMPOST</x:v>
+      </x:c>
+      <x:c r="B10" s="11" t="str">
+        <x:v>Compost</x:v>
+      </x:c>
+      <x:c r="C10" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>Materia orgánica y mejora del suelo</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>Aplicar maduro; evitar contacto directo con cuello</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="11" t="str">
+        <x:v>INS_HENO</x:v>
+      </x:c>
+      <x:c r="B11" s="11" t="str">
+        <x:v>Heno</x:v>
+      </x:c>
+      <x:c r="C11" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D11" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E11" s="11" t="str">
+        <x:v>Cobertura/mulch para humedad y protección de suelo</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>Mantener separado del tronco para evitar hongos</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="11" t="str">
+        <x:v>INS_GALLINAZA</x:v>
+      </x:c>
+      <x:c r="B12" s="11" t="str">
+        <x:v>Gallinaza</x:v>
+      </x:c>
+      <x:c r="C12" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D12" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+      <x:c r="E12" s="11" t="str">
+        <x:v>Abono orgánico alto en nitrógeno</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>Debe estar compostada; riesgo de quemar raíces</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="11" t="str">
+        <x:v>INS_YARAMILA</x:v>
+      </x:c>
+      <x:c r="B13" s="11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="C13" s="11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>Fertilización granulada de suelo</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>Usar dosis controlada; evitar excesos de nitrógeno</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="11" t="str">
+        <x:v>INS_CALCIO_BORO</x:v>
+      </x:c>
+      <x:c r="B14" s="11" t="str">
+        <x:v>Calcio Boro</x:v>
+      </x:c>
+      <x:c r="C14" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="D14" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E14" s="11" t="str">
+        <x:v>Floración, cuajado y llenado temprano</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>Aplicar temprano/tarde; no mezclar sin validar</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="11" t="str">
+        <x:v>INS_MULTIMINERAL</x:v>
+      </x:c>
+      <x:c r="B15" s="11" t="str">
+        <x:v>Multimineral</x:v>
+      </x:c>
+      <x:c r="C15" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="D15" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E15" s="11" t="str">
+        <x:v>Corrección/apoyo nutricional foliar</x:v>
+      </x:c>
+      <x:c r="F15" s="11" t="str">
+        <x:v>Respetar dosis; evitar estrés fuerte</x:v>
+      </x:c>
+      <x:c r="G15" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="11" t="str">
+        <x:v>INS_FOLIAR_7425</x:v>
+      </x:c>
+      <x:c r="B16" s="11" t="str">
+        <x:v>Foliar 7-4-25</x:v>
+      </x:c>
+      <x:c r="C16" s="11" t="str">
+        <x:v>Abono foliar</x:v>
+      </x:c>
+      <x:c r="D16" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E16" s="11" t="str">
+        <x:v>Apoyo potasio/foliar en desarrollo y llenado</x:v>
+      </x:c>
+      <x:c r="F16" s="11" t="str">
+        <x:v>Usar según etapa; evitar exceso</x:v>
+      </x:c>
+      <x:c r="G16" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="11" t="str">
+        <x:v>INS_PAS80</x:v>
+      </x:c>
+      <x:c r="B17" s="11" t="str">
+        <x:v>PAS-80</x:v>
+      </x:c>
+      <x:c r="C17" s="11" t="str">
+        <x:v>Coadyuvante</x:v>
+      </x:c>
+      <x:c r="D17" s="11" t="str">
+        <x:v>Sí</x:v>
+      </x:c>
+      <x:c r="E17" s="11" t="str">
+        <x:v>Mejorar adherencia/cobertura de aplicaciones foliares</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>Usar dosis baja según etiqueta</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str">
+        <x:v>No</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5846,612 +5429,526 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="17.899999618530273" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.81999969482422" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="16.020000457763672" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="8.609999656677246" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="38.4900016784668" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="41.04999923706055" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="15.75" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="25.979999542236328" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="15.609999656677246" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="42.2599983215332" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="13.1899995803833" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="28.399999618530273" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="11.4399995803833" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="6.460000038146973" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="16.149999618530273" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="4.440000057220459" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="15.210000038146973" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="8.479999542236328" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="13.729999542236328" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="16.020000457763672" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="35.2599983215332" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="24" t="str">
-        <x:v>ID_Insumo</x:v>
+        <x:v>Arbol_ID</x:v>
       </x:c>
       <x:c r="B1" s="24" t="str">
-        <x:v>Nombre</x:v>
+        <x:v>Finca_ID</x:v>
       </x:c>
       <x:c r="C1" s="24" t="str">
-        <x:v>Tipo</x:v>
+        <x:v>Finca</x:v>
       </x:c>
       <x:c r="D1" s="24" t="str">
-        <x:v>Disponible</x:v>
+        <x:v>Arbol</x:v>
       </x:c>
       <x:c r="E1" s="24" t="str">
-        <x:v>Uso_Principal</x:v>
+        <x:v>Icono</x:v>
       </x:c>
       <x:c r="F1" s="24" t="str">
-        <x:v>Restricciones/Notas</x:v>
+        <x:v>Estado_Fenologico</x:v>
       </x:c>
       <x:c r="G1" s="24" t="str">
-        <x:v>Compra_Requerida</x:v>
+        <x:v>Trasplante</x:v>
       </x:c>
       <x:c r="H1" s="24" t="str">
-        <x:v>Cantidad_Guia</x:v>
+        <x:v>Estado_Sanitario</x:v>
       </x:c>
       <x:c r="I1" s="24" t="str">
-        <x:v>Unidad_Medida</x:v>
+        <x:v>Evento_Agricola</x:v>
       </x:c>
       <x:c r="J1" s="24" t="str">
-        <x:v>Momento_Aplicacion</x:v>
-      </x:c>
-      <x:c r="K1" s="24" t="str">
-        <x:v>Frecuencia_Dias</x:v>
+        <x:v>Notas</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
-        <x:v>INS_COBRE</x:v>
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
       </x:c>
       <x:c r="B2" s="11" t="str">
-        <x:v>Cobre</x:v>
+        <x:v>FIN_MORAVIA</x:v>
       </x:c>
       <x:c r="C2" s="11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="D2" s="11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
+      <x:c r="E2" s="11" t="str">
+        <x:v>🍎</x:v>
+      </x:c>
+      <x:c r="F2" s="11" t="str">
+        <x:v>Llenado</x:v>
+      </x:c>
+      <x:c r="G2" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H2" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I2" s="11" t="str">
         <x:v>Control fitosanitario</x:v>
       </x:c>
-      <x:c r="D2" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E2" s="11" t="str">
-        <x:v>Hongos/bacteriosis preventivo</x:v>
-      </x:c>
-      <x:c r="F2" s="11" t="str">
-        <x:v>Evitar mezcla incompatible; aplicar temprano/tarde</x:v>
-      </x:c>
-      <x:c r="G2" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H2" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="I2" s="11" t="str">
-        <x:v>ml/L o g/L</x:v>
-      </x:c>
       <x:c r="J2" s="11" t="str">
-        <x:v>Alta humedad / prevención hongos</x:v>
-      </x:c>
-      <x:c r="K2" s="11" t="n">
-        <x:v>14</x:v>
+        <x:v>Poda y manejo de chupones en seguimiento</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
-        <x:v>INS_NEEM</x:v>
+        <x:v>ARB_GUAYABITA_MORAVIA</x:v>
       </x:c>
       <x:c r="B3" s="11" t="str">
-        <x:v>Neem</x:v>
+        <x:v>FIN_MORAVIA</x:v>
       </x:c>
       <x:c r="C3" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Moravia</x:v>
       </x:c>
       <x:c r="D3" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Guayabita del Perú</x:v>
       </x:c>
       <x:c r="E3" s="11" t="str">
-        <x:v>Insectos chupadores / preventivo suave</x:v>
+        <x:v>🌳</x:v>
       </x:c>
       <x:c r="F3" s="11" t="str">
-        <x:v>No aplicar con sol fuerte; verificar etiqueta</x:v>
+        <x:v>Vegetativo</x:v>
       </x:c>
       <x:c r="G3" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="H3" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
+        <x:v>Bueno</x:v>
       </x:c>
       <x:c r="I3" s="11" t="str">
-        <x:v>ml/L</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="J3" s="11" t="str">
-        <x:v>Preventivo / presión baja de plaga</x:v>
-      </x:c>
-      <x:c r="K3" s="11" t="n">
-        <x:v>10</x:v>
+        <x:v>Guayabita del Perú está en Moravia</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>INS_JABON_POTASICO</x:v>
+        <x:v>ARB_GUAYABA_FRAILES</x:v>
       </x:c>
       <x:c r="B4" s="11" t="str">
-        <x:v>Jabón potásico</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C4" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="D4" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Guayaba</x:v>
       </x:c>
       <x:c r="E4" s="11" t="str">
-        <x:v>Insectos blandos y limpieza de melaza</x:v>
+        <x:v>🌳</x:v>
       </x:c>
       <x:c r="F4" s="11" t="str">
-        <x:v>Probar en pocas hojas primero</x:v>
+        <x:v>Floración</x:v>
       </x:c>
       <x:c r="G4" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="H4" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
+        <x:v>Bueno</x:v>
       </x:c>
       <x:c r="I4" s="11" t="str">
-        <x:v>ml/L</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="J4" s="11" t="str">
-        <x:v>Presencia de áfidos/cochinilla/mosca blanca</x:v>
-      </x:c>
-      <x:c r="K4" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>Diferente a Guayabita del Perú</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
-        <x:v>INS_MISTRAL</x:v>
+        <x:v>ARB_GUANABANA_FRAILES</x:v>
       </x:c>
       <x:c r="B5" s="11" t="str">
-        <x:v>Mistral</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C5" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D5" s="11" t="str">
+        <x:v>Guanábana</x:v>
+      </x:c>
+      <x:c r="E5" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F5" s="11" t="str">
+        <x:v>Fructificación</x:v>
+      </x:c>
+      <x:c r="G5" s="11" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="H5" s="11" t="str">
+        <x:v>Atención</x:v>
+      </x:c>
+      <x:c r="I5" s="11" t="str">
         <x:v>Control fitosanitario</x:v>
       </x:c>
-      <x:c r="D5" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E5" s="11" t="str">
-        <x:v>Control fitosanitario correctivo/preventivo</x:v>
-      </x:c>
-      <x:c r="F5" s="11" t="str">
-        <x:v>Usar solo cuando corresponda; respetar etiqueta</x:v>
-      </x:c>
-      <x:c r="G5" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H5" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="I5" s="11" t="str">
-        <x:v>ml/L o g/L</x:v>
-      </x:c>
       <x:c r="J5" s="11" t="str">
-        <x:v>Presión sanitaria / calendario preventivo</x:v>
-      </x:c>
-      <x:c r="K5" s="11" t="n">
-        <x:v>15</x:v>
+        <x:v>Puntos negros en frutos</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
-        <x:v>INS_BICARBONATO</x:v>
+        <x:v>ARB_NARANJA_WASH_FRAILES</x:v>
       </x:c>
       <x:c r="B6" s="11" t="str">
-        <x:v>Bicarbonato de sodio</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C6" s="11" t="str">
-        <x:v>Control fitosanitario</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="D6" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Naranja Washington</x:v>
       </x:c>
       <x:c r="E6" s="11" t="str">
-        <x:v>Apoyo preventivo en hongos superficiales</x:v>
+        <x:v>🍊</x:v>
       </x:c>
       <x:c r="F6" s="11" t="str">
-        <x:v>Evitar exceso; puede quemar hojas</x:v>
+        <x:v>Vegetativo</x:v>
       </x:c>
       <x:c r="G6" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>Jul 2025</x:v>
       </x:c>
       <x:c r="H6" s="11" t="str">
-        <x:v>Baja dosis</x:v>
+        <x:v>Bueno</x:v>
       </x:c>
       <x:c r="I6" s="11" t="str">
-        <x:v>g/L</x:v>
+        <x:v>Abono tierra</x:v>
       </x:c>
       <x:c r="J6" s="11" t="str">
-        <x:v>Prevención ligera / humedad alta</x:v>
-      </x:c>
-      <x:c r="K6" s="11" t="n">
-        <x:v>7</x:v>
+        <x:v>Trasplante 2025</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
-        <x:v>INS_CAL_DOLOMITA</x:v>
+        <x:v>ARB_NARANJA_VALENCIA_FRAILES</x:v>
       </x:c>
       <x:c r="B7" s="11" t="str">
-        <x:v>Cal dolomita</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C7" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D7" s="11" t="str">
+        <x:v>Naranja Valencia</x:v>
+      </x:c>
+      <x:c r="E7" s="11" t="str">
+        <x:v>🍊</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H7" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I7" s="11" t="str">
         <x:v>Abono tierra</x:v>
       </x:c>
-      <x:c r="D7" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E7" s="11" t="str">
-        <x:v>Enmienda de suelo, calcio/magnesio</x:v>
-      </x:c>
-      <x:c r="F7" s="11" t="str">
-        <x:v>No tocar tronco; ideal corona con distancia</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H7" s="11" t="str">
-        <x:v>Según tamaño/edad del árbol</x:v>
-      </x:c>
-      <x:c r="I7" s="11" t="str">
-        <x:v>kg/árbol o g/cama</x:v>
-      </x:c>
       <x:c r="J7" s="11" t="str">
-        <x:v>Postcosecha / enmienda de corona</x:v>
-      </x:c>
-      <x:c r="K7" s="11" t="n">
-        <x:v>180</x:v>
+        <x:v>Trasplante 2025</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
-        <x:v>INS_CENIZA</x:v>
+        <x:v>ARB_LIMON_MANDARINA_FRAILES</x:v>
       </x:c>
       <x:c r="B8" s="11" t="str">
-        <x:v>Ceniza</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C8" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D8" s="11" t="str">
+        <x:v>Limón mandarina</x:v>
+      </x:c>
+      <x:c r="E8" s="11" t="str">
+        <x:v>🍋</x:v>
+      </x:c>
+      <x:c r="F8" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G8" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H8" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I8" s="11" t="str">
         <x:v>Abono tierra</x:v>
       </x:c>
-      <x:c r="D8" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E8" s="11" t="str">
-        <x:v>Potasio/enmienda ligera</x:v>
-      </x:c>
-      <x:c r="F8" s="11" t="str">
-        <x:v>Usar moderado; no exceder en suelos alcalinos</x:v>
-      </x:c>
-      <x:c r="G8" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H8" s="11" t="str">
-        <x:v>Puñado controlado</x:v>
-      </x:c>
-      <x:c r="I8" s="11" t="str">
-        <x:v>g/cama o g/árbol</x:v>
-      </x:c>
       <x:c r="J8" s="11" t="str">
-        <x:v>Postcosecha / crecimiento</x:v>
-      </x:c>
-      <x:c r="K8" s="11" t="n">
-        <x:v>45</x:v>
+        <x:v>Trasplante 2025</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
-        <x:v>INS_MELASA</x:v>
+        <x:v>ARB_LIMON_MESINO_FRAILES</x:v>
       </x:c>
       <x:c r="B9" s="11" t="str">
-        <x:v>Melasa</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C9" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D9" s="11" t="str">
+        <x:v>Limón mesino</x:v>
+      </x:c>
+      <x:c r="E9" s="11" t="str">
+        <x:v>🍋</x:v>
+      </x:c>
+      <x:c r="F9" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G9" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H9" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I9" s="11" t="str">
         <x:v>Abono tierra</x:v>
       </x:c>
-      <x:c r="D9" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E9" s="11" t="str">
-        <x:v>Apoyo microbiológico / mezcla compost</x:v>
-      </x:c>
-      <x:c r="F9" s="11" t="str">
-        <x:v>No exceder; evitar atraer hormigas</x:v>
-      </x:c>
-      <x:c r="G9" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H9" s="11" t="str">
-        <x:v>Baja dosis</x:v>
-      </x:c>
-      <x:c r="I9" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
       <x:c r="J9" s="11" t="str">
-        <x:v>Activación biológica / compost</x:v>
-      </x:c>
-      <x:c r="K9" s="11" t="n">
-        <x:v>30</x:v>
+        <x:v>Trasplante 2025</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
-        <x:v>INS_COMPOST</x:v>
+        <x:v>ARB_LIMON_DULCE_FRAILES</x:v>
       </x:c>
       <x:c r="B10" s="11" t="str">
-        <x:v>Compost</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C10" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D10" s="11" t="str">
+        <x:v>Limón dulce</x:v>
+      </x:c>
+      <x:c r="E10" s="11" t="str">
+        <x:v>🍋</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>Vegetativo</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>Jul 2025</x:v>
+      </x:c>
+      <x:c r="H10" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I10" s="11" t="str">
         <x:v>Abono tierra</x:v>
       </x:c>
-      <x:c r="D10" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E10" s="11" t="str">
-        <x:v>Materia orgánica y estructura de suelo</x:v>
-      </x:c>
-      <x:c r="F10" s="11" t="str">
-        <x:v>No cubrir pegado al tronco</x:v>
-      </x:c>
-      <x:c r="G10" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H10" s="11" t="str">
-        <x:v>Capa superficial</x:v>
-      </x:c>
-      <x:c r="I10" s="11" t="str">
-        <x:v>kg/cama o kg/árbol</x:v>
-      </x:c>
       <x:c r="J10" s="11" t="str">
-        <x:v>Siembra / postcosecha / mantenimiento</x:v>
-      </x:c>
-      <x:c r="K10" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>Trasplante 2025</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
-        <x:v>INS_HENO</x:v>
+        <x:v>ARB_MANDARINA_FRAILES</x:v>
       </x:c>
       <x:c r="B11" s="11" t="str">
-        <x:v>Heno</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C11" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="D11" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Mandarina</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>Cobertura/mulch y humedad</x:v>
+        <x:v>🍊</x:v>
       </x:c>
       <x:c r="F11" s="11" t="str">
-        <x:v>No tocar base del tronco</x:v>
+        <x:v>Brotes</x:v>
       </x:c>
       <x:c r="G11" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>Jul 2025</x:v>
       </x:c>
       <x:c r="H11" s="11" t="str">
-        <x:v>Capa de cobertura</x:v>
+        <x:v>Bueno</x:v>
       </x:c>
       <x:c r="I11" s="11" t="str">
-        <x:v>cm de cobertura</x:v>
+        <x:v>Abono foliar</x:v>
       </x:c>
       <x:c r="J11" s="11" t="str">
-        <x:v>Época seca / conservación humedad</x:v>
-      </x:c>
-      <x:c r="K11" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>Trasplante 2025</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
-        <x:v>INS_GALLINAZA</x:v>
+        <x:v>ARB_ANONA_FRAILES</x:v>
       </x:c>
       <x:c r="B12" s="11" t="str">
-        <x:v>Gallinaza</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C12" s="11" t="str">
-        <x:v>Abono tierra</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="D12" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Anona</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>Nitrógeno y fertilidad de suelo</x:v>
+        <x:v>🌳</x:v>
       </x:c>
       <x:c r="F12" s="11" t="str">
-        <x:v>Debe estar compostada; puede quemar</x:v>
+        <x:v>Recuperación</x:v>
       </x:c>
       <x:c r="G12" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="H12" s="11" t="str">
-        <x:v>Muy moderado</x:v>
+        <x:v>Estrés</x:v>
       </x:c>
       <x:c r="I12" s="11" t="str">
-        <x:v>g/cama o g/árbol</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="J12" s="11" t="str">
-        <x:v>Vegetativo / recuperación</x:v>
-      </x:c>
-      <x:c r="K12" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>Defoliación/recuperación</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
-        <x:v>INS_YARAMILA</x:v>
+        <x:v>ARB_NISPERO_FRAILES</x:v>
       </x:c>
       <x:c r="B13" s="11" t="str">
-        <x:v>YaraMila</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C13" s="11" t="str">
+        <x:v>Frailes</x:v>
+      </x:c>
+      <x:c r="D13" s="11" t="str">
+        <x:v>Níspero</x:v>
+      </x:c>
+      <x:c r="E13" s="11" t="str">
+        <x:v>🌳</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>Establecimiento</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>Reciente</x:v>
+      </x:c>
+      <x:c r="H13" s="11" t="str">
+        <x:v>Bueno</x:v>
+      </x:c>
+      <x:c r="I13" s="11" t="str">
         <x:v>Abono tierra</x:v>
       </x:c>
-      <x:c r="D13" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E13" s="11" t="str">
-        <x:v>Fertilización NPK para crecimiento/fructificación</x:v>
-      </x:c>
-      <x:c r="F13" s="11" t="str">
-        <x:v>Evitar estrés hídrico; ajustar a tamaño del árbol</x:v>
-      </x:c>
-      <x:c r="G13" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H13" s="11" t="str">
-        <x:v>Según tamaño/edad; iniciar bajo</x:v>
-      </x:c>
-      <x:c r="I13" s="11" t="str">
-        <x:v>g/árbol o g/cama</x:v>
-      </x:c>
       <x:c r="J13" s="11" t="str">
-        <x:v>Vegetativo / postcosecha / prefloración según cultivo</x:v>
-      </x:c>
-      <x:c r="K13" s="11" t="n">
-        <x:v>60</x:v>
+        <x:v>Árbol joven</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
-        <x:v>INS_CALCIO_BORO</x:v>
+        <x:v>ARB_DURAZNO_FRAILES</x:v>
       </x:c>
       <x:c r="B14" s="11" t="str">
-        <x:v>Calcio Boro</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C14" s="11" t="str">
-        <x:v>Abono foliar</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="D14" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Durazno</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>Floración, cuajado y llenado temprano</x:v>
+        <x:v>🌸</x:v>
       </x:c>
       <x:c r="F14" s="11" t="str">
-        <x:v>No aplicar con calor fuerte; revisar mezcla</x:v>
+        <x:v>Vegetativo</x:v>
       </x:c>
       <x:c r="G14" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="H14" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
+        <x:v>Bueno</x:v>
       </x:c>
       <x:c r="I14" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="J14" s="11" t="str">
-        <x:v>Floración / cuajado / llenado temprano</x:v>
-      </x:c>
-      <x:c r="K14" s="11" t="n">
-        <x:v>10</x:v>
-      </x:c>
+        <x:v>Poda</x:v>
+      </x:c>
+      <x:c r="J14" s="11" t="str"/>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
-        <x:v>INS_MULTIMINERAL</x:v>
+        <x:v>ARB_MANGO_FRAILES</x:v>
       </x:c>
       <x:c r="B15" s="11" t="str">
-        <x:v>Multimineral</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C15" s="11" t="str">
-        <x:v>Abono foliar</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="D15" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Mango peludo</x:v>
       </x:c>
       <x:c r="E15" s="11" t="str">
-        <x:v>Micronutrientes y apoyo general</x:v>
+        <x:v>🥭</x:v>
       </x:c>
       <x:c r="F15" s="11" t="str">
-        <x:v>No mezclar sin validar compatibilidad</x:v>
+        <x:v>Vegetativo</x:v>
       </x:c>
       <x:c r="G15" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="H15" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
+        <x:v>Bueno</x:v>
       </x:c>
       <x:c r="I15" s="11" t="str">
-        <x:v>ml/L</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="J15" s="11" t="str">
-        <x:v>Vegetativo / recuperación / soporte general</x:v>
-      </x:c>
-      <x:c r="K15" s="11" t="n">
-        <x:v>21</x:v>
+        <x:v>Mango 10 años</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
-        <x:v>INS_FOLIAR_7_4_25</x:v>
+        <x:v>ARB_MAMON_CHINO_FRAILES</x:v>
       </x:c>
       <x:c r="B16" s="11" t="str">
-        <x:v>Foliar 7-4-25</x:v>
+        <x:v>FIN_FRAILES</x:v>
       </x:c>
       <x:c r="C16" s="11" t="str">
-        <x:v>Abono foliar</x:v>
+        <x:v>Frailes</x:v>
       </x:c>
       <x:c r="D16" s="11" t="str">
-        <x:v>Sí</x:v>
+        <x:v>Mamón chino</x:v>
       </x:c>
       <x:c r="E16" s="11" t="str">
-        <x:v>Apoyo potasio/llenado</x:v>
+        <x:v>🌳</x:v>
       </x:c>
       <x:c r="F16" s="11" t="str">
-        <x:v>Evitar exceso; aplicar temprano/tarde</x:v>
+        <x:v>Recuperación</x:v>
       </x:c>
       <x:c r="G16" s="11" t="str">
-        <x:v>No</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="H16" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
+        <x:v>Atención</x:v>
       </x:c>
       <x:c r="I16" s="11" t="str">
-        <x:v>ml/L</x:v>
+        <x:v>Control fitosanitario</x:v>
       </x:c>
       <x:c r="J16" s="11" t="str">
-        <x:v>Llenado de fruto / desarrollo</x:v>
-      </x:c>
-      <x:c r="K16" s="11" t="n">
-        <x:v>15</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17">
-      <x:c r="A17" s="11" t="str">
-        <x:v>INS_PAS80</x:v>
-      </x:c>
-      <x:c r="B17" s="11" t="str">
-        <x:v>PAS-80</x:v>
-      </x:c>
-      <x:c r="C17" s="11" t="str">
-        <x:v>Coadyuvante</x:v>
-      </x:c>
-      <x:c r="D17" s="11" t="str">
-        <x:v>Sí</x:v>
-      </x:c>
-      <x:c r="E17" s="11" t="str">
-        <x:v>Adherente/dispersante para mezcla</x:v>
-      </x:c>
-      <x:c r="F17" s="11" t="str">
-        <x:v>Usar dosis indicada; no guardar mezcla vieja</x:v>
-      </x:c>
-      <x:c r="G17" s="11" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="H17" s="11" t="str">
-        <x:v>Según etiqueta</x:v>
-      </x:c>
-      <x:c r="I17" s="11" t="str">
-        <x:v>ml/L</x:v>
-      </x:c>
-      <x:c r="J17" s="11" t="str">
-        <x:v>Cuando la mezcla foliar lo requiera</x:v>
-      </x:c>
-      <x:c r="K17" s="11" t="n">
-        <x:v>0</x:v>
+        <x:v>Afectación por viento</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/FincaOS_Data.xlsx
+++ b/FincaOS_Data.xlsx
@@ -2,16 +2,16 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="R9aad752ec9a94537"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="R4227a49d0f304110"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="R9dd6a40f9cb141f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="Rc586b383e229446b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R7b4481c77f444a7a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="Ra67245b67036419c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rec6e71267c9e4fd7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="8" r:id="R92d437cfcdcb4aa4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arboles" sheetId="9" r:id="R4f69b264cfb94400"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventosAgricolas" sheetId="10" r:id="Rcf79399ec49c4a7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard_MVP" sheetId="1" r:id="Rb7f887c168534185"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fincas" sheetId="2" r:id="Rf0569c01504e4751"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Unidades" sheetId="3" r:id="Rf19c455c24a84c02"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CatalogoCultivos" sheetId="4" r:id="Ra4b413b9fe29427e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CultivosSembrados" sheetId="5" r:id="R46a07e26a3fd49b7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VistaCultivos" sheetId="6" r:id="R37182d96bffb4887"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Listas" sheetId="7" r:id="Rd722c5f4479548c9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Insumos" sheetId="8" r:id="R56f712c4e29a48f6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arboles" sheetId="9" r:id="R510d3cef9ec44d32"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventosAgricolas" sheetId="10" r:id="Rc36c01b373524560"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -872,16 +872,151 @@
       </x:c>
     </x:row>
     <x:row r="9">
+      <x:c r="A9" t="str">
+        <x:v>EVT_008</x:v>
+      </x:c>
+      <x:c r="B9" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C9" t="str">
+        <x:v>INS_MISTRAL</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="E9" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F9" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="G9" t="str">
+        <x:v>Manzano tico - Moravia</x:v>
+      </x:c>
+      <x:c r="H9" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="J9"/>
+      <x:c r="K9"/>
+      <x:c r="L9"/>
+      <x:c r="M9"/>
+      <x:c r="N9" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="O9" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
       <x:c r="P9" s="18"/>
-      <x:c r="Q9" s="18"/>
+      <x:c r="Q9" s="18" t="n">
+        <x:v>46181</x:v>
+      </x:c>
+      <x:c r="R9" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="S9" t="str">
+        <x:v>Historial: control fitosanitario aplicado</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
+      <x:c r="A10" t="str">
+        <x:v>EVT_009</x:v>
+      </x:c>
+      <x:c r="B10" t="str">
+        <x:v>Control fitosanitario</x:v>
+      </x:c>
+      <x:c r="C10" t="str">
+        <x:v>INS_MISTRAL</x:v>
+      </x:c>
+      <x:c r="D10" t="str">
+        <x:v>Mistral</x:v>
+      </x:c>
+      <x:c r="E10" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F10" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="G10" t="str">
+        <x:v>Manzano tico - Moravia</x:v>
+      </x:c>
+      <x:c r="H10" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="J10"/>
+      <x:c r="K10"/>
+      <x:c r="L10"/>
+      <x:c r="M10"/>
+      <x:c r="N10" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="O10" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
       <x:c r="P10" s="18"/>
-      <x:c r="Q10" s="18"/>
+      <x:c r="Q10" s="18" t="n">
+        <x:v>46154</x:v>
+      </x:c>
+      <x:c r="R10" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="S10" t="str">
+        <x:v>Historial: control previo</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
+      <x:c r="A11" t="str">
+        <x:v>EVT_010</x:v>
+      </x:c>
+      <x:c r="B11" t="str">
+        <x:v>Abono tierra</x:v>
+      </x:c>
+      <x:c r="C11" t="str">
+        <x:v>INS_YARAMILA</x:v>
+      </x:c>
+      <x:c r="D11" t="str">
+        <x:v>YaraMila</x:v>
+      </x:c>
+      <x:c r="E11" t="str">
+        <x:v>Arbol</x:v>
+      </x:c>
+      <x:c r="F11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="G11" t="str">
+        <x:v>Manzano tico - Moravia</x:v>
+      </x:c>
+      <x:c r="H11" t="str">
+        <x:v>FIN_MORAVIA</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Moravia</x:v>
+      </x:c>
+      <x:c r="J11"/>
+      <x:c r="K11"/>
+      <x:c r="L11"/>
+      <x:c r="M11"/>
+      <x:c r="N11" t="str">
+        <x:v>ARB_MANZANO_MORAVIA</x:v>
+      </x:c>
+      <x:c r="O11" t="str">
+        <x:v>Manzano tico</x:v>
+      </x:c>
       <x:c r="P11" s="18"/>
-      <x:c r="Q11" s="18"/>
+      <x:c r="Q11" s="18" t="n">
+        <x:v>46132</x:v>
+      </x:c>
+      <x:c r="R11" t="str">
+        <x:v>Completado</x:v>
+      </x:c>
+      <x:c r="S11" t="str">
+        <x:v>Historial: abonada de tierra</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="P12" s="18"/>
@@ -1299,7 +1434,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2c2aa61fcde94ed2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a142f89001f4c2f"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1487,7 +1622,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1f4a4299ed9a4465"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7057e33a034744a0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1953,7 +2088,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R92f6337ef8614c14"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re93c6e87d4b543f6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -3281,7 +3416,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Refc14cba555b43ec"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbba4109d898f47ca"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4931,7 +5066,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R24f9597babe14961"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d02400a87c9411a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5011,7 +5146,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc327f05eb480415e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R363939c737774509"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5051,6 +5186,15 @@
       <x:c r="G1" s="24" t="str">
         <x:v>Compra_Requerida</x:v>
       </x:c>
+      <x:c r="H1" t="str">
+        <x:v>Cantidad_Guia</x:v>
+      </x:c>
+      <x:c r="I1" t="str">
+        <x:v>Momento_Aplicacion</x:v>
+      </x:c>
+      <x:c r="J1" t="str">
+        <x:v>Frecuencia_Dias</x:v>
+      </x:c>
     </x:row>
     <x:row r="2">
       <x:c r="A2" s="11" t="str">
@@ -5074,6 +5218,15 @@
       <x:c r="G2" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H2" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I2" t="str">
+        <x:v>Preventivo / presión de hongos</x:v>
+      </x:c>
+      <x:c r="J2" t="n">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="11" t="str">
@@ -5097,6 +5250,15 @@
       <x:c r="G3" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H3" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I3" t="str">
+        <x:v>Preventivo / presión de insectos</x:v>
+      </x:c>
+      <x:c r="J3" t="n">
+        <x:v>15</x:v>
+      </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
@@ -5120,6 +5282,15 @@
       <x:c r="G4" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H4" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I4" t="str">
+        <x:v>Presencia de insectos blandos</x:v>
+      </x:c>
+      <x:c r="J4" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="11" t="str">
@@ -5143,6 +5314,15 @@
       <x:c r="G5" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H5" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I5" t="str">
+        <x:v>Preventivo / control activo</x:v>
+      </x:c>
+      <x:c r="J5" t="n">
+        <x:v>30</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="11" t="str">
@@ -5166,6 +5346,15 @@
       <x:c r="G6" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H6" t="str">
+        <x:v>Baja dosis</x:v>
+      </x:c>
+      <x:c r="I6" t="str">
+        <x:v>Preventivo hongos superficiales</x:v>
+      </x:c>
+      <x:c r="J6" t="n">
+        <x:v>10</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="11" t="str">
@@ -5189,6 +5378,15 @@
       <x:c r="G7" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H7" t="str">
+        <x:v>Según tamaño de árbol</x:v>
+      </x:c>
+      <x:c r="I7" t="str">
+        <x:v>Postcosecha / preparación de suelo</x:v>
+      </x:c>
+      <x:c r="J7" t="n">
+        <x:v>180</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="11" t="str">
@@ -5212,6 +5410,15 @@
       <x:c r="G8" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H8" t="str">
+        <x:v>Puñado controlado</x:v>
+      </x:c>
+      <x:c r="I8" t="str">
+        <x:v>Postcosecha / desarrollo vegetativo</x:v>
+      </x:c>
+      <x:c r="J8" t="n">
+        <x:v>60</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="11" t="str">
@@ -5235,6 +5442,15 @@
       <x:c r="G9" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H9" t="str">
+        <x:v>Baja dosis</x:v>
+      </x:c>
+      <x:c r="I9" t="str">
+        <x:v>Activación biológica / compost</x:v>
+      </x:c>
+      <x:c r="J9" t="n">
+        <x:v>30</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="11" t="str">
@@ -5258,6 +5474,15 @@
       <x:c r="G10" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H10" t="str">
+        <x:v>Capa superficial</x:v>
+      </x:c>
+      <x:c r="I10" t="str">
+        <x:v>Postcosecha / establecimiento</x:v>
+      </x:c>
+      <x:c r="J10" t="n">
+        <x:v>90</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="11" t="str">
@@ -5281,6 +5506,15 @@
       <x:c r="G11" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H11" t="str">
+        <x:v>Cobertura sin tocar tronco</x:v>
+      </x:c>
+      <x:c r="I11" t="str">
+        <x:v>Época seca / protección de suelo</x:v>
+      </x:c>
+      <x:c r="J11" t="n">
+        <x:v>60</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="11" t="str">
@@ -5304,6 +5538,15 @@
       <x:c r="G12" s="11" t="str">
         <x:v>Sí</x:v>
       </x:c>
+      <x:c r="H12" t="str">
+        <x:v>Solo compostada</x:v>
+      </x:c>
+      <x:c r="I12" t="str">
+        <x:v>Vegetativo / recuperación</x:v>
+      </x:c>
+      <x:c r="J12" t="n">
+        <x:v>90</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="11" t="str">
@@ -5327,6 +5570,15 @@
       <x:c r="G13" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H13" t="str">
+        <x:v>Según tamaño de árbol</x:v>
+      </x:c>
+      <x:c r="I13" t="str">
+        <x:v>Floración / postcosecha / vegetativo</x:v>
+      </x:c>
+      <x:c r="J13" t="n">
+        <x:v>45</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="11" t="str">
@@ -5350,6 +5602,15 @@
       <x:c r="G14" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H14" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I14" t="str">
+        <x:v>Floración / cuajado / llenado temprano</x:v>
+      </x:c>
+      <x:c r="J14" t="n">
+        <x:v>15</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="11" t="str">
@@ -5373,6 +5634,15 @@
       <x:c r="G15" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H15" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I15" t="str">
+        <x:v>Vegetativo / recuperación</x:v>
+      </x:c>
+      <x:c r="J15" t="n">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="11" t="str">
@@ -5396,6 +5666,15 @@
       <x:c r="G16" s="11" t="str">
         <x:v>No</x:v>
       </x:c>
+      <x:c r="H16" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I16" t="str">
+        <x:v>Llenado / desarrollo</x:v>
+      </x:c>
+      <x:c r="J16" t="n">
+        <x:v>21</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="11" t="str">
@@ -5418,6 +5697,15 @@
       </x:c>
       <x:c r="G17" s="11" t="str">
         <x:v>No</x:v>
+      </x:c>
+      <x:c r="H17" t="str">
+        <x:v>Según etiqueta</x:v>
+      </x:c>
+      <x:c r="I17" t="str">
+        <x:v>Coadyuvante en aplicaciones foliares</x:v>
+      </x:c>
+      <x:c r="J17" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
